--- a/Predictions/rolling_gt_next_tick_with_pv.xlsx
+++ b/Predictions/rolling_gt_next_tick_with_pv.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1107624843716621</v>
+        <v>0.1107624769210815</v>
       </c>
       <c r="B2" t="n">
         <v>0.7629929184913635</v>
       </c>
       <c r="C2" t="n">
-        <v>21.44140815734863</v>
+        <v>21.44140625</v>
       </c>
       <c r="D2" t="n">
-        <v>6.114813327789307</v>
+        <v>6.114814281463623</v>
       </c>
       <c r="E2" t="n">
         <v>1.687668561935425</v>
@@ -490,7 +490,7 @@
         <v>16.07298469543457</v>
       </c>
       <c r="G2" t="n">
-        <v>55.25888061523438</v>
+        <v>55.25887680053711</v>
       </c>
       <c r="H2" t="n">
         <v>-4.423366069793701</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1374953985214233</v>
+        <v>0.1374954283237457</v>
       </c>
       <c r="B3" t="n">
         <v>0.8006601929664612</v>
@@ -507,10 +507,10 @@
         <v>19.59602355957031</v>
       </c>
       <c r="D3" t="n">
-        <v>5.919834613800049</v>
+        <v>5.919833660125732</v>
       </c>
       <c r="E3" t="n">
-        <v>2.981912136077881</v>
+        <v>2.981911897659302</v>
       </c>
       <c r="F3" t="n">
         <v>19.03303527832031</v>
@@ -519,12 +519,12 @@
         <v>55.29248809814453</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.138886213302612</v>
+        <v>-1.138886451721191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1669481098651886</v>
+        <v>0.166948139667511</v>
       </c>
       <c r="B4" t="n">
         <v>0.8350825905799866</v>
@@ -533,7 +533,7 @@
         <v>17.61653137207031</v>
       </c>
       <c r="D4" t="n">
-        <v>5.380171298980713</v>
+        <v>5.380170345306396</v>
       </c>
       <c r="E4" t="n">
         <v>3.968274831771851</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1985412538051605</v>
+        <v>0.1985412836074829</v>
       </c>
       <c r="B5" t="n">
         <v>0.865940272808075</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.2312982678413391</v>
+        <v>0.2312982976436615</v>
       </c>
       <c r="B6" t="n">
         <v>0.8934224843978882</v>
@@ -585,19 +585,19 @@
         <v>13.49853134155273</v>
       </c>
       <c r="D6" t="n">
-        <v>3.635778903961182</v>
+        <v>3.635779857635498</v>
       </c>
       <c r="E6" t="n">
-        <v>5.488000392913818</v>
+        <v>5.48799991607666</v>
       </c>
       <c r="F6" t="n">
-        <v>26.14764976501465</v>
+        <v>26.14765167236328</v>
       </c>
       <c r="G6" t="n">
         <v>46.0722541809082</v>
       </c>
       <c r="H6" t="n">
-        <v>6.949481010437012</v>
+        <v>6.949480533599854</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         <v>11.46507358551025</v>
       </c>
       <c r="D7" t="n">
-        <v>2.587293148040771</v>
+        <v>2.587292194366455</v>
       </c>
       <c r="E7" t="n">
         <v>6.158910751342773</v>
@@ -620,7 +620,7 @@
         <v>27.96586418151855</v>
       </c>
       <c r="G7" t="n">
-        <v>40.49612045288086</v>
+        <v>40.49611663818359</v>
       </c>
       <c r="H7" t="n">
         <v>8.029861450195312</v>
@@ -631,16 +631,16 @@
         <v>0.2967199087142944</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9389623403549194</v>
+        <v>0.9389622807502747</v>
       </c>
       <c r="C8" t="n">
         <v>9.480586051940918</v>
       </c>
       <c r="D8" t="n">
-        <v>1.515555024147034</v>
+        <v>1.515554904937744</v>
       </c>
       <c r="E8" t="n">
-        <v>6.814532279968262</v>
+        <v>6.814531803131104</v>
       </c>
       <c r="F8" t="n">
         <v>29.4472770690918</v>
@@ -663,39 +663,39 @@
         <v>7.545021057128906</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4990278482437134</v>
+        <v>0.4990276992321014</v>
       </c>
       <c r="E9" t="n">
         <v>7.496321678161621</v>
       </c>
       <c r="F9" t="n">
-        <v>30.52943801879883</v>
+        <v>30.52943992614746</v>
       </c>
       <c r="G9" t="n">
         <v>26.73877334594727</v>
       </c>
       <c r="H9" t="n">
-        <v>7.803411483764648</v>
+        <v>7.80341100692749</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.3592848479747772</v>
+        <v>0.3592848181724548</v>
       </c>
       <c r="B10" t="n">
         <v>0.968774139881134</v>
       </c>
       <c r="C10" t="n">
-        <v>5.665897369384766</v>
+        <v>5.665896892547607</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3710817098617554</v>
+        <v>-0.3710818588733673</v>
       </c>
       <c r="E10" t="n">
         <v>8.258571624755859</v>
       </c>
       <c r="F10" t="n">
-        <v>31.18669128417969</v>
+        <v>31.18669319152832</v>
       </c>
       <c r="G10" t="n">
         <v>19.17094230651855</v>
@@ -712,22 +712,22 @@
         <v>0.9764173626899719</v>
       </c>
       <c r="C11" t="n">
-        <v>3.868793249130249</v>
+        <v>3.868793964385986</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9978708028793335</v>
+        <v>-0.9978709816932678</v>
       </c>
       <c r="E11" t="n">
-        <v>9.133467674255371</v>
+        <v>9.133468627929688</v>
       </c>
       <c r="F11" t="n">
         <v>31.4458179473877</v>
       </c>
       <c r="G11" t="n">
-        <v>11.62716674804688</v>
+        <v>11.62716579437256</v>
       </c>
       <c r="H11" t="n">
-        <v>5.568443775177002</v>
+        <v>5.568443298339844</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C12" t="n">
-        <v>2.187930822372437</v>
+        <v>2.187931537628174</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.318833708763123</v>
+        <v>-1.318831920623779</v>
       </c>
       <c r="E12" t="n">
         <v>10.08470821380615</v>
@@ -750,7 +750,7 @@
         <v>31.3984489440918</v>
       </c>
       <c r="G12" t="n">
-        <v>4.618947505950928</v>
+        <v>4.618947982788086</v>
       </c>
       <c r="H12" t="n">
         <v>4.522222995758057</v>
@@ -764,10 +764,10 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C13" t="n">
-        <v>0.650766134262085</v>
+        <v>0.6507658362388611</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.312886595726013</v>
+        <v>-1.312886714935303</v>
       </c>
       <c r="E13" t="n">
         <v>11.02143955230713</v>
@@ -776,10 +776,10 @@
         <v>31.20336723327637</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.256485462188721</v>
+        <v>-1.256487011909485</v>
       </c>
       <c r="H13" t="n">
-        <v>4.039758682250977</v>
+        <v>4.039758205413818</v>
       </c>
     </row>
     <row r="14">
@@ -790,22 +790,22 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.7364141941070557</v>
+        <v>-0.7364144921302795</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9886602163314819</v>
+        <v>-0.9886603951454163</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83179378509521</v>
+        <v>11.8317928314209</v>
       </c>
       <c r="F14" t="n">
         <v>30.99928665161133</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.457664966583252</v>
+        <v>-5.457664489746094</v>
       </c>
       <c r="H14" t="n">
-        <v>4.073398113250732</v>
+        <v>4.073397636413574</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.997195482254028</v>
+        <v>-1.997194766998291</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3740171194076538</v>
+        <v>-0.3740153610706329</v>
       </c>
       <c r="E15" t="n">
         <v>12.39922714233398</v>
@@ -828,10 +828,10 @@
         <v>30.85886573791504</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.632524967193604</v>
+        <v>-7.632524490356445</v>
       </c>
       <c r="H15" t="n">
-        <v>4.258270740509033</v>
+        <v>4.258270263671875</v>
       </c>
     </row>
     <row r="16">
@@ -842,10 +842,10 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C16" t="n">
-        <v>-3.188065767288208</v>
+        <v>-3.188065052032471</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4734827280044556</v>
+        <v>0.4734825789928436</v>
       </c>
       <c r="E16" t="n">
         <v>12.64423179626465</v>
@@ -854,10 +854,10 @@
         <v>30.77327919006348</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.68272066116333</v>
+        <v>-7.682722091674805</v>
       </c>
       <c r="H16" t="n">
-        <v>4.103098392486572</v>
+        <v>4.103097915649414</v>
       </c>
     </row>
     <row r="17">
@@ -868,22 +868,22 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C17" t="n">
-        <v>-4.351275444030762</v>
+        <v>-4.351274967193604</v>
       </c>
       <c r="D17" t="n">
-        <v>1.528610825538635</v>
+        <v>1.528610706329346</v>
       </c>
       <c r="E17" t="n">
         <v>12.49044704437256</v>
       </c>
       <c r="F17" t="n">
-        <v>30.66972732543945</v>
+        <v>30.66972923278809</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.047764301300049</v>
+        <v>-6.047765731811523</v>
       </c>
       <c r="H17" t="n">
-        <v>3.16002345085144</v>
+        <v>3.160023212432861</v>
       </c>
     </row>
     <row r="18">
@@ -894,22 +894,22 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C18" t="n">
-        <v>-5.475905418395996</v>
+        <v>-5.475904941558838</v>
       </c>
       <c r="D18" t="n">
         <v>2.834546566009521</v>
       </c>
       <c r="E18" t="n">
-        <v>11.81196022033691</v>
+        <v>11.8119592666626</v>
       </c>
       <c r="F18" t="n">
         <v>30.48380851745605</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.294216632843018</v>
+        <v>-3.294218301773071</v>
       </c>
       <c r="H18" t="n">
-        <v>1.22650408744812</v>
+        <v>1.226503968238831</v>
       </c>
     </row>
     <row r="19">
@@ -920,10 +920,10 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C19" t="n">
-        <v>-6.448916435241699</v>
+        <v>-6.448917865753174</v>
       </c>
       <c r="D19" t="n">
-        <v>4.556563854217529</v>
+        <v>4.556564807891846</v>
       </c>
       <c r="E19" t="n">
         <v>10.3313102722168</v>
@@ -932,10 +932,10 @@
         <v>30.19507789611816</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06810718774795532</v>
+        <v>0.06810939311981201</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.259037494659424</v>
+        <v>-1.259037256240845</v>
       </c>
     </row>
     <row r="20">
@@ -946,19 +946,19 @@
         <v>0.9794306755065918</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.070195198059082</v>
+        <v>-7.070194721221924</v>
       </c>
       <c r="D20" t="n">
-        <v>6.916427135467529</v>
+        <v>6.916428089141846</v>
       </c>
       <c r="E20" t="n">
         <v>7.71525764465332</v>
       </c>
       <c r="F20" t="n">
-        <v>33.2146110534668</v>
+        <v>33.21461486816406</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9901661276817322</v>
+        <v>-0.9901658296585083</v>
       </c>
       <c r="H20" t="n">
         <v>1.466728448867798</v>
@@ -969,13 +969,13 @@
         <v>0.5925468802452087</v>
       </c>
       <c r="B21" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.093592643737793</v>
+        <v>-7.093594074249268</v>
       </c>
       <c r="D21" t="n">
-        <v>10.16660118103027</v>
+        <v>10.16660022735596</v>
       </c>
       <c r="E21" t="n">
         <v>3.634465217590332</v>
@@ -984,10 +984,10 @@
         <v>32.7855110168457</v>
       </c>
       <c r="G21" t="n">
-        <v>2.01120138168335</v>
+        <v>2.011201620101929</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8537764549255371</v>
+        <v>-0.8537766933441162</v>
       </c>
     </row>
     <row r="22">
@@ -995,25 +995,25 @@
         <v>0.5929203629493713</v>
       </c>
       <c r="B22" t="n">
-        <v>0.007268107961863279</v>
+        <v>0.0072680888697505</v>
       </c>
       <c r="C22" t="n">
-        <v>-6.299344062805176</v>
+        <v>-6.299343585968018</v>
       </c>
       <c r="D22" t="n">
-        <v>14.49208831787109</v>
+        <v>14.49208736419678</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.859313011169434</v>
+        <v>-1.859313368797302</v>
       </c>
       <c r="F22" t="n">
-        <v>32.17982482910156</v>
+        <v>32.17982864379883</v>
       </c>
       <c r="G22" t="n">
-        <v>4.955769062042236</v>
+        <v>4.955769538879395</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.485604763031006</v>
+        <v>-2.485605001449585</v>
       </c>
     </row>
     <row r="23">
@@ -1021,10 +1021,10 @@
         <v>0.6016235947608948</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01752708107233047</v>
+        <v>0.01752712018787861</v>
       </c>
       <c r="C23" t="n">
-        <v>-4.545924186706543</v>
+        <v>-4.545923709869385</v>
       </c>
       <c r="D23" t="n">
         <v>19.91064834594727</v>
@@ -1033,13 +1033,13 @@
         <v>-7.802365779876709</v>
       </c>
       <c r="F23" t="n">
-        <v>31.40562057495117</v>
+        <v>31.4056224822998</v>
       </c>
       <c r="G23" t="n">
-        <v>7.610508441925049</v>
+        <v>7.610507965087891</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.901726245880127</v>
+        <v>-2.90172553062439</v>
       </c>
     </row>
     <row r="24">
@@ -1047,10 +1047,10 @@
         <v>0.6208371520042419</v>
       </c>
       <c r="B24" t="n">
-        <v>0.03064052015542984</v>
+        <v>0.0306404996663332</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.955256700515747</v>
+        <v>-1.95525598526001</v>
       </c>
       <c r="D24" t="n">
         <v>25.99744606018066</v>
@@ -1065,7 +1065,7 @@
         <v>9.75511360168457</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.094965934753418</v>
+        <v>-2.094965696334839</v>
       </c>
     </row>
     <row r="25">
@@ -1073,16 +1073,16 @@
         <v>0.6492250561714172</v>
       </c>
       <c r="B25" t="n">
-        <v>0.04692760854959488</v>
+        <v>0.04692758992314339</v>
       </c>
       <c r="C25" t="n">
-        <v>1.239973783493042</v>
+        <v>1.239973545074463</v>
       </c>
       <c r="D25" t="n">
-        <v>32.0445671081543</v>
+        <v>32.04457092285156</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.51277160644531</v>
+        <v>-14.512770652771</v>
       </c>
       <c r="F25" t="n">
         <v>29.25117301940918</v>
@@ -1099,19 +1099,19 @@
         <v>0.6842376589775085</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06713233143091202</v>
+        <v>0.06713230907917023</v>
       </c>
       <c r="C26" t="n">
-        <v>4.734204292297363</v>
+        <v>4.734203815460205</v>
       </c>
       <c r="D26" t="n">
         <v>37.17813110351562</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.66947174072266</v>
+        <v>-13.66947078704834</v>
       </c>
       <c r="F26" t="n">
-        <v>27.81206703186035</v>
+        <v>27.81206893920898</v>
       </c>
       <c r="G26" t="n">
         <v>11.90242004394531</v>
@@ -1125,7 +1125,7 @@
         <v>0.7225265502929688</v>
       </c>
       <c r="B27" t="n">
-        <v>0.09150777012109756</v>
+        <v>0.09150777757167816</v>
       </c>
       <c r="C27" t="n">
         <v>8.234172821044922</v>
@@ -1137,13 +1137,13 @@
         <v>-10.5537166595459</v>
       </c>
       <c r="F27" t="n">
-        <v>26.13946914672852</v>
+        <v>26.13947105407715</v>
       </c>
       <c r="G27" t="n">
         <v>12.00064373016357</v>
       </c>
       <c r="H27" t="n">
-        <v>2.994667053222656</v>
+        <v>2.994666814804077</v>
       </c>
     </row>
     <row r="28">
@@ -1151,7 +1151,7 @@
         <v>0.7608784437179565</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1198380663990974</v>
+        <v>0.1198380142450333</v>
       </c>
       <c r="C28" t="n">
         <v>11.54106521606445</v>
@@ -1177,7 +1177,7 @@
         <v>0.7971145510673523</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1513696312904358</v>
+        <v>0.151369646191597</v>
       </c>
       <c r="C29" t="n">
         <v>14.54943466186523</v>
@@ -1186,7 +1186,7 @@
         <v>41.62061309814453</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.210516452789307</v>
+        <v>-2.210516691207886</v>
       </c>
       <c r="F29" t="n">
         <v>22.28615951538086</v>
@@ -1203,13 +1203,13 @@
         <v>0.8300795555114746</v>
       </c>
       <c r="B30" t="n">
-        <v>0.18510502576828</v>
+        <v>0.1851050406694412</v>
       </c>
       <c r="C30" t="n">
         <v>17.20433235168457</v>
       </c>
       <c r="D30" t="n">
-        <v>39.36634826660156</v>
+        <v>39.36635208129883</v>
       </c>
       <c r="E30" t="n">
         <v>1.327176213264465</v>
@@ -1229,7 +1229,7 @@
         <v>0.8591712713241577</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2201094925403595</v>
+        <v>0.2201094478368759</v>
       </c>
       <c r="C31" t="n">
         <v>19.48697662353516</v>
@@ -1247,7 +1247,7 @@
         <v>9.274946212768555</v>
       </c>
       <c r="H31" t="n">
-        <v>7.433788776397705</v>
+        <v>7.433788299560547</v>
       </c>
     </row>
     <row r="32">
@@ -1270,7 +1270,7 @@
         <v>16.00725746154785</v>
       </c>
       <c r="G32" t="n">
-        <v>8.332728385925293</v>
+        <v>8.332729339599609</v>
       </c>
       <c r="H32" t="n">
         <v>8.257535934448242</v>
@@ -1284,7 +1284,7 @@
         <v>0.2914565205574036</v>
       </c>
       <c r="C33" t="n">
-        <v>22.99179077148438</v>
+        <v>22.99178886413574</v>
       </c>
       <c r="D33" t="n">
         <v>25.12253761291504</v>
@@ -1296,10 +1296,10 @@
         <v>13.93195343017578</v>
       </c>
       <c r="G33" t="n">
-        <v>7.443483829498291</v>
+        <v>7.443483352661133</v>
       </c>
       <c r="H33" t="n">
-        <v>9.117576599121094</v>
+        <v>9.117575645446777</v>
       </c>
     </row>
     <row r="34">
@@ -1310,19 +1310,19 @@
         <v>0.3266077935695648</v>
       </c>
       <c r="C34" t="n">
-        <v>24.23853492736816</v>
+        <v>24.2385368347168</v>
       </c>
       <c r="D34" t="n">
         <v>19.04565238952637</v>
       </c>
       <c r="E34" t="n">
-        <v>5.743017673492432</v>
+        <v>5.74301815032959</v>
       </c>
       <c r="F34" t="n">
-        <v>11.93467235565186</v>
+        <v>11.93467330932617</v>
       </c>
       <c r="G34" t="n">
-        <v>6.658355236053467</v>
+        <v>6.658356666564941</v>
       </c>
       <c r="H34" t="n">
         <v>10.03778266906738</v>
@@ -1333,7 +1333,7 @@
         <v>0.9362504482269287</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3604375422000885</v>
+        <v>0.3604375720024109</v>
       </c>
       <c r="C35" t="n">
         <v>25.19003677368164</v>
@@ -1345,10 +1345,10 @@
         <v>5.093740940093994</v>
       </c>
       <c r="F35" t="n">
-        <v>10.06984424591064</v>
+        <v>10.06984519958496</v>
       </c>
       <c r="G35" t="n">
-        <v>6.036590099334717</v>
+        <v>6.036589622497559</v>
       </c>
       <c r="H35" t="n">
         <v>11.03246116638184</v>
@@ -1362,7 +1362,7 @@
         <v>0.3920238316059113</v>
       </c>
       <c r="C36" t="n">
-        <v>25.90891075134277</v>
+        <v>25.90891265869141</v>
       </c>
       <c r="D36" t="n">
         <v>6.407106876373291</v>
@@ -1374,7 +1374,7 @@
         <v>8.393510818481445</v>
       </c>
       <c r="G36" t="n">
-        <v>5.63928747177124</v>
+        <v>5.639286994934082</v>
       </c>
       <c r="H36" t="n">
         <v>12.10856056213379</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.9545540809631348</v>
+        <v>0.95455402135849</v>
       </c>
       <c r="B37" t="n">
         <v>0.4204173982143402</v>
@@ -1391,7 +1391,7 @@
         <v>26.47961616516113</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1908765882253647</v>
+        <v>0.1908764392137527</v>
       </c>
       <c r="E37" t="n">
         <v>3.902754306793213</v>
@@ -1400,7 +1400,7 @@
         <v>6.927595138549805</v>
       </c>
       <c r="G37" t="n">
-        <v>5.495574474334717</v>
+        <v>5.495574951171875</v>
       </c>
       <c r="H37" t="n">
         <v>13.25740051269531</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.9608076810836792</v>
+        <v>0.9608076214790344</v>
       </c>
       <c r="B38" t="n">
         <v>0.4452469348907471</v>
@@ -1417,7 +1417,7 @@
         <v>27.01716804504395</v>
       </c>
       <c r="D38" t="n">
-        <v>-5.453996181488037</v>
+        <v>-5.453994274139404</v>
       </c>
       <c r="E38" t="n">
         <v>3.77524209022522</v>
@@ -1426,7 +1426,7 @@
         <v>5.653020858764648</v>
       </c>
       <c r="G38" t="n">
-        <v>5.607202053070068</v>
+        <v>5.60720157623291</v>
       </c>
       <c r="H38" t="n">
         <v>14.44929218292236</v>
@@ -1443,7 +1443,7 @@
         <v>27.63172721862793</v>
       </c>
       <c r="D39" t="n">
-        <v>-9.88369083404541</v>
+        <v>-9.883689880371094</v>
       </c>
       <c r="E39" t="n">
         <v>3.769729852676392</v>
@@ -1452,7 +1452,7 @@
         <v>4.520417213439941</v>
       </c>
       <c r="G39" t="n">
-        <v>5.964938640594482</v>
+        <v>5.964939117431641</v>
       </c>
       <c r="H39" t="n">
         <v>15.62326335906982</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.9734322428703308</v>
+        <v>0.973432183265686</v>
       </c>
       <c r="B40" t="n">
         <v>0.486019492149353</v>
@@ -1469,16 +1469,16 @@
         <v>28.34905624389648</v>
       </c>
       <c r="D40" t="n">
-        <v>-12.5137357711792</v>
+        <v>-12.51373863220215</v>
       </c>
       <c r="E40" t="n">
-        <v>3.639242887496948</v>
+        <v>3.639243125915527</v>
       </c>
       <c r="F40" t="n">
-        <v>3.458949089050293</v>
+        <v>3.458948135375977</v>
       </c>
       <c r="G40" t="n">
-        <v>6.569222927093506</v>
+        <v>6.569222450256348</v>
       </c>
       <c r="H40" t="n">
         <v>16.68514633178711</v>
@@ -1495,7 +1495,7 @@
         <v>29.06997489929199</v>
       </c>
       <c r="D41" t="n">
-        <v>-13.12063121795654</v>
+        <v>-13.12063217163086</v>
       </c>
       <c r="E41" t="n">
         <v>3.326799869537354</v>
@@ -1504,15 +1504,15 @@
         <v>2.391517639160156</v>
       </c>
       <c r="G41" t="n">
-        <v>7.427855968475342</v>
+        <v>7.4278564453125</v>
       </c>
       <c r="H41" t="n">
-        <v>17.55253410339355</v>
+        <v>17.55253219604492</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.9891922473907471</v>
+        <v>0.9891921877861023</v>
       </c>
       <c r="B42" t="n">
         <v>0.5220785737037659</v>
@@ -1521,10 +1521,10 @@
         <v>29.58150672912598</v>
       </c>
       <c r="D42" t="n">
-        <v>-11.96098804473877</v>
+        <v>-11.96098899841309</v>
       </c>
       <c r="E42" t="n">
-        <v>2.848669052124023</v>
+        <v>2.848669290542603</v>
       </c>
       <c r="F42" t="n">
         <v>1.275003433227539</v>
@@ -1547,19 +1547,19 @@
         <v>29.70211601257324</v>
       </c>
       <c r="D43" t="n">
-        <v>-9.792624473571777</v>
+        <v>-9.792625427246094</v>
       </c>
       <c r="E43" t="n">
         <v>2.015948534011841</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1299047321081161</v>
+        <v>0.1299048066139221</v>
       </c>
       <c r="G43" t="n">
         <v>10.13568115234375</v>
       </c>
       <c r="H43" t="n">
-        <v>18.32455635070801</v>
+        <v>18.32455444335938</v>
       </c>
     </row>
     <row r="44">
@@ -1573,13 +1573,13 @@
         <v>29.37685966491699</v>
       </c>
       <c r="D44" t="n">
-        <v>-7.267556667327881</v>
+        <v>-7.267554759979248</v>
       </c>
       <c r="E44" t="n">
         <v>0.4735918343067169</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.9172849655151367</v>
+        <v>-0.9172829985618591</v>
       </c>
       <c r="G44" t="n">
         <v>12.25109195709229</v>
@@ -1596,16 +1596,16 @@
         <v>0.5781227350234985</v>
       </c>
       <c r="C45" t="n">
-        <v>28.68072509765625</v>
+        <v>28.68072700500488</v>
       </c>
       <c r="D45" t="n">
-        <v>-4.764201641082764</v>
+        <v>-4.764203548431396</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.753300666809082</v>
+        <v>-1.753300547599792</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.645218849182129</v>
+        <v>-1.645216941833496</v>
       </c>
       <c r="G45" t="n">
         <v>15.12150096893311</v>
@@ -1628,10 +1628,10 @@
         <v>-2.595841884613037</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5760158896446228</v>
+        <v>0.576015830039978</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3660573959350586</v>
+        <v>-0.3660592436790466</v>
       </c>
       <c r="G46" t="n">
         <v>19.6419792175293</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B47" t="n">
         <v>0.6052631139755249</v>
@@ -1651,13 +1651,13 @@
         <v>29.13036918640137</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6823934316635132</v>
+        <v>-0.6823936104774475</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.754701137542725</v>
+        <v>-1.754701256752014</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1451044231653214</v>
+        <v>-0.1451043486595154</v>
       </c>
       <c r="G47" t="n">
         <v>23.73296546936035</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01604280434548855</v>
+        <v>0.01604279689490795</v>
       </c>
       <c r="B48" t="n">
         <v>0.607780933380127</v>
@@ -1677,13 +1677,13 @@
         <v>27.92717742919922</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9289079904556274</v>
+        <v>0.9289059042930603</v>
       </c>
       <c r="E48" t="n">
-        <v>-3.43358325958252</v>
+        <v>-3.433582782745361</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9709062576293945</v>
+        <v>0.9709063172340393</v>
       </c>
       <c r="G48" t="n">
         <v>28.96307373046875</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.03489366918802261</v>
+        <v>0.03489365801215172</v>
       </c>
       <c r="B49" t="n">
         <v>0.6204983592033386</v>
@@ -1703,7 +1703,7 @@
         <v>26.66284942626953</v>
       </c>
       <c r="D49" t="n">
-        <v>2.388295650482178</v>
+        <v>2.388296604156494</v>
       </c>
       <c r="E49" t="n">
         <v>-3.697185039520264</v>
@@ -1712,41 +1712,41 @@
         <v>2.996949195861816</v>
       </c>
       <c r="G49" t="n">
-        <v>35.18606185913086</v>
+        <v>35.18606567382812</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.792515754699707</v>
+        <v>-3.792515993118286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.05470237880945206</v>
+        <v>0.05470236763358116</v>
       </c>
       <c r="B50" t="n">
         <v>0.6435858607292175</v>
       </c>
       <c r="C50" t="n">
-        <v>25.37053680419922</v>
+        <v>25.37053871154785</v>
       </c>
       <c r="D50" t="n">
-        <v>3.774511814117432</v>
+        <v>3.774512767791748</v>
       </c>
       <c r="E50" t="n">
         <v>-2.612247705459595</v>
       </c>
       <c r="F50" t="n">
-        <v>5.746723175048828</v>
+        <v>5.746724128723145</v>
       </c>
       <c r="G50" t="n">
         <v>41.77863693237305</v>
       </c>
       <c r="H50" t="n">
-        <v>-8.214187622070312</v>
+        <v>-8.214188575744629</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.07494954019784927</v>
+        <v>0.07494953274726868</v>
       </c>
       <c r="B51" t="n">
         <v>0.6749206185340881</v>
@@ -1758,7 +1758,7 @@
         <v>4.945450305938721</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.8296518921852112</v>
+        <v>-0.829651951789856</v>
       </c>
       <c r="F51" t="n">
         <v>8.90379524230957</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.09658081084489822</v>
+        <v>0.09658080339431763</v>
       </c>
       <c r="B52" t="n">
         <v>0.7108967304229736</v>
@@ -1784,13 +1784,13 @@
         <v>5.629170894622803</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9590094685554504</v>
+        <v>0.9590094089508057</v>
       </c>
       <c r="F52" t="n">
         <v>12.17672157287598</v>
       </c>
       <c r="G52" t="n">
-        <v>52.34543991088867</v>
+        <v>52.34543609619141</v>
       </c>
       <c r="H52" t="n">
         <v>-8.828831672668457</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.1211669817566872</v>
+        <v>0.1211669743061066</v>
       </c>
       <c r="B53" t="n">
         <v>0.7481929659843445</v>
@@ -1807,7 +1807,7 @@
         <v>20.62509536743164</v>
       </c>
       <c r="D53" t="n">
-        <v>5.734955310821533</v>
+        <v>5.73495626449585</v>
       </c>
       <c r="E53" t="n">
         <v>2.428501844406128</v>
@@ -1819,7 +1819,7 @@
         <v>54.76484298706055</v>
       </c>
       <c r="H53" t="n">
-        <v>-6.026090621948242</v>
+        <v>-6.0260910987854</v>
       </c>
     </row>
     <row r="54">
@@ -1845,12 +1845,12 @@
         <v>55.08745956420898</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.492030143737793</v>
+        <v>-2.492030382156372</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.1806264221668243</v>
+        <v>0.1806264519691467</v>
       </c>
       <c r="B55" t="n">
         <v>0.8176935315132141</v>
@@ -1871,12 +1871,12 @@
         <v>53.61552810668945</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9945365190505981</v>
+        <v>0.9945365786552429</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.2141285240650177</v>
+        <v>0.2141284942626953</v>
       </c>
       <c r="B56" t="n">
         <v>0.8483681678771973</v>
@@ -1897,7 +1897,7 @@
         <v>50.66776275634766</v>
       </c>
       <c r="H56" t="n">
-        <v>3.945390224456787</v>
+        <v>3.945389986038208</v>
       </c>
     </row>
     <row r="57">
@@ -1911,7 +1911,7 @@
         <v>12.11798667907715</v>
       </c>
       <c r="D57" t="n">
-        <v>2.836286067962646</v>
+        <v>2.83628511428833</v>
       </c>
       <c r="E57" t="n">
         <v>6.182946681976318</v>
@@ -1923,7 +1923,7 @@
         <v>46.47842025756836</v>
       </c>
       <c r="H57" t="n">
-        <v>6.130643367767334</v>
+        <v>6.130642890930176</v>
       </c>
     </row>
     <row r="58">
@@ -1937,19 +1937,19 @@
         <v>10.01347827911377</v>
       </c>
       <c r="D58" t="n">
-        <v>1.95212709903717</v>
+        <v>1.952127933502197</v>
       </c>
       <c r="E58" t="n">
-        <v>6.964167594909668</v>
+        <v>6.964168071746826</v>
       </c>
       <c r="F58" t="n">
-        <v>27.55125427246094</v>
+        <v>27.55125617980957</v>
       </c>
       <c r="G58" t="n">
         <v>41.25951385498047</v>
       </c>
       <c r="H58" t="n">
-        <v>7.542943000793457</v>
+        <v>7.542942523956299</v>
       </c>
     </row>
     <row r="59">
@@ -1960,16 +1960,16 @@
         <v>0.9233917593955994</v>
       </c>
       <c r="C59" t="n">
-        <v>7.990589618682861</v>
+        <v>7.990589141845703</v>
       </c>
       <c r="D59" t="n">
-        <v>1.112545609474182</v>
+        <v>1.112545490264893</v>
       </c>
       <c r="E59" t="n">
         <v>7.732068538665771</v>
       </c>
       <c r="F59" t="n">
-        <v>29.14215278625488</v>
+        <v>29.14215469360352</v>
       </c>
       <c r="G59" t="n">
         <v>35.14380264282227</v>
@@ -1983,13 +1983,13 @@
         <v>0.3472479581832886</v>
       </c>
       <c r="B60" t="n">
-        <v>0.9415206909179688</v>
+        <v>0.941520631313324</v>
       </c>
       <c r="C60" t="n">
-        <v>6.04466438293457</v>
+        <v>6.044664859771729</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3263117074966431</v>
+        <v>0.3263134658336639</v>
       </c>
       <c r="E60" t="n">
         <v>8.491707801818848</v>
@@ -2012,45 +2012,45 @@
         <v>0.9549421072006226</v>
       </c>
       <c r="C61" t="n">
-        <v>4.175992965698242</v>
+        <v>4.175992488861084</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3612912893295288</v>
+        <v>-0.3612914383411407</v>
       </c>
       <c r="E61" t="n">
-        <v>9.256364822387695</v>
+        <v>9.256365776062012</v>
       </c>
       <c r="F61" t="n">
-        <v>31.07729721069336</v>
+        <v>31.07729911804199</v>
       </c>
       <c r="G61" t="n">
         <v>21.00459289550781</v>
       </c>
       <c r="H61" t="n">
-        <v>7.246137619018555</v>
+        <v>7.246137142181396</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.4070127308368683</v>
+        <v>0.4070127010345459</v>
       </c>
       <c r="B62" t="n">
         <v>0.9635723829269409</v>
       </c>
       <c r="C62" t="n">
-        <v>2.40432333946228</v>
+        <v>2.404323101043701</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8600324392318726</v>
+        <v>-0.8600307106971741</v>
       </c>
       <c r="E62" t="n">
-        <v>10.03280830383301</v>
+        <v>10.03280925750732</v>
       </c>
       <c r="F62" t="n">
         <v>31.46946907043457</v>
       </c>
       <c r="G62" t="n">
-        <v>13.69804763793945</v>
+        <v>13.69804668426514</v>
       </c>
       <c r="H62" t="n">
         <v>6.251384258270264</v>
@@ -2064,22 +2064,22 @@
         <v>0.9680413603782654</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7545859813690186</v>
+        <v>0.7545866370201111</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.079459547996521</v>
+        <v>-1.079461574554443</v>
       </c>
       <c r="E63" t="n">
         <v>10.7972936630249</v>
       </c>
       <c r="F63" t="n">
-        <v>31.60136795043945</v>
+        <v>31.60136985778809</v>
       </c>
       <c r="G63" t="n">
-        <v>6.854531764984131</v>
+        <v>6.854532241821289</v>
       </c>
       <c r="H63" t="n">
-        <v>5.450605869293213</v>
+        <v>5.450605392456055</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
         <v>0.9695444107055664</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.7457306385040283</v>
+        <v>-0.7457318902015686</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9319089651107788</v>
+        <v>-0.9319091439247131</v>
       </c>
       <c r="E64" t="n">
         <v>11.49567031860352</v>
@@ -2102,10 +2102,10 @@
         <v>31.60845565795898</v>
       </c>
       <c r="G64" t="n">
-        <v>1.060098171234131</v>
+        <v>1.060096621513367</v>
       </c>
       <c r="H64" t="n">
-        <v>5.136620044708252</v>
+        <v>5.136619567871094</v>
       </c>
     </row>
     <row r="65">
@@ -2116,22 +2116,22 @@
         <v>0.9696251749992371</v>
       </c>
       <c r="C65" t="n">
-        <v>-2.090733766555786</v>
+        <v>-2.090734958648682</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.3694432973861694</v>
+        <v>-0.3694434463977814</v>
       </c>
       <c r="E65" t="n">
-        <v>12.05819797515869</v>
+        <v>12.05819702148438</v>
       </c>
       <c r="F65" t="n">
-        <v>31.61435508728027</v>
+        <v>31.61435699462891</v>
       </c>
       <c r="G65" t="n">
-        <v>-3.233219623565674</v>
+        <v>-3.233217477798462</v>
       </c>
       <c r="H65" t="n">
-        <v>5.258790016174316</v>
+        <v>5.258789539337158</v>
       </c>
     </row>
     <row r="66">
@@ -2142,19 +2142,19 @@
         <v>0.9696923494338989</v>
       </c>
       <c r="C66" t="n">
-        <v>-3.311526536941528</v>
+        <v>-3.311525821685791</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5874487161636353</v>
+        <v>0.5874485373497009</v>
       </c>
       <c r="E66" t="n">
-        <v>12.41564464569092</v>
+        <v>12.41564559936523</v>
       </c>
       <c r="F66" t="n">
-        <v>31.67366981506348</v>
+        <v>31.67367172241211</v>
       </c>
       <c r="G66" t="n">
-        <v>-5.701130390167236</v>
+        <v>-5.701131820678711</v>
       </c>
       <c r="H66" t="n">
         <v>5.564603805541992</v>
@@ -2168,19 +2168,19 @@
         <v>0.9703683257102966</v>
       </c>
       <c r="C67" t="n">
-        <v>-4.465447425842285</v>
+        <v>-4.46544885635376</v>
       </c>
       <c r="D67" t="n">
-        <v>1.867310166358948</v>
+        <v>1.867310047149658</v>
       </c>
       <c r="E67" t="n">
         <v>12.48532295227051</v>
       </c>
       <c r="F67" t="n">
-        <v>31.77260398864746</v>
+        <v>31.77260589599609</v>
       </c>
       <c r="G67" t="n">
-        <v>-6.210098743438721</v>
+        <v>-6.210098266601562</v>
       </c>
       <c r="H67" t="n">
         <v>5.666619777679443</v>
@@ -2194,10 +2194,10 @@
         <v>0.9714956879615784</v>
       </c>
       <c r="C68" t="n">
-        <v>-5.599362373352051</v>
+        <v>-5.599361896514893</v>
       </c>
       <c r="D68" t="n">
-        <v>3.371726512908936</v>
+        <v>3.371727466583252</v>
       </c>
       <c r="E68" t="n">
         <v>12.17688655853271</v>
@@ -2206,7 +2206,7 @@
         <v>31.84543418884277</v>
       </c>
       <c r="G68" t="n">
-        <v>-4.995518207550049</v>
+        <v>-4.995517730712891</v>
       </c>
       <c r="H68" t="n">
         <v>5.067599773406982</v>
@@ -2220,7 +2220,7 @@
         <v>0.9723256230354309</v>
       </c>
       <c r="C69" t="n">
-        <v>-6.687911033630371</v>
+        <v>-6.687912464141846</v>
       </c>
       <c r="D69" t="n">
         <v>5.096287250518799</v>
@@ -2229,10 +2229,10 @@
         <v>11.30015659332275</v>
       </c>
       <c r="F69" t="n">
-        <v>31.82487297058105</v>
+        <v>31.82487487792969</v>
       </c>
       <c r="G69" t="n">
-        <v>-2.512287616729736</v>
+        <v>-2.51228928565979</v>
       </c>
       <c r="H69" t="n">
         <v>3.378950834274292</v>
@@ -2246,7 +2246,7 @@
         <v>0.9723256230354309</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.606743812561035</v>
+        <v>-7.606743335723877</v>
       </c>
       <c r="D70" t="n">
         <v>7.166304111480713</v>
@@ -2255,13 +2255,13 @@
         <v>9.52202033996582</v>
       </c>
       <c r="F70" t="n">
-        <v>31.66789436340332</v>
+        <v>31.66789627075195</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7786327004432678</v>
+        <v>0.7786329984664917</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8097211122512817</v>
+        <v>0.8097212314605713</v>
       </c>
     </row>
     <row r="71">
@@ -2284,7 +2284,7 @@
         <v>34.27399444580078</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4575152993202209</v>
+        <v>0.4575155973434448</v>
       </c>
       <c r="H71" t="n">
         <v>1.409748196601868</v>
@@ -2295,22 +2295,22 @@
         <v>0.5999999046325684</v>
       </c>
       <c r="B72" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C72" t="n">
-        <v>-8.007960319519043</v>
+        <v>-8.007962226867676</v>
       </c>
       <c r="D72" t="n">
         <v>13.46810722351074</v>
       </c>
       <c r="E72" t="n">
-        <v>1.531050801277161</v>
+        <v>1.531050682067871</v>
       </c>
       <c r="F72" t="n">
         <v>33.96356964111328</v>
       </c>
       <c r="G72" t="n">
-        <v>3.732045650482178</v>
+        <v>3.732045888900757</v>
       </c>
       <c r="H72" t="n">
         <v>-1.345711708068848</v>
@@ -2321,10 +2321,10 @@
         <v>0.6013975143432617</v>
       </c>
       <c r="B73" t="n">
-        <v>0.005424059461802244</v>
+        <v>0.005424040369689465</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.028367042541504</v>
+        <v>-7.028366565704346</v>
       </c>
       <c r="D73" t="n">
         <v>18.24349975585938</v>
@@ -2336,10 +2336,10 @@
         <v>33.5078125</v>
       </c>
       <c r="G73" t="n">
-        <v>7.016332149505615</v>
+        <v>7.01633358001709</v>
       </c>
       <c r="H73" t="n">
-        <v>-3.118787288665771</v>
+        <v>-3.118787527084351</v>
       </c>
     </row>
     <row r="74">
@@ -2347,10 +2347,10 @@
         <v>0.61162930727005</v>
       </c>
       <c r="B74" t="n">
-        <v>0.01338747795671225</v>
+        <v>0.01338745933026075</v>
       </c>
       <c r="C74" t="n">
-        <v>-5.141280174255371</v>
+        <v>-5.141279697418213</v>
       </c>
       <c r="D74" t="n">
         <v>24.08427619934082</v>
@@ -2365,7 +2365,7 @@
         <v>10.08639812469482</v>
       </c>
       <c r="H74" t="n">
-        <v>-3.212769031524658</v>
+        <v>-3.212769269943237</v>
       </c>
     </row>
     <row r="75">
@@ -2373,25 +2373,25 @@
         <v>0.6313397884368896</v>
       </c>
       <c r="B75" t="n">
-        <v>0.02402154356241226</v>
+        <v>0.0240215826779604</v>
       </c>
       <c r="C75" t="n">
-        <v>-2.456477403640747</v>
+        <v>-2.45647668838501</v>
       </c>
       <c r="D75" t="n">
         <v>30.4969539642334</v>
       </c>
       <c r="E75" t="n">
-        <v>-15.45810031890869</v>
+        <v>-15.45810222625732</v>
       </c>
       <c r="F75" t="n">
-        <v>32.08594512939453</v>
+        <v>32.0859489440918</v>
       </c>
       <c r="G75" t="n">
         <v>12.66594886779785</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.800118207931519</v>
+        <v>-1.800117969512939</v>
       </c>
     </row>
     <row r="76">
@@ -2399,10 +2399,10 @@
         <v>0.6593824028968811</v>
       </c>
       <c r="B76" t="n">
-        <v>0.03823158890008926</v>
+        <v>0.03823157027363777</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7708213329315186</v>
+        <v>0.7708210349082947</v>
       </c>
       <c r="D76" t="n">
         <v>36.64367294311523</v>
@@ -2425,10 +2425,10 @@
         <v>0.6930912733078003</v>
       </c>
       <c r="B77" t="n">
-        <v>0.05715463310480118</v>
+        <v>0.05715467408299446</v>
       </c>
       <c r="C77" t="n">
-        <v>4.227009773254395</v>
+        <v>4.227010250091553</v>
       </c>
       <c r="D77" t="n">
         <v>41.55078887939453</v>
@@ -2451,10 +2451,10 @@
         <v>0.7291909456253052</v>
       </c>
       <c r="B78" t="n">
-        <v>0.08121929317712784</v>
+        <v>0.08121927082538605</v>
       </c>
       <c r="C78" t="n">
-        <v>7.626902103424072</v>
+        <v>7.626901626586914</v>
       </c>
       <c r="D78" t="n">
         <v>44.61349105834961</v>
@@ -2477,7 +2477,7 @@
         <v>0.7647025585174561</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1102267280220985</v>
+        <v>0.1102267056703568</v>
       </c>
       <c r="C79" t="n">
         <v>10.79610252380371</v>
@@ -2492,10 +2492,10 @@
         <v>26.05494689941406</v>
       </c>
       <c r="G79" t="n">
-        <v>15.49099159240723</v>
+        <v>15.49099063873291</v>
       </c>
       <c r="H79" t="n">
-        <v>5.696434020996094</v>
+        <v>5.696433544158936</v>
       </c>
     </row>
     <row r="80">
@@ -2503,7 +2503,7 @@
         <v>0.7978046536445618</v>
       </c>
       <c r="B80" t="n">
-        <v>0.143610805273056</v>
+        <v>0.1436107903718948</v>
       </c>
       <c r="C80" t="n">
         <v>13.64182281494141</v>
@@ -2512,16 +2512,16 @@
         <v>44.71590042114258</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.666900873184204</v>
+        <v>-1.666900992393494</v>
       </c>
       <c r="F80" t="n">
         <v>23.95768737792969</v>
       </c>
       <c r="G80" t="n">
-        <v>14.75194549560547</v>
+        <v>14.75194454193115</v>
       </c>
       <c r="H80" t="n">
-        <v>6.825351238250732</v>
+        <v>6.825350761413574</v>
       </c>
     </row>
     <row r="81">
@@ -2529,7 +2529,7 @@
         <v>0.8275279998779297</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1802560985088348</v>
+        <v>0.1802560538053513</v>
       </c>
       <c r="C81" t="n">
         <v>16.12667274475098</v>
@@ -2547,7 +2547,7 @@
         <v>13.68058681488037</v>
       </c>
       <c r="H81" t="n">
-        <v>7.697139263153076</v>
+        <v>7.69713830947876</v>
       </c>
     </row>
     <row r="82">
@@ -2555,7 +2555,7 @@
         <v>0.8534821271896362</v>
       </c>
       <c r="B82" t="n">
-        <v>0.2192039489746094</v>
+        <v>0.2192039340734482</v>
       </c>
       <c r="C82" t="n">
         <v>18.22812461853027</v>
@@ -2564,13 +2564,13 @@
         <v>38.35565567016602</v>
       </c>
       <c r="E82" t="n">
-        <v>4.212202548980713</v>
+        <v>4.212202072143555</v>
       </c>
       <c r="F82" t="n">
         <v>19.42578506469727</v>
       </c>
       <c r="G82" t="n">
-        <v>12.39847564697266</v>
+        <v>12.39847469329834</v>
       </c>
       <c r="H82" t="n">
         <v>8.400934219360352</v>
@@ -2596,7 +2596,7 @@
         <v>17.1215763092041</v>
       </c>
       <c r="G83" t="n">
-        <v>11.04671382904053</v>
+        <v>11.04671287536621</v>
       </c>
       <c r="H83" t="n">
         <v>9.043695449829102</v>
@@ -2625,7 +2625,7 @@
         <v>9.737434387207031</v>
       </c>
       <c r="H84" t="n">
-        <v>9.694579124450684</v>
+        <v>9.694578170776367</v>
       </c>
     </row>
     <row r="85">
@@ -2665,7 +2665,7 @@
         <v>23.17848205566406</v>
       </c>
       <c r="D86" t="n">
-        <v>14.20132541656494</v>
+        <v>14.20132446289062</v>
       </c>
       <c r="E86" t="n">
         <v>5.743066787719727</v>
@@ -2674,7 +2674,7 @@
         <v>10.96358776092529</v>
       </c>
       <c r="G86" t="n">
-        <v>7.613511562347412</v>
+        <v>7.613511085510254</v>
       </c>
       <c r="H86" t="n">
         <v>11.1883544921875</v>
@@ -2691,19 +2691,19 @@
         <v>23.70354652404785</v>
       </c>
       <c r="D87" t="n">
-        <v>7.590354442596436</v>
+        <v>7.590355396270752</v>
       </c>
       <c r="E87" t="n">
         <v>4.921989917755127</v>
       </c>
       <c r="F87" t="n">
-        <v>9.372425079345703</v>
+        <v>9.37242603302002</v>
       </c>
       <c r="G87" t="n">
-        <v>6.997741222381592</v>
+        <v>6.997740745544434</v>
       </c>
       <c r="H87" t="n">
-        <v>12.13063907623291</v>
+        <v>12.13063812255859</v>
       </c>
     </row>
     <row r="88">
@@ -2714,27 +2714,27 @@
         <v>0.4351032972335815</v>
       </c>
       <c r="C88" t="n">
-        <v>24.09939193725586</v>
+        <v>24.09939384460449</v>
       </c>
       <c r="D88" t="n">
-        <v>1.376961350440979</v>
+        <v>1.376961231231689</v>
       </c>
       <c r="E88" t="n">
         <v>4.189527988433838</v>
       </c>
       <c r="F88" t="n">
-        <v>8.044873237609863</v>
+        <v>8.04487419128418</v>
       </c>
       <c r="G88" t="n">
-        <v>6.761260509490967</v>
+        <v>6.761260032653809</v>
       </c>
       <c r="H88" t="n">
-        <v>13.22689056396484</v>
+        <v>13.22688961029053</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.9367566108703613</v>
+        <v>0.9367565512657166</v>
       </c>
       <c r="B89" t="n">
         <v>0.4582995176315308</v>
@@ -2743,24 +2743,24 @@
         <v>24.48716354370117</v>
       </c>
       <c r="D89" t="n">
-        <v>-4.144858837127686</v>
+        <v>-4.144860744476318</v>
       </c>
       <c r="E89" t="n">
-        <v>3.816786050796509</v>
+        <v>3.816786289215088</v>
       </c>
       <c r="F89" t="n">
         <v>6.950642585754395</v>
       </c>
       <c r="G89" t="n">
-        <v>6.922660350799561</v>
+        <v>6.922660827636719</v>
       </c>
       <c r="H89" t="n">
-        <v>14.44065284729004</v>
+        <v>14.44065189361572</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.9408068656921387</v>
+        <v>0.9408068060874939</v>
       </c>
       <c r="B90" t="n">
         <v>0.4774189293384552</v>
@@ -2769,16 +2769,16 @@
         <v>24.97182655334473</v>
       </c>
       <c r="D90" t="n">
-        <v>-8.54133129119873</v>
+        <v>-8.541332244873047</v>
       </c>
       <c r="E90" t="n">
-        <v>3.695663690567017</v>
+        <v>3.695663452148438</v>
       </c>
       <c r="F90" t="n">
         <v>6.029208183288574</v>
       </c>
       <c r="G90" t="n">
-        <v>7.47267484664917</v>
+        <v>7.472675323486328</v>
       </c>
       <c r="H90" t="n">
         <v>15.6882209777832</v>
@@ -2792,16 +2792,16 @@
         <v>0.4935190975666046</v>
       </c>
       <c r="C91" t="n">
-        <v>25.58839797973633</v>
+        <v>25.58839988708496</v>
       </c>
       <c r="D91" t="n">
-        <v>-11.32310581207275</v>
+        <v>-11.32310676574707</v>
       </c>
       <c r="E91" t="n">
-        <v>3.506877183914185</v>
+        <v>3.506877422332764</v>
       </c>
       <c r="F91" t="n">
-        <v>5.18459415435791</v>
+        <v>5.184595108032227</v>
       </c>
       <c r="G91" t="n">
         <v>8.341655731201172</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.9523091912269592</v>
+        <v>0.9523091316223145</v>
       </c>
       <c r="B92" t="n">
         <v>0.5082769393920898</v>
@@ -2821,42 +2821,42 @@
         <v>26.26418876647949</v>
       </c>
       <c r="D92" t="n">
-        <v>-12.14970874786377</v>
+        <v>-12.14970970153809</v>
       </c>
       <c r="E92" t="n">
         <v>3.128812789916992</v>
       </c>
       <c r="F92" t="n">
-        <v>4.322245597839355</v>
+        <v>4.322244644165039</v>
       </c>
       <c r="G92" t="n">
-        <v>9.470156669616699</v>
+        <v>9.470157623291016</v>
       </c>
       <c r="H92" t="n">
-        <v>17.86553764343262</v>
+        <v>17.86553955078125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.9593678116798401</v>
+        <v>0.9593677520751953</v>
       </c>
       <c r="B93" t="n">
         <v>0.5233447551727295</v>
       </c>
       <c r="C93" t="n">
-        <v>26.84214210510254</v>
+        <v>26.84214401245117</v>
       </c>
       <c r="D93" t="n">
-        <v>-11.31028461456299</v>
+        <v>-11.31028747558594</v>
       </c>
       <c r="E93" t="n">
         <v>2.702703237533569</v>
       </c>
       <c r="F93" t="n">
-        <v>3.356194496154785</v>
+        <v>3.356195449829102</v>
       </c>
       <c r="G93" t="n">
-        <v>10.81924152374268</v>
+        <v>10.81924057006836</v>
       </c>
       <c r="H93" t="n">
         <v>18.59156227111816</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.9654044508934021</v>
+        <v>0.9654043912887573</v>
       </c>
       <c r="B94" t="n">
         <v>0.5402244329452515</v>
@@ -2873,13 +2873,13 @@
         <v>27.18791198730469</v>
       </c>
       <c r="D94" t="n">
-        <v>-9.345295906066895</v>
+        <v>-9.345296859741211</v>
       </c>
       <c r="E94" t="n">
         <v>2.156238794326782</v>
       </c>
       <c r="F94" t="n">
-        <v>2.262472152709961</v>
+        <v>2.262473106384277</v>
       </c>
       <c r="G94" t="n">
         <v>12.38584804534912</v>
@@ -2899,7 +2899,7 @@
         <v>27.25304985046387</v>
       </c>
       <c r="D95" t="n">
-        <v>-6.806540966033936</v>
+        <v>-6.806542873382568</v>
       </c>
       <c r="E95" t="n">
         <v>0.9915872812271118</v>
@@ -2928,10 +2928,10 @@
         <v>-4.052876949310303</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.081645488739014</v>
+        <v>-1.081645369529724</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1440915912389755</v>
+        <v>0.1440916657447815</v>
       </c>
       <c r="G96" t="n">
         <v>16.55619621276855</v>
@@ -2948,27 +2948,27 @@
         <v>0.59634929895401</v>
       </c>
       <c r="C97" t="n">
-        <v>32.7109489440918</v>
+        <v>32.71094512939453</v>
       </c>
       <c r="D97" t="n">
-        <v>5.448959827423096</v>
+        <v>5.448960781097412</v>
       </c>
       <c r="E97" t="n">
-        <v>-6.057275772094727</v>
+        <v>-6.057275295257568</v>
       </c>
       <c r="F97" t="n">
-        <v>-14.11501598358154</v>
+        <v>-14.11501789093018</v>
       </c>
       <c r="G97" t="n">
-        <v>12.89249801635742</v>
+        <v>12.89249706268311</v>
       </c>
       <c r="H97" t="n">
-        <v>5.304746627807617</v>
+        <v>5.304746150970459</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B98" t="n">
         <v>0.6025266051292419</v>
@@ -2977,7 +2977,7 @@
         <v>33.47395706176758</v>
       </c>
       <c r="D98" t="n">
-        <v>9.642599105834961</v>
+        <v>9.642598152160645</v>
       </c>
       <c r="E98" t="n">
         <v>-9.472084045410156</v>
@@ -2989,12 +2989,12 @@
         <v>17.87347030639648</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.463013172149658</v>
+        <v>-1.463012933731079</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B99" t="n">
         <v>0.6164657473564148</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B100" t="n">
         <v>0.6369240880012512</v>
@@ -3032,13 +3032,13 @@
         <v>18.1113224029541</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.310549259185791</v>
+        <v>-7.310548305511475</v>
       </c>
       <c r="F100" t="n">
         <v>-6.529208183288574</v>
       </c>
       <c r="G100" t="n">
-        <v>29.64704322814941</v>
+        <v>29.64704132080078</v>
       </c>
       <c r="H100" t="n">
         <v>-14.00612926483154</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B101" t="n">
         <v>0.6631808280944824</v>
@@ -3064,7 +3064,7 @@
         <v>-2.674740791320801</v>
       </c>
       <c r="G101" t="n">
-        <v>36.3421745300293</v>
+        <v>36.34217834472656</v>
       </c>
       <c r="H101" t="n">
         <v>-14.67357158660889</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B102" t="n">
         <v>0.6940001845359802</v>
@@ -3084,7 +3084,7 @@
         <v>20.80165100097656</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.427673578262329</v>
+        <v>-1.427673697471619</v>
       </c>
       <c r="F102" t="n">
         <v>1.544735908508301</v>
@@ -3093,18 +3093,18 @@
         <v>43.04413986206055</v>
       </c>
       <c r="H102" t="n">
-        <v>-12.00063800811768</v>
+        <v>-12.00063896179199</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.008664227090775967</v>
+        <v>0.008664277382194996</v>
       </c>
       <c r="B103" t="n">
         <v>0.727738082408905</v>
       </c>
       <c r="C103" t="n">
-        <v>29.93349456787109</v>
+        <v>29.93349266052246</v>
       </c>
       <c r="D103" t="n">
         <v>19.66530990600586</v>
@@ -3124,13 +3124,13 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.03818187862634659</v>
+        <v>0.03818186745047569</v>
       </c>
       <c r="B104" t="n">
         <v>0.7625082731246948</v>
       </c>
       <c r="C104" t="n">
-        <v>27.33155822753906</v>
+        <v>27.33155632019043</v>
       </c>
       <c r="D104" t="n">
         <v>17.99419403076172</v>
@@ -3139,18 +3139,18 @@
         <v>1.68007755279541</v>
       </c>
       <c r="F104" t="n">
-        <v>10.14219856262207</v>
+        <v>10.14219951629639</v>
       </c>
       <c r="G104" t="n">
         <v>53.00614547729492</v>
       </c>
       <c r="H104" t="n">
-        <v>-4.409514904022217</v>
+        <v>-4.409515380859375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.07395092397928238</v>
+        <v>0.07395091652870178</v>
       </c>
       <c r="B105" t="n">
         <v>0.796481192111969</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.1133703961968422</v>
+        <v>0.1133703887462616</v>
       </c>
       <c r="B106" t="n">
         <v>0.8281999826431274</v>
@@ -3188,7 +3188,7 @@
         <v>14.00260829925537</v>
       </c>
       <c r="E106" t="n">
-        <v>3.857009410858154</v>
+        <v>3.857009649276733</v>
       </c>
       <c r="F106" t="n">
         <v>17.67443466186523</v>
@@ -3197,12 +3197,12 @@
         <v>55.03853988647461</v>
       </c>
       <c r="H106" t="n">
-        <v>0.8124592304229736</v>
+        <v>0.8124593496322632</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.1554375886917114</v>
+        <v>0.1554376184940338</v>
       </c>
       <c r="B107" t="n">
         <v>0.8567070364952087</v>
@@ -3211,7 +3211,7 @@
         <v>18.18756294250488</v>
       </c>
       <c r="D107" t="n">
-        <v>11.0638370513916</v>
+        <v>11.06383609771729</v>
       </c>
       <c r="E107" t="n">
         <v>4.040149211883545</v>
@@ -3220,7 +3220,7 @@
         <v>20.77007102966309</v>
       </c>
       <c r="G107" t="n">
-        <v>53.06145095825195</v>
+        <v>53.06144714355469</v>
       </c>
       <c r="H107" t="n">
         <v>2.335421085357666</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.1996540725231171</v>
+        <v>0.1996541023254395</v>
       </c>
       <c r="B108" t="n">
         <v>0.8814589977264404</v>
@@ -3237,10 +3237,10 @@
         <v>14.93478775024414</v>
       </c>
       <c r="D108" t="n">
-        <v>7.746928691864014</v>
+        <v>7.74692964553833</v>
       </c>
       <c r="E108" t="n">
-        <v>3.790030717849731</v>
+        <v>3.790030956268311</v>
       </c>
       <c r="F108" t="n">
         <v>23.35972023010254</v>
@@ -3263,19 +3263,19 @@
         <v>11.83092212677002</v>
       </c>
       <c r="D109" t="n">
-        <v>4.829380512237549</v>
+        <v>4.829379558563232</v>
       </c>
       <c r="E109" t="n">
         <v>3.679421901702881</v>
       </c>
       <c r="F109" t="n">
-        <v>25.42351150512695</v>
+        <v>25.42351341247559</v>
       </c>
       <c r="G109" t="n">
-        <v>44.37055969238281</v>
+        <v>44.37055587768555</v>
       </c>
       <c r="H109" t="n">
-        <v>3.82109522819519</v>
+        <v>3.821094989776611</v>
       </c>
     </row>
     <row r="110">
@@ -3295,7 +3295,7 @@
         <v>4.032492160797119</v>
       </c>
       <c r="F110" t="n">
-        <v>26.95767402648926</v>
+        <v>26.95767593383789</v>
       </c>
       <c r="G110" t="n">
         <v>38.24296569824219</v>
@@ -3312,10 +3312,10 @@
         <v>0.9309334754943848</v>
       </c>
       <c r="C111" t="n">
-        <v>6.481892585754395</v>
+        <v>6.481892108917236</v>
       </c>
       <c r="D111" t="n">
-        <v>1.641085267066956</v>
+        <v>1.641087055206299</v>
       </c>
       <c r="E111" t="n">
         <v>4.870926380157471</v>
@@ -3338,16 +3338,16 @@
         <v>0.9391915202140808</v>
       </c>
       <c r="C112" t="n">
-        <v>4.177309036254883</v>
+        <v>4.177308559417725</v>
       </c>
       <c r="D112" t="n">
-        <v>1.156832337379456</v>
+        <v>1.156832218170166</v>
       </c>
       <c r="E112" t="n">
         <v>6.054930686950684</v>
       </c>
       <c r="F112" t="n">
-        <v>28.5993537902832</v>
+        <v>28.59935569763184</v>
       </c>
       <c r="G112" t="n">
         <v>24.11040687561035</v>
@@ -3364,10 +3364,10 @@
         <v>0.9440599679946899</v>
       </c>
       <c r="C113" t="n">
-        <v>1.974237203598022</v>
+        <v>1.974236965179443</v>
       </c>
       <c r="D113" t="n">
-        <v>1.000515580177307</v>
+        <v>1.000515460968018</v>
       </c>
       <c r="E113" t="n">
         <v>7.37754487991333</v>
@@ -3379,7 +3379,7 @@
         <v>16.89493179321289</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.267461776733398</v>
+        <v>-1.267461538314819</v>
       </c>
     </row>
     <row r="114">
@@ -3390,22 +3390,22 @@
         <v>0.9465979337692261</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.2144033759832382</v>
+        <v>-0.2144036591053009</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9009290933609009</v>
+        <v>0.9009289145469666</v>
       </c>
       <c r="E114" t="n">
-        <v>8.644565582275391</v>
+        <v>8.644564628601074</v>
       </c>
       <c r="F114" t="n">
         <v>29.11742973327637</v>
       </c>
       <c r="G114" t="n">
-        <v>10.12013149261475</v>
+        <v>10.12013053894043</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.764822483062744</v>
+        <v>-2.764822721481323</v>
       </c>
     </row>
     <row r="115">
@@ -3413,25 +3413,25 @@
         <v>0.4526273906230927</v>
       </c>
       <c r="B115" t="n">
-        <v>0.9482024312019348</v>
+        <v>0.94820237159729</v>
       </c>
       <c r="C115" t="n">
-        <v>-2.402331590652466</v>
+        <v>-2.402330875396729</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7573534250259399</v>
+        <v>0.7573532462120056</v>
       </c>
       <c r="E115" t="n">
-        <v>9.740626335144043</v>
+        <v>9.740625381469727</v>
       </c>
       <c r="F115" t="n">
-        <v>29.3732967376709</v>
+        <v>29.37329864501953</v>
       </c>
       <c r="G115" t="n">
-        <v>4.297740459442139</v>
+        <v>4.297740936279297</v>
       </c>
       <c r="H115" t="n">
-        <v>-3.387939453125</v>
+        <v>-3.387938737869263</v>
       </c>
     </row>
     <row r="116">
@@ -3442,10 +3442,10 @@
         <v>0.9502482414245605</v>
       </c>
       <c r="C116" t="n">
-        <v>-4.526888847351074</v>
+        <v>-4.526888370513916</v>
       </c>
       <c r="D116" t="n">
-        <v>0.6776186227798462</v>
+        <v>0.6776184439659119</v>
       </c>
       <c r="E116" t="n">
         <v>10.64062023162842</v>
@@ -3454,10 +3454,10 @@
         <v>29.78906440734863</v>
       </c>
       <c r="G116" t="n">
-        <v>0.07262569665908813</v>
+        <v>0.0726240873336792</v>
       </c>
       <c r="H116" t="n">
-        <v>-3.23035192489624</v>
+        <v>-3.230351686477661</v>
       </c>
     </row>
     <row r="117">
@@ -3468,10 +3468,10 @@
         <v>0.9535725712776184</v>
       </c>
       <c r="C117" t="n">
-        <v>-6.476078987121582</v>
+        <v>-6.476080417633057</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9419180154800415</v>
+        <v>0.9419178366661072</v>
       </c>
       <c r="E117" t="n">
         <v>11.40600776672363</v>
@@ -3480,10 +3480,10 @@
         <v>30.36520957946777</v>
       </c>
       <c r="G117" t="n">
-        <v>-2.015465259552002</v>
+        <v>-2.015466928482056</v>
       </c>
       <c r="H117" t="n">
-        <v>-2.646555423736572</v>
+        <v>-2.646555662155151</v>
       </c>
     </row>
     <row r="118">
@@ -3494,10 +3494,10 @@
         <v>0.9581792950630188</v>
       </c>
       <c r="C118" t="n">
-        <v>-8.135214805603027</v>
+        <v>-8.13521671295166</v>
       </c>
       <c r="D118" t="n">
-        <v>1.881794571876526</v>
+        <v>1.881794452667236</v>
       </c>
       <c r="E118" t="n">
         <v>12.11329174041748</v>
@@ -3506,10 +3506,10 @@
         <v>31.01923751831055</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.854647159576416</v>
+        <v>-1.854646801948547</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.10475492477417</v>
+        <v>-2.104755163192749</v>
       </c>
     </row>
     <row r="119">
@@ -3517,13 +3517,13 @@
         <v>0.5615153908729553</v>
       </c>
       <c r="B119" t="n">
-        <v>0.9634087681770325</v>
+        <v>0.9634087085723877</v>
       </c>
       <c r="C119" t="n">
-        <v>-9.456294059753418</v>
+        <v>-9.456295967102051</v>
       </c>
       <c r="D119" t="n">
-        <v>3.643178462982178</v>
+        <v>3.643179416656494</v>
       </c>
       <c r="E119" t="n">
         <v>12.71645355224609</v>
@@ -3532,10 +3532,10 @@
         <v>31.65631866455078</v>
       </c>
       <c r="G119" t="n">
-        <v>0.1830459237098694</v>
+        <v>0.1830462217330933</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.170740604400635</v>
+        <v>-2.170740842819214</v>
       </c>
     </row>
     <row r="120">
@@ -3552,16 +3552,16 @@
         <v>6.231581211090088</v>
       </c>
       <c r="E120" t="n">
-        <v>13.00448036193848</v>
+        <v>13.00448131561279</v>
       </c>
       <c r="F120" t="n">
         <v>32.23357391357422</v>
       </c>
       <c r="G120" t="n">
-        <v>3.402154445648193</v>
+        <v>3.402154684066772</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.377328872680664</v>
+        <v>-3.377328634262085</v>
       </c>
     </row>
     <row r="121">
@@ -3572,22 +3572,22 @@
         <v>0.9731182456016541</v>
       </c>
       <c r="C121" t="n">
-        <v>-10.93468952178955</v>
+        <v>-10.93469142913818</v>
       </c>
       <c r="D121" t="n">
         <v>9.66666316986084</v>
       </c>
       <c r="E121" t="n">
-        <v>12.62370109558105</v>
+        <v>12.62370014190674</v>
       </c>
       <c r="F121" t="n">
-        <v>32.76180267333984</v>
+        <v>32.76180648803711</v>
       </c>
       <c r="G121" t="n">
-        <v>7.14194917678833</v>
+        <v>7.141948699951172</v>
       </c>
       <c r="H121" t="n">
-        <v>-5.669342994689941</v>
+        <v>-5.669342517852783</v>
       </c>
     </row>
     <row r="122">
@@ -3607,7 +3607,7 @@
         <v>10.98014354705811</v>
       </c>
       <c r="F122" t="n">
-        <v>35.59557723999023</v>
+        <v>35.5955810546875</v>
       </c>
       <c r="G122" t="n">
         <v>11.8169002532959</v>
@@ -3621,7 +3621,7 @@
         <v>0.6003017425537109</v>
       </c>
       <c r="B123" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C123" t="n">
         <v>-10.21685314178467</v>
@@ -3630,13 +3630,13 @@
         <v>19.03135108947754</v>
       </c>
       <c r="E123" t="n">
-        <v>7.145895957946777</v>
+        <v>7.145896434783936</v>
       </c>
       <c r="F123" t="n">
         <v>35.63029098510742</v>
       </c>
       <c r="G123" t="n">
-        <v>15.15485858917236</v>
+        <v>15.15485763549805</v>
       </c>
       <c r="H123" t="n">
         <v>-8.394699096679688</v>
@@ -3647,7 +3647,7 @@
         <v>0.6065787672996521</v>
       </c>
       <c r="B124" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C124" t="n">
         <v>-8.885464668273926</v>
@@ -3656,7 +3656,7 @@
         <v>24.39792442321777</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3149249851703644</v>
+        <v>0.3149249255657196</v>
       </c>
       <c r="F124" t="n">
         <v>35.29672241210938</v>
@@ -3673,10 +3673,10 @@
         <v>0.6187805533409119</v>
       </c>
       <c r="B125" t="n">
-        <v>0.003496981458738446</v>
+        <v>0.003496962366625667</v>
       </c>
       <c r="C125" t="n">
-        <v>-6.977997779846191</v>
+        <v>-6.977999210357666</v>
       </c>
       <c r="D125" t="n">
         <v>29.73955345153809</v>
@@ -3691,7 +3691,7 @@
         <v>20.8059139251709</v>
       </c>
       <c r="H125" t="n">
-        <v>-6.079531669616699</v>
+        <v>-6.079532146453857</v>
       </c>
     </row>
     <row r="126">
@@ -3699,10 +3699,10 @@
         <v>0.6362619400024414</v>
       </c>
       <c r="B126" t="n">
-        <v>0.01307181175798178</v>
+        <v>0.01307179313153028</v>
       </c>
       <c r="C126" t="n">
-        <v>-4.505127906799316</v>
+        <v>-4.505127429962158</v>
       </c>
       <c r="D126" t="n">
         <v>35.09157943725586</v>
@@ -3711,13 +3711,13 @@
         <v>-15.93817806243896</v>
       </c>
       <c r="F126" t="n">
-        <v>33.10154342651367</v>
+        <v>33.10154724121094</v>
       </c>
       <c r="G126" t="n">
         <v>22.39847373962402</v>
       </c>
       <c r="H126" t="n">
-        <v>-3.516439437866211</v>
+        <v>-3.51643967628479</v>
       </c>
     </row>
     <row r="127">
@@ -3725,10 +3725,10 @@
         <v>0.6589251160621643</v>
       </c>
       <c r="B127" t="n">
-        <v>0.02918294817209244</v>
+        <v>0.0291829276829958</v>
       </c>
       <c r="C127" t="n">
-        <v>-1.396153688430786</v>
+        <v>-1.396151065826416</v>
       </c>
       <c r="D127" t="n">
         <v>40.80989456176758</v>
@@ -3737,7 +3737,7 @@
         <v>-18.16719818115234</v>
       </c>
       <c r="F127" t="n">
-        <v>31.16701507568359</v>
+        <v>31.16701698303223</v>
       </c>
       <c r="G127" t="n">
         <v>22.90609550476074</v>
@@ -3751,25 +3751,25 @@
         <v>0.6874180436134338</v>
       </c>
       <c r="B128" t="n">
-        <v>0.05181906372308731</v>
+        <v>0.05181904509663582</v>
       </c>
       <c r="C128" t="n">
-        <v>2.366365194320679</v>
+        <v>2.3663649559021</v>
       </c>
       <c r="D128" t="n">
         <v>46.96034240722656</v>
       </c>
       <c r="E128" t="n">
-        <v>-15.93325328826904</v>
+        <v>-15.93325138092041</v>
       </c>
       <c r="F128" t="n">
-        <v>28.74524116516113</v>
+        <v>28.74524307250977</v>
       </c>
       <c r="G128" t="n">
         <v>22.43967628479004</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9277579784393311</v>
+        <v>0.9277579188346863</v>
       </c>
     </row>
     <row r="129">
@@ -3777,19 +3777,19 @@
         <v>0.7219004034996033</v>
       </c>
       <c r="B129" t="n">
-        <v>0.08015648275613785</v>
+        <v>0.08015646040439606</v>
       </c>
       <c r="C129" t="n">
-        <v>6.582390785217285</v>
+        <v>6.582391262054443</v>
       </c>
       <c r="D129" t="n">
-        <v>52.80185317993164</v>
+        <v>52.80184936523438</v>
       </c>
       <c r="E129" t="n">
         <v>-12.10377597808838</v>
       </c>
       <c r="F129" t="n">
-        <v>25.9461669921875</v>
+        <v>25.94616889953613</v>
       </c>
       <c r="G129" t="n">
         <v>21.11116790771484</v>
@@ -3803,7 +3803,7 @@
         <v>0.7605391144752502</v>
       </c>
       <c r="B130" t="n">
-        <v>0.1129087284207344</v>
+        <v>0.112908735871315</v>
       </c>
       <c r="C130" t="n">
         <v>10.92053031921387</v>
@@ -3829,16 +3829,16 @@
         <v>0.8002969622612</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1486511528491974</v>
+        <v>0.1486511379480362</v>
       </c>
       <c r="C131" t="n">
         <v>15.04599761962891</v>
       </c>
       <c r="D131" t="n">
-        <v>59.98260116577148</v>
+        <v>59.98259735107422</v>
       </c>
       <c r="E131" t="n">
-        <v>-4.670529365539551</v>
+        <v>-4.670528888702393</v>
       </c>
       <c r="F131" t="n">
         <v>19.71154022216797</v>
@@ -3847,7 +3847,7 @@
         <v>15.97082328796387</v>
       </c>
       <c r="H131" t="n">
-        <v>3.661338806152344</v>
+        <v>3.661338567733765</v>
       </c>
     </row>
     <row r="132">
@@ -3855,7 +3855,7 @@
         <v>0.8381056785583496</v>
       </c>
       <c r="B132" t="n">
-        <v>0.1858607232570648</v>
+        <v>0.1858607679605484</v>
       </c>
       <c r="C132" t="n">
         <v>18.74056243896484</v>
@@ -3864,7 +3864,7 @@
         <v>60.46043395996094</v>
       </c>
       <c r="E132" t="n">
-        <v>-1.584898471832275</v>
+        <v>-1.584898591041565</v>
       </c>
       <c r="F132" t="n">
         <v>16.54908752441406</v>
@@ -3881,19 +3881,19 @@
         <v>0.8719653487205505</v>
       </c>
       <c r="B133" t="n">
-        <v>0.2228648960590363</v>
+        <v>0.2228649407625198</v>
       </c>
       <c r="C133" t="n">
         <v>21.90056228637695</v>
       </c>
       <c r="D133" t="n">
-        <v>58.78124237060547</v>
+        <v>58.7812385559082</v>
       </c>
       <c r="E133" t="n">
         <v>0.9838740229606628</v>
       </c>
       <c r="F133" t="n">
-        <v>13.53957939147949</v>
+        <v>13.53958034515381</v>
       </c>
       <c r="G133" t="n">
         <v>9.315546035766602</v>
@@ -3919,10 +3919,10 @@
         <v>2.933851480484009</v>
       </c>
       <c r="F134" t="n">
-        <v>10.76827621459961</v>
+        <v>10.76827716827393</v>
       </c>
       <c r="G134" t="n">
-        <v>6.670467853546143</v>
+        <v>6.670468330383301</v>
       </c>
       <c r="H134" t="n">
         <v>3.584855556488037</v>
@@ -3939,7 +3939,7 @@
         <v>26.39323425292969</v>
       </c>
       <c r="D135" t="n">
-        <v>49.6650505065918</v>
+        <v>49.66505432128906</v>
       </c>
       <c r="E135" t="n">
         <v>4.161262989044189</v>
@@ -3948,15 +3948,15 @@
         <v>8.238372802734375</v>
       </c>
       <c r="G135" t="n">
-        <v>4.813408374786377</v>
+        <v>4.813408851623535</v>
       </c>
       <c r="H135" t="n">
-        <v>4.1109619140625</v>
+        <v>4.110961437225342</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.9420999884605408</v>
+        <v>0.942099928855896</v>
       </c>
       <c r="B136" t="n">
         <v>0.3201094269752502</v>
@@ -3968,13 +3968,13 @@
         <v>42.70198059082031</v>
       </c>
       <c r="E136" t="n">
-        <v>4.564177513122559</v>
+        <v>4.564177989959717</v>
       </c>
       <c r="F136" t="n">
-        <v>5.868978500366211</v>
+        <v>5.868977546691895</v>
       </c>
       <c r="G136" t="n">
-        <v>3.620648860931396</v>
+        <v>3.620649099349976</v>
       </c>
       <c r="H136" t="n">
         <v>4.976856231689453</v>
@@ -3997,13 +3997,13 @@
         <v>3.94160270690918</v>
       </c>
       <c r="F137" t="n">
-        <v>3.520482063293457</v>
+        <v>3.520481109619141</v>
       </c>
       <c r="G137" t="n">
-        <v>2.80244779586792</v>
+        <v>2.802448034286499</v>
       </c>
       <c r="H137" t="n">
-        <v>6.032258033752441</v>
+        <v>6.032257556915283</v>
       </c>
     </row>
     <row r="138">
@@ -4026,33 +4026,33 @@
         <v>1.052264213562012</v>
       </c>
       <c r="G138" t="n">
-        <v>2.056178569793701</v>
+        <v>2.05617880821228</v>
       </c>
       <c r="H138" t="n">
-        <v>7.116895198822021</v>
+        <v>7.116894721984863</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.9593270421028137</v>
+        <v>0.9593269824981689</v>
       </c>
       <c r="B139" t="n">
         <v>0.4041948318481445</v>
       </c>
       <c r="C139" t="n">
-        <v>28.04783248901367</v>
+        <v>28.0478343963623</v>
       </c>
       <c r="D139" t="n">
         <v>17.96771049499512</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.3512796461582184</v>
+        <v>-0.3512795865535736</v>
       </c>
       <c r="F139" t="n">
         <v>-1.60366153717041</v>
       </c>
       <c r="G139" t="n">
-        <v>1.198741436004639</v>
+        <v>1.198739886283875</v>
       </c>
       <c r="H139" t="n">
         <v>8.126598358154297</v>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.9593270421028137</v>
+        <v>0.9593269824981689</v>
       </c>
       <c r="B140" t="n">
         <v>0.4352720677852631</v>
@@ -4072,21 +4072,21 @@
         <v>10.77225208282471</v>
       </c>
       <c r="E140" t="n">
-        <v>-2.090726375579834</v>
+        <v>-2.090726137161255</v>
       </c>
       <c r="F140" t="n">
-        <v>-4.394654273986816</v>
+        <v>-4.394652366638184</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2495437264442444</v>
+        <v>0.2495440244674683</v>
       </c>
       <c r="H140" t="n">
-        <v>9.045050621032715</v>
+        <v>9.045049667358398</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.9593270421028137</v>
+        <v>0.9593269824981689</v>
       </c>
       <c r="B141" t="n">
         <v>0.4679297506809235</v>
@@ -4095,16 +4095,16 @@
         <v>27.80424690246582</v>
       </c>
       <c r="D141" t="n">
-        <v>4.871069431304932</v>
+        <v>4.871070384979248</v>
       </c>
       <c r="E141" t="n">
-        <v>-2.13569974899292</v>
+        <v>-2.135699987411499</v>
       </c>
       <c r="F141" t="n">
         <v>-7.160786628723145</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.5786251425743103</v>
+        <v>-0.5786248445510864</v>
       </c>
       <c r="H141" t="n">
         <v>9.931349754333496</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.9593270421028137</v>
+        <v>0.9593269824981689</v>
       </c>
       <c r="B142" t="n">
         <v>0.5002965331077576</v>
@@ -4121,16 +4121,16 @@
         <v>28.07055282592773</v>
       </c>
       <c r="D142" t="n">
-        <v>0.7866884469985962</v>
+        <v>0.7866901755332947</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.026734113693237</v>
+        <v>-1.026734232902527</v>
       </c>
       <c r="F142" t="n">
         <v>-9.702609062194824</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.9846557974815369</v>
+        <v>-0.9846574068069458</v>
       </c>
       <c r="H142" t="n">
         <v>10.85061550140381</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.9593270421028137</v>
+        <v>0.9593269824981689</v>
       </c>
       <c r="B143" t="n">
         <v>0.5300386548042297</v>
@@ -4147,19 +4147,19 @@
         <v>28.51385307312012</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.003869414329529</v>
+        <v>-1.003869533538818</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.2127651423215866</v>
+        <v>-0.2127651870250702</v>
       </c>
       <c r="F143" t="n">
         <v>-11.85473346710205</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.7114605307579041</v>
+        <v>-0.7114602327346802</v>
       </c>
       <c r="H143" t="n">
-        <v>11.77196502685547</v>
+        <v>11.77196598052979</v>
       </c>
     </row>
     <row r="144">
@@ -4170,19 +4170,19 @@
         <v>0.555220901966095</v>
       </c>
       <c r="C144" t="n">
-        <v>28.97129058837891</v>
+        <v>28.97129249572754</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.5029195547103882</v>
+        <v>-0.5029197335243225</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.853667676448822</v>
+        <v>-0.8536676168441772</v>
       </c>
       <c r="F144" t="n">
         <v>-13.51886463165283</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3758159279823303</v>
+        <v>0.3758162260055542</v>
       </c>
       <c r="H144" t="n">
         <v>12.52795505523682</v>
@@ -4196,19 +4196,19 @@
         <v>0.5746930837631226</v>
       </c>
       <c r="C145" t="n">
-        <v>29.36255836486816</v>
+        <v>29.36255645751953</v>
       </c>
       <c r="D145" t="n">
-        <v>1.839624047279358</v>
+        <v>1.839622974395752</v>
       </c>
       <c r="E145" t="n">
-        <v>-3.068986654281616</v>
+        <v>-3.068986415863037</v>
       </c>
       <c r="F145" t="n">
-        <v>-14.64296627044678</v>
+        <v>-14.64296817779541</v>
       </c>
       <c r="G145" t="n">
-        <v>2.299872875213623</v>
+        <v>2.299873113632202</v>
       </c>
       <c r="H145" t="n">
         <v>12.81040573120117</v>
@@ -4228,13 +4228,13 @@
         <v>5.257265567779541</v>
       </c>
       <c r="E146" t="n">
-        <v>-5.918110370635986</v>
+        <v>-5.918110847473145</v>
       </c>
       <c r="F146" t="n">
         <v>-15.17396450042725</v>
       </c>
       <c r="G146" t="n">
-        <v>5.042630672454834</v>
+        <v>5.042629241943359</v>
       </c>
       <c r="H146" t="n">
         <v>12.13060283660889</v>
@@ -4251,16 +4251,16 @@
         <v>29.99117279052734</v>
       </c>
       <c r="D147" t="n">
-        <v>9.069263458251953</v>
+        <v>9.06926155090332</v>
       </c>
       <c r="E147" t="n">
         <v>-8.310957908630371</v>
       </c>
       <c r="F147" t="n">
-        <v>-15.0294828414917</v>
+        <v>-15.02948665618896</v>
       </c>
       <c r="G147" t="n">
-        <v>8.58693790435791</v>
+        <v>8.586936950683594</v>
       </c>
       <c r="H147" t="n">
         <v>9.833248138427734</v>
@@ -4277,13 +4277,13 @@
         <v>31.54406356811523</v>
       </c>
       <c r="D148" t="n">
-        <v>9.519939422607422</v>
+        <v>9.519938468933105</v>
       </c>
       <c r="E148" t="n">
         <v>-5.253461837768555</v>
       </c>
       <c r="F148" t="n">
-        <v>-16.38406753540039</v>
+        <v>-16.38406562805176</v>
       </c>
       <c r="G148" t="n">
         <v>15.58547306060791</v>
@@ -4294,33 +4294,33 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B149" t="n">
         <v>0.5945975184440613</v>
       </c>
       <c r="C149" t="n">
-        <v>31.88261032104492</v>
+        <v>31.88261222839355</v>
       </c>
       <c r="D149" t="n">
         <v>13.56563663482666</v>
       </c>
       <c r="E149" t="n">
-        <v>-6.814529895782471</v>
+        <v>-6.814529418945312</v>
       </c>
       <c r="F149" t="n">
-        <v>-14.68702411651611</v>
+        <v>-14.68702602386475</v>
       </c>
       <c r="G149" t="n">
         <v>20.53302955627441</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.462053775787354</v>
+        <v>-3.462053537368774</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B150" t="n">
         <v>0.6086172461509705</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B151" t="n">
         <v>0.6290242075920105</v>
@@ -4361,7 +4361,7 @@
         <v>-3.894246101379395</v>
       </c>
       <c r="F151" t="n">
-        <v>-9.042162895202637</v>
+        <v>-9.04216480255127</v>
       </c>
       <c r="G151" t="n">
         <v>32.63379287719727</v>
@@ -4372,19 +4372,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.002122199861332774</v>
+        <v>0.002122191013768315</v>
       </c>
       <c r="B152" t="n">
         <v>0.6552510857582092</v>
       </c>
       <c r="C152" t="n">
-        <v>29.98164176940918</v>
+        <v>29.98164367675781</v>
       </c>
       <c r="D152" t="n">
         <v>21.23181533813477</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.49606728553772</v>
+        <v>-1.496067404747009</v>
       </c>
       <c r="F152" t="n">
         <v>-5.264573097229004</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.02146241627633572</v>
+        <v>0.02146240882575512</v>
       </c>
       <c r="B153" t="n">
         <v>0.6864588260650635</v>
@@ -4410,7 +4410,7 @@
         <v>20.17507171630859</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5703038573265076</v>
+        <v>0.5703037977218628</v>
       </c>
       <c r="F153" t="n">
         <v>-1.041567802429199</v>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.05032888799905777</v>
+        <v>0.05032887682318687</v>
       </c>
       <c r="B154" t="n">
         <v>0.7213463187217712</v>
@@ -4445,12 +4445,12 @@
         <v>51.44086456298828</v>
       </c>
       <c r="H154" t="n">
-        <v>-7.191113471984863</v>
+        <v>-7.19111442565918</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.08345458656549454</v>
+        <v>0.08345457911491394</v>
       </c>
       <c r="B155" t="n">
         <v>0.7580199241638184</v>
@@ -4468,15 +4468,15 @@
         <v>7.778188705444336</v>
       </c>
       <c r="G155" t="n">
-        <v>54.73610305786133</v>
+        <v>54.73609924316406</v>
       </c>
       <c r="H155" t="n">
-        <v>-3.261296272277832</v>
+        <v>-3.261296033859253</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.1166191175580025</v>
+        <v>0.1166190803050995</v>
       </c>
       <c r="B156" t="n">
         <v>0.794208824634552</v>
@@ -4488,10 +4488,10 @@
         <v>16.87634658813477</v>
       </c>
       <c r="E156" t="n">
-        <v>5.218241214752197</v>
+        <v>5.218241691589355</v>
       </c>
       <c r="F156" t="n">
-        <v>11.83971309661865</v>
+        <v>11.83971405029297</v>
       </c>
       <c r="G156" t="n">
         <v>55.75179290771484</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.1834927797317505</v>
+        <v>0.1834928095340729</v>
       </c>
       <c r="B158" t="n">
         <v>0.8571236133575439</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.2216275632381439</v>
+        <v>0.2216275930404663</v>
       </c>
       <c r="B159" t="n">
         <v>0.8814563751220703</v>
@@ -4601,7 +4601,7 @@
         <v>40.71825408935547</v>
       </c>
       <c r="H160" t="n">
-        <v>2.807422876358032</v>
+        <v>2.807422637939453</v>
       </c>
     </row>
     <row r="161">
@@ -4612,7 +4612,7 @@
         <v>0.9138880968093872</v>
       </c>
       <c r="C161" t="n">
-        <v>6.739657402038574</v>
+        <v>6.7396559715271</v>
       </c>
       <c r="D161" t="n">
         <v>3.490407466888428</v>
@@ -4621,13 +4621,13 @@
         <v>5.840417861938477</v>
       </c>
       <c r="F161" t="n">
-        <v>23.23067665100098</v>
+        <v>23.23067855834961</v>
       </c>
       <c r="G161" t="n">
         <v>33.95138168334961</v>
       </c>
       <c r="H161" t="n">
-        <v>2.88063383102417</v>
+        <v>2.880633592605591</v>
       </c>
     </row>
     <row r="162">
@@ -4638,13 +4638,13 @@
         <v>0.921866238117218</v>
       </c>
       <c r="C162" t="n">
-        <v>4.034048080444336</v>
+        <v>4.034048557281494</v>
       </c>
       <c r="D162" t="n">
-        <v>1.854011178016663</v>
+        <v>1.854010105133057</v>
       </c>
       <c r="E162" t="n">
-        <v>6.303715705871582</v>
+        <v>6.303715229034424</v>
       </c>
       <c r="F162" t="n">
         <v>23.57231140136719</v>
@@ -4653,7 +4653,7 @@
         <v>26.44856643676758</v>
       </c>
       <c r="H162" t="n">
-        <v>2.463344812393188</v>
+        <v>2.463344573974609</v>
       </c>
     </row>
     <row r="163">
@@ -4664,10 +4664,10 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C163" t="n">
-        <v>1.425791501998901</v>
+        <v>1.425792217254639</v>
       </c>
       <c r="D163" t="n">
-        <v>0.7336050271987915</v>
+        <v>0.7336048483848572</v>
       </c>
       <c r="E163" t="n">
         <v>7.104920387268066</v>
@@ -4679,21 +4679,21 @@
         <v>18.4015941619873</v>
       </c>
       <c r="H163" t="n">
-        <v>1.477619886398315</v>
+        <v>1.477619767189026</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0.4137240648269653</v>
+        <v>0.4137240350246429</v>
       </c>
       <c r="B164" t="n">
         <v>0.9246885776519775</v>
       </c>
       <c r="C164" t="n">
-        <v>-1.0372154712677</v>
+        <v>-1.037214756011963</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1136938259005547</v>
+        <v>0.1136936694383621</v>
       </c>
       <c r="E164" t="n">
         <v>8.180473327636719</v>
@@ -4705,7 +4705,7 @@
         <v>10.24388885498047</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1576206833124161</v>
+        <v>0.1576207727193832</v>
       </c>
     </row>
     <row r="165">
@@ -4716,22 +4716,22 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C165" t="n">
-        <v>-3.284035921096802</v>
+        <v>-3.284033298492432</v>
       </c>
       <c r="D165" t="n">
-        <v>0.001717199920676649</v>
+        <v>0.001717048115096986</v>
       </c>
       <c r="E165" t="n">
         <v>9.489165306091309</v>
       </c>
       <c r="F165" t="n">
-        <v>22.33822631835938</v>
+        <v>22.33822822570801</v>
       </c>
       <c r="G165" t="n">
-        <v>2.711741924285889</v>
+        <v>2.711742162704468</v>
       </c>
       <c r="H165" t="n">
-        <v>-1.176342010498047</v>
+        <v>-1.176342248916626</v>
       </c>
     </row>
     <row r="166">
@@ -4742,10 +4742,10 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C166" t="n">
-        <v>-5.25831127166748</v>
+        <v>-5.258308887481689</v>
       </c>
       <c r="D166" t="n">
-        <v>0.3669420480728149</v>
+        <v>0.366941899061203</v>
       </c>
       <c r="E166" t="n">
         <v>10.97675132751465</v>
@@ -4754,7 +4754,7 @@
         <v>22.03657150268555</v>
       </c>
       <c r="G166" t="n">
-        <v>-3.21966028213501</v>
+        <v>-3.219660043716431</v>
       </c>
       <c r="H166" t="n">
         <v>-2.145746231079102</v>
@@ -4768,22 +4768,22 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C167" t="n">
-        <v>-6.93187427520752</v>
+        <v>-6.931873798370361</v>
       </c>
       <c r="D167" t="n">
-        <v>1.16355574131012</v>
+        <v>1.16355562210083</v>
       </c>
       <c r="E167" t="n">
-        <v>12.52114772796631</v>
+        <v>12.52114677429199</v>
       </c>
       <c r="F167" t="n">
         <v>22.16421890258789</v>
       </c>
       <c r="G167" t="n">
-        <v>-6.596498966217041</v>
+        <v>-6.596500396728516</v>
       </c>
       <c r="H167" t="n">
-        <v>-2.283126354217529</v>
+        <v>-2.28312611579895</v>
       </c>
     </row>
     <row r="168">
@@ -4794,10 +4794,10 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C168" t="n">
-        <v>-8.331479072570801</v>
+        <v>-8.331480979919434</v>
       </c>
       <c r="D168" t="n">
-        <v>2.322122097015381</v>
+        <v>2.322123050689697</v>
       </c>
       <c r="E168" t="n">
         <v>13.89237785339355</v>
@@ -4806,10 +4806,10 @@
         <v>22.73730087280273</v>
       </c>
       <c r="G168" t="n">
-        <v>-6.938131809234619</v>
+        <v>-6.938131332397461</v>
       </c>
       <c r="H168" t="n">
-        <v>-1.426787614822388</v>
+        <v>-1.426787376403809</v>
       </c>
     </row>
     <row r="169">
@@ -4820,22 +4820,22 @@
         <v>0.9246885776519775</v>
       </c>
       <c r="C169" t="n">
-        <v>-9.535000801086426</v>
+        <v>-9.535002708435059</v>
       </c>
       <c r="D169" t="n">
-        <v>3.765028476715088</v>
+        <v>3.765029430389404</v>
       </c>
       <c r="E169" t="n">
-        <v>14.7605562210083</v>
+        <v>14.76055717468262</v>
       </c>
       <c r="F169" t="n">
         <v>23.60786247253418</v>
       </c>
       <c r="G169" t="n">
-        <v>-4.543470859527588</v>
+        <v>-4.543468475341797</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.1620659679174423</v>
+        <v>-0.1620659977197647</v>
       </c>
     </row>
     <row r="170">
@@ -4846,7 +4846,7 @@
         <v>0.9249822497367859</v>
       </c>
       <c r="C170" t="n">
-        <v>-10.57363605499268</v>
+        <v>-10.57363796234131</v>
       </c>
       <c r="D170" t="n">
         <v>5.563311100006104</v>
@@ -4858,7 +4858,7 @@
         <v>24.52619743347168</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.4279865622520447</v>
+        <v>-0.4279881715774536</v>
       </c>
       <c r="H170" t="n">
         <v>0.3658528327941895</v>
@@ -4869,22 +4869,22 @@
         <v>0.5785559415817261</v>
       </c>
       <c r="B171" t="n">
-        <v>0.9325689077377319</v>
+        <v>0.9325688481330872</v>
       </c>
       <c r="C171" t="n">
-        <v>-11.30011081695557</v>
+        <v>-11.3001127243042</v>
       </c>
       <c r="D171" t="n">
         <v>8.095279693603516</v>
       </c>
       <c r="E171" t="n">
-        <v>14.3198299407959</v>
+        <v>14.31983089447021</v>
       </c>
       <c r="F171" t="n">
-        <v>25.2607421875</v>
+        <v>25.26074409484863</v>
       </c>
       <c r="G171" t="n">
-        <v>4.073113918304443</v>
+        <v>4.073112487792969</v>
       </c>
       <c r="H171" t="n">
         <v>-0.8365252017974854</v>
@@ -4904,16 +4904,16 @@
         <v>11.79491806030273</v>
       </c>
       <c r="E172" t="n">
-        <v>12.81716346740723</v>
+        <v>12.81716442108154</v>
       </c>
       <c r="F172" t="n">
-        <v>25.69960975646973</v>
+        <v>25.69961166381836</v>
       </c>
       <c r="G172" t="n">
         <v>8.02421760559082</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.660946369171143</v>
+        <v>-3.660946130752563</v>
       </c>
     </row>
     <row r="173">
@@ -4947,10 +4947,10 @@
         <v>0.5968697667121887</v>
       </c>
       <c r="B174" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C174" t="n">
-        <v>-9.259343147277832</v>
+        <v>-9.259345054626465</v>
       </c>
       <c r="D174" t="n">
         <v>22.20937538146973</v>
@@ -4962,7 +4962,7 @@
         <v>32.64299774169922</v>
       </c>
       <c r="G174" t="n">
-        <v>11.38341236114502</v>
+        <v>11.3834114074707</v>
       </c>
       <c r="H174" t="n">
         <v>-8.159849166870117</v>
@@ -4973,10 +4973,10 @@
         <v>0.6112648248672485</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0005332001601345837</v>
+        <v>0.0005332406144589186</v>
       </c>
       <c r="C175" t="n">
-        <v>-7.096270561218262</v>
+        <v>-7.096271991729736</v>
       </c>
       <c r="D175" t="n">
         <v>27.70474433898926</v>
@@ -4985,10 +4985,10 @@
         <v>-6.226450443267822</v>
       </c>
       <c r="F175" t="n">
-        <v>32.31375122070312</v>
+        <v>32.31375503540039</v>
       </c>
       <c r="G175" t="n">
-        <v>14.44857692718506</v>
+        <v>14.44857597351074</v>
       </c>
       <c r="H175" t="n">
         <v>-8.25111198425293</v>
@@ -4999,10 +4999,10 @@
         <v>0.6318724751472473</v>
       </c>
       <c r="B176" t="n">
-        <v>0.004391826223582029</v>
+        <v>0.00439180713146925</v>
       </c>
       <c r="C176" t="n">
-        <v>-4.484148979187012</v>
+        <v>-4.484146595001221</v>
       </c>
       <c r="D176" t="n">
         <v>32.8923454284668</v>
@@ -5017,7 +5017,7 @@
         <v>17.25416564941406</v>
       </c>
       <c r="H176" t="n">
-        <v>-6.346748352050781</v>
+        <v>-6.346749305725098</v>
       </c>
     </row>
     <row r="177">
@@ -5025,10 +5025,10 @@
         <v>0.656758189201355</v>
       </c>
       <c r="B177" t="n">
-        <v>0.01303074415773153</v>
+        <v>0.01303072553128004</v>
       </c>
       <c r="C177" t="n">
-        <v>-1.416091203689575</v>
+        <v>-1.416090488433838</v>
       </c>
       <c r="D177" t="n">
         <v>38.13530731201172</v>
@@ -5043,7 +5043,7 @@
         <v>18.87170600891113</v>
       </c>
       <c r="H177" t="n">
-        <v>-3.829887866973877</v>
+        <v>-3.829888105392456</v>
       </c>
     </row>
     <row r="178">
@@ -5051,13 +5051,13 @@
         <v>0.6859877109527588</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0286470428109169</v>
+        <v>0.02864708192646503</v>
       </c>
       <c r="C178" t="n">
-        <v>2.237298727035522</v>
+        <v>2.237298488616943</v>
       </c>
       <c r="D178" t="n">
-        <v>43.9439811706543</v>
+        <v>43.94398498535156</v>
       </c>
       <c r="E178" t="n">
         <v>-19.91087913513184</v>
@@ -5077,10 +5077,10 @@
         <v>0.720793604850769</v>
       </c>
       <c r="B179" t="n">
-        <v>0.05231747776269913</v>
+        <v>0.05231745913624763</v>
       </c>
       <c r="C179" t="n">
-        <v>6.468018531799316</v>
+        <v>6.468019008636475</v>
       </c>
       <c r="D179" t="n">
         <v>49.97467803955078</v>
@@ -5095,7 +5095,7 @@
         <v>17.6115550994873</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1107643991708755</v>
+        <v>0.1107644960284233</v>
       </c>
     </row>
     <row r="180">
@@ -5103,7 +5103,7 @@
         <v>0.7610998153686523</v>
       </c>
       <c r="B180" t="n">
-        <v>0.08323613554239273</v>
+        <v>0.08323611319065094</v>
       </c>
       <c r="C180" t="n">
         <v>10.96612358093262</v>
@@ -5121,7 +5121,7 @@
         <v>15.40421485900879</v>
       </c>
       <c r="H180" t="n">
-        <v>1.268120527267456</v>
+        <v>1.268120408058167</v>
       </c>
     </row>
     <row r="181">
@@ -5129,16 +5129,16 @@
         <v>0.8039534091949463</v>
       </c>
       <c r="B181" t="n">
-        <v>0.1194589212536812</v>
+        <v>0.1194589287042618</v>
       </c>
       <c r="C181" t="n">
         <v>15.29684925079346</v>
       </c>
       <c r="D181" t="n">
-        <v>58.52754592895508</v>
+        <v>58.52754211425781</v>
       </c>
       <c r="E181" t="n">
-        <v>-5.65667200088501</v>
+        <v>-5.656672477722168</v>
       </c>
       <c r="F181" t="n">
         <v>19.13573265075684</v>
@@ -5155,22 +5155,22 @@
         <v>0.8452123403549194</v>
       </c>
       <c r="B182" t="n">
-        <v>0.1588315665721893</v>
+        <v>0.1588316112756729</v>
       </c>
       <c r="C182" t="n">
         <v>19.12456130981445</v>
       </c>
       <c r="D182" t="n">
-        <v>59.81311798095703</v>
+        <v>59.81311416625977</v>
       </c>
       <c r="E182" t="n">
-        <v>-1.806278944015503</v>
+        <v>-1.806279063224792</v>
       </c>
       <c r="F182" t="n">
         <v>15.68352031707764</v>
       </c>
       <c r="G182" t="n">
-        <v>9.14877986907959</v>
+        <v>9.148778915405273</v>
       </c>
       <c r="H182" t="n">
         <v>1.710887551307678</v>
@@ -5181,10 +5181,10 @@
         <v>0.8816790580749512</v>
       </c>
       <c r="B183" t="n">
-        <v>0.1992898285388947</v>
+        <v>0.1992898136377335</v>
       </c>
       <c r="C183" t="n">
-        <v>22.31101417541504</v>
+        <v>22.31101608276367</v>
       </c>
       <c r="D183" t="n">
         <v>58.86860275268555</v>
@@ -5196,7 +5196,7 @@
         <v>12.30996417999268</v>
       </c>
       <c r="G183" t="n">
-        <v>5.72249174118042</v>
+        <v>5.722491264343262</v>
       </c>
       <c r="H183" t="n">
         <v>1.365616798400879</v>
@@ -5207,22 +5207,22 @@
         <v>0.9120364785194397</v>
       </c>
       <c r="B184" t="n">
-        <v>0.2388262152671814</v>
+        <v>0.2388261705636978</v>
       </c>
       <c r="C184" t="n">
         <v>24.83685302734375</v>
       </c>
       <c r="D184" t="n">
-        <v>55.77118682861328</v>
+        <v>55.77118301391602</v>
       </c>
       <c r="E184" t="n">
         <v>3.534459352493286</v>
       </c>
       <c r="F184" t="n">
-        <v>9.164272308349609</v>
+        <v>9.164273262023926</v>
       </c>
       <c r="G184" t="n">
-        <v>2.783320903778076</v>
+        <v>2.783321142196655</v>
       </c>
       <c r="H184" t="n">
         <v>1.266554474830627</v>
@@ -5239,16 +5239,16 @@
         <v>26.69604873657227</v>
       </c>
       <c r="D185" t="n">
-        <v>50.71401214599609</v>
+        <v>50.71400833129883</v>
       </c>
       <c r="E185" t="n">
         <v>4.55280876159668</v>
       </c>
       <c r="F185" t="n">
-        <v>6.332698822021484</v>
+        <v>6.332697868347168</v>
       </c>
       <c r="G185" t="n">
-        <v>0.7093310952186584</v>
+        <v>0.7093313932418823</v>
       </c>
       <c r="H185" t="n">
         <v>1.73780083656311</v>
@@ -5274,10 +5274,10 @@
         <v>3.81613826751709</v>
       </c>
       <c r="G186" t="n">
-        <v>-0.4160389304161072</v>
+        <v>-0.4160405397415161</v>
       </c>
       <c r="H186" t="n">
-        <v>2.777571439743042</v>
+        <v>2.777571201324463</v>
       </c>
     </row>
     <row r="187">
@@ -5300,10 +5300,10 @@
         <v>1.530478477478027</v>
       </c>
       <c r="G187" t="n">
-        <v>-0.7764496207237244</v>
+        <v>-0.7764493227005005</v>
       </c>
       <c r="H187" t="n">
-        <v>4.180874824523926</v>
+        <v>4.180874347686768</v>
       </c>
     </row>
     <row r="188">
@@ -5323,10 +5323,10 @@
         <v>2.734725952148438</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.6530733108520508</v>
+        <v>-0.653073251247406</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.6808952689170837</v>
+        <v>-0.6808949708938599</v>
       </c>
       <c r="H188" t="n">
         <v>5.72688102722168</v>
@@ -5346,16 +5346,16 @@
         <v>17.97307205200195</v>
       </c>
       <c r="E189" t="n">
-        <v>0.359995573759079</v>
+        <v>0.3599956333637238</v>
       </c>
       <c r="F189" t="n">
-        <v>-2.848418235778809</v>
+        <v>-2.848420143127441</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.4013561606407166</v>
+        <v>-0.4013558626174927</v>
       </c>
       <c r="H189" t="n">
-        <v>7.267461776733398</v>
+        <v>7.26746129989624</v>
       </c>
     </row>
     <row r="190">
@@ -5369,16 +5369,16 @@
         <v>27.27387237548828</v>
       </c>
       <c r="D190" t="n">
-        <v>10.13713264465332</v>
+        <v>10.137131690979</v>
       </c>
       <c r="E190" t="n">
         <v>-2.001528024673462</v>
       </c>
       <c r="F190" t="n">
-        <v>-5.111010551452637</v>
+        <v>-5.111008644104004</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.09692806005477905</v>
+        <v>-0.09692776203155518</v>
       </c>
       <c r="H190" t="n">
         <v>8.719694137573242</v>
@@ -5404,7 +5404,7 @@
         <v>-7.423369407653809</v>
       </c>
       <c r="G191" t="n">
-        <v>0.1920333504676819</v>
+        <v>0.1920355558395386</v>
       </c>
       <c r="H191" t="n">
         <v>10.03079605102539</v>
@@ -5421,16 +5421,16 @@
         <v>27.34112739562988</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.3549016714096069</v>
+        <v>-0.3549018204212189</v>
       </c>
       <c r="E192" t="n">
-        <v>-2.798229932785034</v>
+        <v>-2.798229694366455</v>
       </c>
       <c r="F192" t="n">
         <v>-9.715960502624512</v>
       </c>
       <c r="G192" t="n">
-        <v>0.504094660282135</v>
+        <v>0.5040949583053589</v>
       </c>
       <c r="H192" t="n">
         <v>11.13447856903076</v>
@@ -5447,16 +5447,16 @@
         <v>27.94517707824707</v>
       </c>
       <c r="D193" t="n">
-        <v>-2.091500759124756</v>
+        <v>-2.091498851776123</v>
       </c>
       <c r="E193" t="n">
-        <v>-1.59312105178833</v>
+        <v>-1.59312117099762</v>
       </c>
       <c r="F193" t="n">
         <v>-11.89795780181885</v>
       </c>
       <c r="G193" t="n">
-        <v>0.9314437508583069</v>
+        <v>0.9314440488815308</v>
       </c>
       <c r="H193" t="n">
         <v>11.957594871521</v>
@@ -5473,16 +5473,16 @@
         <v>28.60050201416016</v>
       </c>
       <c r="D194" t="n">
-        <v>-1.584760069847107</v>
+        <v>-1.584760189056396</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.2559510767459869</v>
+        <v>-0.2559510171413422</v>
       </c>
       <c r="F194" t="n">
         <v>-13.87221050262451</v>
       </c>
       <c r="G194" t="n">
-        <v>1.631898403167725</v>
+        <v>1.631898760795593</v>
       </c>
       <c r="H194" t="n">
         <v>12.46585655212402</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.9719566702842712</v>
+        <v>0.9719565510749817</v>
       </c>
       <c r="B195" t="n">
         <v>0.5456681847572327</v>
@@ -5499,7 +5499,7 @@
         <v>29.13460350036621</v>
       </c>
       <c r="D195" t="n">
-        <v>0.5982805490493774</v>
+        <v>0.5982822775840759</v>
       </c>
       <c r="E195" t="n">
         <v>0.6736176013946533</v>
@@ -5508,15 +5508,15 @@
         <v>-15.52835750579834</v>
       </c>
       <c r="G195" t="n">
-        <v>2.841630458831787</v>
+        <v>2.841628789901733</v>
       </c>
       <c r="H195" t="n">
-        <v>12.65200710296631</v>
+        <v>12.65200805664062</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.9770449995994568</v>
+        <v>0.977044939994812</v>
       </c>
       <c r="B196" t="n">
         <v>0.5650774240493774</v>
@@ -5528,13 +5528,13 @@
         <v>3.644351482391357</v>
       </c>
       <c r="E196" t="n">
-        <v>0.4265215992927551</v>
+        <v>0.4265215694904327</v>
       </c>
       <c r="F196" t="n">
-        <v>-16.73695373535156</v>
+        <v>-16.73695182800293</v>
       </c>
       <c r="G196" t="n">
-        <v>4.801170825958252</v>
+        <v>4.801170349121094</v>
       </c>
       <c r="H196" t="n">
         <v>12.40149021148682</v>
@@ -5554,13 +5554,13 @@
         <v>6.670427799224854</v>
       </c>
       <c r="E197" t="n">
-        <v>-1.718868255615234</v>
+        <v>-1.718868374824524</v>
       </c>
       <c r="F197" t="n">
-        <v>-17.35958480834961</v>
+        <v>-17.35958290100098</v>
       </c>
       <c r="G197" t="n">
-        <v>7.625985622406006</v>
+        <v>7.625986099243164</v>
       </c>
       <c r="H197" t="n">
         <v>11.31737518310547</v>
@@ -5577,13 +5577,13 @@
         <v>29.68305587768555</v>
       </c>
       <c r="D198" t="n">
-        <v>9.641531944274902</v>
+        <v>9.641530990600586</v>
       </c>
       <c r="E198" t="n">
-        <v>-4.753839492797852</v>
+        <v>-4.753839015960693</v>
       </c>
       <c r="F198" t="n">
-        <v>-17.27353286743164</v>
+        <v>-17.27353096008301</v>
       </c>
       <c r="G198" t="n">
         <v>11.26139068603516</v>
@@ -5603,16 +5603,16 @@
         <v>32.72341537475586</v>
       </c>
       <c r="D199" t="n">
-        <v>8.115840911865234</v>
+        <v>8.115839004516602</v>
       </c>
       <c r="E199" t="n">
         <v>-4.783977031707764</v>
       </c>
       <c r="F199" t="n">
-        <v>-16.03171157836914</v>
+        <v>-16.03171348571777</v>
       </c>
       <c r="G199" t="n">
-        <v>12.90883827209473</v>
+        <v>12.90883731842041</v>
       </c>
       <c r="H199" t="n">
         <v>2.589628219604492</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B200" t="n">
         <v>0.61091148853302</v>
@@ -5635,18 +5635,18 @@
         <v>-6.459099769592285</v>
       </c>
       <c r="F200" t="n">
-        <v>-14.21571254730225</v>
+        <v>-14.21571063995361</v>
       </c>
       <c r="G200" t="n">
         <v>18.38468551635742</v>
       </c>
       <c r="H200" t="n">
-        <v>-4.079713344573975</v>
+        <v>-4.079713821411133</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B201" t="n">
         <v>0.624312162399292</v>
@@ -5672,13 +5672,13 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B202" t="n">
         <v>0.6430636048316956</v>
       </c>
       <c r="C202" t="n">
-        <v>33.33849334716797</v>
+        <v>33.3384895324707</v>
       </c>
       <c r="D202" t="n">
         <v>19.5012092590332</v>
@@ -5693,24 +5693,24 @@
         <v>30.4012508392334</v>
       </c>
       <c r="H202" t="n">
-        <v>-17.53884696960449</v>
+        <v>-17.53884506225586</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B203" t="n">
         <v>0.6665224432945251</v>
       </c>
       <c r="C203" t="n">
-        <v>31.99574089050293</v>
+        <v>31.99574279785156</v>
       </c>
       <c r="D203" t="n">
         <v>20.23374176025391</v>
       </c>
       <c r="E203" t="n">
-        <v>-2.289539813995361</v>
+        <v>-2.28954005241394</v>
       </c>
       <c r="F203" t="n">
         <v>-4.755084037780762</v>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.009759283624589443</v>
+        <v>0.009759274311363697</v>
       </c>
       <c r="B204" t="n">
         <v>0.6941239833831787</v>
@@ -5736,10 +5736,10 @@
         <v>19.42002105712891</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.1829331368207932</v>
+        <v>-0.1829331815242767</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.5478315353393555</v>
+        <v>-0.5478314757347107</v>
       </c>
       <c r="G204" t="n">
         <v>42.85980987548828</v>
@@ -5750,13 +5750,13 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.03729579597711563</v>
+        <v>0.03729578480124474</v>
       </c>
       <c r="B205" t="n">
         <v>0.7251701354980469</v>
       </c>
       <c r="C205" t="n">
-        <v>27.44333267211914</v>
+        <v>27.44333457946777</v>
       </c>
       <c r="D205" t="n">
         <v>17.82676696777344</v>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.07081440836191177</v>
+        <v>0.07081446051597595</v>
       </c>
       <c r="B206" t="n">
         <v>0.7585616111755371</v>
       </c>
       <c r="C206" t="n">
-        <v>24.69412803649902</v>
+        <v>24.69412994384766</v>
       </c>
       <c r="D206" t="n">
         <v>15.8731164932251</v>
@@ -5791,10 +5791,10 @@
         <v>2.432731151580811</v>
       </c>
       <c r="F206" t="n">
-        <v>8.617196083068848</v>
+        <v>8.617197036743164</v>
       </c>
       <c r="G206" t="n">
-        <v>52.35831832885742</v>
+        <v>52.35831451416016</v>
       </c>
       <c r="H206" t="n">
         <v>-8.143244743347168</v>
@@ -5802,7 +5802,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.1076857224106789</v>
+        <v>0.1076857149600983</v>
       </c>
       <c r="B207" t="n">
         <v>0.7928006649017334</v>
@@ -5811,7 +5811,7 @@
         <v>21.76468849182129</v>
       </c>
       <c r="D207" t="n">
-        <v>13.42293453216553</v>
+        <v>13.42293357849121</v>
       </c>
       <c r="E207" t="n">
         <v>2.914615869522095</v>
@@ -5820,15 +5820,15 @@
         <v>13.1414623260498</v>
       </c>
       <c r="G207" t="n">
-        <v>54.70961761474609</v>
+        <v>54.70961380004883</v>
       </c>
       <c r="H207" t="n">
-        <v>-4.752289772033691</v>
+        <v>-4.75229024887085</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0.1469742357730865</v>
+        <v>0.1469742655754089</v>
       </c>
       <c r="B208" t="n">
         <v>0.8261861205101013</v>
@@ -5837,7 +5837,7 @@
         <v>18.69356155395508</v>
       </c>
       <c r="D208" t="n">
-        <v>10.34388446807861</v>
+        <v>10.3438835144043</v>
       </c>
       <c r="E208" t="n">
         <v>2.92203688621521</v>
@@ -5849,12 +5849,12 @@
         <v>55.22616195678711</v>
       </c>
       <c r="H208" t="n">
-        <v>-2.055549621582031</v>
+        <v>-2.055549383163452</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0.1881629824638367</v>
+        <v>0.1881630420684814</v>
       </c>
       <c r="B209" t="n">
         <v>0.8571828603744507</v>
@@ -5863,7 +5863,7 @@
         <v>15.61940097808838</v>
       </c>
       <c r="D209" t="n">
-        <v>7.067325115203857</v>
+        <v>7.067324161529541</v>
       </c>
       <c r="E209" t="n">
         <v>2.754967212677002</v>
@@ -5872,15 +5872,15 @@
         <v>21.07096099853516</v>
       </c>
       <c r="G209" t="n">
-        <v>53.9926643371582</v>
+        <v>53.99266052246094</v>
       </c>
       <c r="H209" t="n">
-        <v>0.2048963457345963</v>
+        <v>0.2048963159322739</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.2293924391269684</v>
+        <v>0.2293924987316132</v>
       </c>
       <c r="B210" t="n">
         <v>0.8846994042396545</v>
@@ -5918,7 +5918,7 @@
         <v>2.210823535919189</v>
       </c>
       <c r="E211" t="n">
-        <v>3.171652317047119</v>
+        <v>3.17165207862854</v>
       </c>
       <c r="F211" t="n">
         <v>26.76634407043457</v>
@@ -5927,7 +5927,7 @@
         <v>46.96974182128906</v>
       </c>
       <c r="H211" t="n">
-        <v>3.746608257293701</v>
+        <v>3.746608018875122</v>
       </c>
     </row>
     <row r="212">
@@ -5938,19 +5938,19 @@
         <v>0.926726758480072</v>
       </c>
       <c r="C212" t="n">
-        <v>7.427088260650635</v>
+        <v>7.427087306976318</v>
       </c>
       <c r="D212" t="n">
-        <v>0.8014646768569946</v>
+        <v>0.8014644980430603</v>
       </c>
       <c r="E212" t="n">
-        <v>3.840819120407104</v>
+        <v>3.840819358825684</v>
       </c>
       <c r="F212" t="n">
-        <v>28.62588310241699</v>
+        <v>28.62588500976562</v>
       </c>
       <c r="G212" t="n">
-        <v>41.46113586425781</v>
+        <v>41.46113204956055</v>
       </c>
       <c r="H212" t="n">
         <v>4.496410846710205</v>
@@ -5964,10 +5964,10 @@
         <v>0.9404487013816833</v>
       </c>
       <c r="C213" t="n">
-        <v>4.894728660583496</v>
+        <v>4.894728183746338</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.2763780355453491</v>
+        <v>-0.2763762772083282</v>
       </c>
       <c r="E213" t="n">
         <v>4.592483997344971</v>
@@ -5979,7 +5979,7 @@
         <v>34.75399780273438</v>
       </c>
       <c r="H213" t="n">
-        <v>4.10507345199585</v>
+        <v>4.105072975158691</v>
       </c>
     </row>
     <row r="214">
@@ -5990,16 +5990,16 @@
         <v>0.9491561055183411</v>
       </c>
       <c r="C214" t="n">
-        <v>2.356503248214722</v>
+        <v>2.356503009796143</v>
       </c>
       <c r="D214" t="n">
-        <v>-1.20487916469574</v>
+        <v>-1.204879283905029</v>
       </c>
       <c r="E214" t="n">
         <v>5.3277268409729</v>
       </c>
       <c r="F214" t="n">
-        <v>30.36335754394531</v>
+        <v>30.36335945129395</v>
       </c>
       <c r="G214" t="n">
         <v>27.0286808013916</v>
@@ -6016,13 +6016,13 @@
         <v>0.9532698392868042</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.1404249519109726</v>
+        <v>-0.1404252350330353</v>
       </c>
       <c r="D215" t="n">
-        <v>-1.95022714138031</v>
+        <v>-1.9502272605896</v>
       </c>
       <c r="E215" t="n">
-        <v>6.122318744659424</v>
+        <v>6.122319221496582</v>
       </c>
       <c r="F215" t="n">
         <v>30.44340896606445</v>
@@ -6031,7 +6031,7 @@
         <v>18.66259574890137</v>
       </c>
       <c r="H215" t="n">
-        <v>0.2759703397750854</v>
+        <v>0.275970458984375</v>
       </c>
     </row>
     <row r="216">
@@ -6042,22 +6042,22 @@
         <v>0.9538605809211731</v>
       </c>
       <c r="C216" t="n">
-        <v>-2.472937822341919</v>
+        <v>-2.472937107086182</v>
       </c>
       <c r="D216" t="n">
-        <v>-2.305814266204834</v>
+        <v>-2.305810451507568</v>
       </c>
       <c r="E216" t="n">
-        <v>7.148919582366943</v>
+        <v>7.148920059204102</v>
       </c>
       <c r="F216" t="n">
         <v>30.28093338012695</v>
       </c>
       <c r="G216" t="n">
-        <v>10.31049346923828</v>
+        <v>10.31049251556396</v>
       </c>
       <c r="H216" t="n">
-        <v>-1.903061628341675</v>
+        <v>-1.903061389923096</v>
       </c>
     </row>
     <row r="217">
@@ -6068,22 +6068,22 @@
         <v>0.9538605809211731</v>
       </c>
       <c r="C217" t="n">
-        <v>-4.500632286071777</v>
+        <v>-4.500633716583252</v>
       </c>
       <c r="D217" t="n">
-        <v>-2.01308012008667</v>
+        <v>-2.013082027435303</v>
       </c>
       <c r="E217" t="n">
-        <v>8.541281700134277</v>
+        <v>8.541282653808594</v>
       </c>
       <c r="F217" t="n">
         <v>30.15394401550293</v>
       </c>
       <c r="G217" t="n">
-        <v>2.915610790252686</v>
+        <v>2.915609121322632</v>
       </c>
       <c r="H217" t="n">
-        <v>-3.395564556121826</v>
+        <v>-3.395564794540405</v>
       </c>
     </row>
     <row r="218">
@@ -6094,22 +6094,22 @@
         <v>0.9538605809211731</v>
       </c>
       <c r="C218" t="n">
-        <v>-6.168215751647949</v>
+        <v>-6.168215274810791</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.9690755605697632</v>
+        <v>-0.9690757393836975</v>
       </c>
       <c r="E218" t="n">
         <v>10.24686908721924</v>
       </c>
       <c r="F218" t="n">
-        <v>30.29035186767578</v>
+        <v>30.29035377502441</v>
       </c>
       <c r="G218" t="n">
-        <v>-2.425781726837158</v>
+        <v>-2.425783395767212</v>
       </c>
       <c r="H218" t="n">
-        <v>-3.991297245025635</v>
+        <v>-3.991297006607056</v>
       </c>
     </row>
     <row r="219">
@@ -6120,10 +6120,10 @@
         <v>0.9538605809211731</v>
       </c>
       <c r="C219" t="n">
-        <v>-7.530976295471191</v>
+        <v>-7.530977725982666</v>
       </c>
       <c r="D219" t="n">
-        <v>0.7058588266372681</v>
+        <v>0.7058605551719666</v>
       </c>
       <c r="E219" t="n">
         <v>11.99321937561035</v>
@@ -6132,10 +6132,10 @@
         <v>30.77606201171875</v>
       </c>
       <c r="G219" t="n">
-        <v>-4.842243671417236</v>
+        <v>-4.842243194580078</v>
       </c>
       <c r="H219" t="n">
-        <v>-3.744932174682617</v>
+        <v>-3.744931936264038</v>
       </c>
     </row>
     <row r="220">
@@ -6149,7 +6149,7 @@
         <v>-8.682629585266113</v>
       </c>
       <c r="D220" t="n">
-        <v>2.814560413360596</v>
+        <v>2.814561367034912</v>
       </c>
       <c r="E220" t="n">
         <v>13.38725090026855</v>
@@ -6158,10 +6158,10 @@
         <v>31.53286170959473</v>
       </c>
       <c r="G220" t="n">
-        <v>-4.160192966461182</v>
+        <v>-4.160192489624023</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.045681953430176</v>
+        <v>-3.045682191848755</v>
       </c>
     </row>
     <row r="221">
@@ -6172,10 +6172,10 @@
         <v>0.9618998765945435</v>
       </c>
       <c r="C221" t="n">
-        <v>-9.620762825012207</v>
+        <v>-9.62076473236084</v>
       </c>
       <c r="D221" t="n">
-        <v>5.362066745758057</v>
+        <v>5.362067699432373</v>
       </c>
       <c r="E221" t="n">
         <v>14.10321140289307</v>
@@ -6184,10 +6184,10 @@
         <v>32.38537979125977</v>
       </c>
       <c r="G221" t="n">
-        <v>-1.087681293487549</v>
+        <v>-1.08768093585968</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.715541839599609</v>
+        <v>-2.71554160118103</v>
       </c>
     </row>
     <row r="222">
@@ -6195,13 +6195,13 @@
         <v>0.5679038763046265</v>
       </c>
       <c r="B222" t="n">
-        <v>0.9681907892227173</v>
+        <v>0.9681907296180725</v>
       </c>
       <c r="C222" t="n">
         <v>-10.18505001068115</v>
       </c>
       <c r="D222" t="n">
-        <v>8.628351211547852</v>
+        <v>8.628350257873535</v>
       </c>
       <c r="E222" t="n">
         <v>13.9066333770752</v>
@@ -6210,10 +6210,10 @@
         <v>33.16251373291016</v>
       </c>
       <c r="G222" t="n">
-        <v>3.114234447479248</v>
+        <v>3.114234685897827</v>
       </c>
       <c r="H222" t="n">
-        <v>-3.691694736480713</v>
+        <v>-3.691694974899292</v>
       </c>
     </row>
     <row r="223">
@@ -6233,10 +6233,10 @@
         <v>12.39472103118896</v>
       </c>
       <c r="F223" t="n">
-        <v>33.78034210205078</v>
+        <v>33.78033828735352</v>
       </c>
       <c r="G223" t="n">
-        <v>7.368970394134521</v>
+        <v>7.368969917297363</v>
       </c>
       <c r="H223" t="n">
         <v>-6.174063682556152</v>
@@ -6250,7 +6250,7 @@
         <v>0.9784844517707825</v>
       </c>
       <c r="C224" t="n">
-        <v>-9.296059608459473</v>
+        <v>-9.296061515808105</v>
       </c>
       <c r="D224" t="n">
         <v>18.09382438659668</v>
@@ -6262,7 +6262,7 @@
         <v>36.696044921875</v>
       </c>
       <c r="G224" t="n">
-        <v>11.1909761428833</v>
+        <v>11.19097518920898</v>
       </c>
       <c r="H224" t="n">
         <v>-6.304224014282227</v>
@@ -6273,10 +6273,10 @@
         <v>0.5842673182487488</v>
       </c>
       <c r="B225" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C225" t="n">
-        <v>-7.674901008605957</v>
+        <v>-7.674902439117432</v>
       </c>
       <c r="D225" t="n">
         <v>23.70100975036621</v>
@@ -6288,7 +6288,7 @@
         <v>36.92168807983398</v>
       </c>
       <c r="G225" t="n">
-        <v>14.83047771453857</v>
+        <v>14.83047676086426</v>
       </c>
       <c r="H225" t="n">
         <v>-8.207394599914551</v>
@@ -6299,16 +6299,16 @@
         <v>0.6003067493438721</v>
       </c>
       <c r="B226" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C226" t="n">
-        <v>-5.440899848937988</v>
+        <v>-5.44089937210083</v>
       </c>
       <c r="D226" t="n">
         <v>29.23537445068359</v>
       </c>
       <c r="E226" t="n">
-        <v>-6.969194412231445</v>
+        <v>-6.969193935394287</v>
       </c>
       <c r="F226" t="n">
         <v>36.69089508056641</v>
@@ -6325,10 +6325,10 @@
         <v>0.6224095225334167</v>
       </c>
       <c r="B227" t="n">
-        <v>5.749551201006398e-05</v>
+        <v>5.747634349972941e-05</v>
       </c>
       <c r="C227" t="n">
-        <v>-2.660975694656372</v>
+        <v>-2.660976886749268</v>
       </c>
       <c r="D227" t="n">
         <v>34.73098373413086</v>
@@ -6351,10 +6351,10 @@
         <v>0.6499136090278625</v>
       </c>
       <c r="B228" t="n">
-        <v>0.00958643015474081</v>
+        <v>0.009586411528289318</v>
       </c>
       <c r="C228" t="n">
-        <v>0.727039098739624</v>
+        <v>0.7270388007164001</v>
       </c>
       <c r="D228" t="n">
         <v>40.63057708740234</v>
@@ -6377,10 +6377,10 @@
         <v>0.6834339499473572</v>
       </c>
       <c r="B229" t="n">
-        <v>0.0272882953286171</v>
+        <v>0.02728827483952045</v>
       </c>
       <c r="C229" t="n">
-        <v>4.714947700500488</v>
+        <v>4.71494722366333</v>
       </c>
       <c r="D229" t="n">
         <v>47.07179260253906</v>
@@ -6389,13 +6389,13 @@
         <v>-14.53153228759766</v>
       </c>
       <c r="F229" t="n">
-        <v>31.97977638244629</v>
+        <v>31.97977828979492</v>
       </c>
       <c r="G229" t="n">
         <v>20.37187767028809</v>
       </c>
       <c r="H229" t="n">
-        <v>-2.77977180480957</v>
+        <v>-2.779771089553833</v>
       </c>
     </row>
     <row r="230">
@@ -6403,19 +6403,19 @@
         <v>0.7228895425796509</v>
       </c>
       <c r="B230" t="n">
-        <v>0.05262783914804459</v>
+        <v>0.05262782052159309</v>
       </c>
       <c r="C230" t="n">
         <v>9.05533504486084</v>
       </c>
       <c r="D230" t="n">
-        <v>53.2828369140625</v>
+        <v>53.28283309936523</v>
       </c>
       <c r="E230" t="n">
         <v>-10.12814044952393</v>
       </c>
       <c r="F230" t="n">
-        <v>29.21370697021484</v>
+        <v>29.21370887756348</v>
       </c>
       <c r="G230" t="n">
         <v>18.75815200805664</v>
@@ -6429,7 +6429,7 @@
         <v>0.7658325433731079</v>
       </c>
       <c r="B231" t="n">
-        <v>0.08349386602640152</v>
+        <v>0.08349384367465973</v>
       </c>
       <c r="C231" t="n">
         <v>13.32387351989746</v>
@@ -6441,13 +6441,13 @@
         <v>-5.716984272003174</v>
       </c>
       <c r="F231" t="n">
-        <v>26.18086242675781</v>
+        <v>26.18086433410645</v>
       </c>
       <c r="G231" t="n">
         <v>16.65291404724121</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.00533245736733079</v>
+        <v>-0.005332360975444317</v>
       </c>
     </row>
     <row r="232">
@@ -6455,13 +6455,13 @@
         <v>0.8080646395683289</v>
       </c>
       <c r="B232" t="n">
-        <v>0.1173367276787758</v>
+        <v>0.117336705327034</v>
       </c>
       <c r="C232" t="n">
         <v>17.14870452880859</v>
       </c>
       <c r="D232" t="n">
-        <v>60.73695373535156</v>
+        <v>60.7369499206543</v>
       </c>
       <c r="E232" t="n">
         <v>-2.068775653839111</v>
@@ -6473,7 +6473,7 @@
         <v>14.27495861053467</v>
       </c>
       <c r="H232" t="n">
-        <v>0.6683195829391479</v>
+        <v>0.6683197021484375</v>
       </c>
     </row>
     <row r="233">
@@ -6481,7 +6481,7 @@
         <v>0.8459067940711975</v>
       </c>
       <c r="B233" t="n">
-        <v>0.1521754264831543</v>
+        <v>0.1521753817796707</v>
       </c>
       <c r="C233" t="n">
         <v>20.35327529907227</v>
@@ -6490,7 +6490,7 @@
         <v>60.86723709106445</v>
       </c>
       <c r="E233" t="n">
-        <v>0.533854067325592</v>
+        <v>0.5338540077209473</v>
       </c>
       <c r="F233" t="n">
         <v>19.95163154602051</v>
@@ -6499,7 +6499,7 @@
         <v>11.73736763000488</v>
       </c>
       <c r="H233" t="n">
-        <v>0.9332634210586548</v>
+        <v>0.93326336145401</v>
       </c>
     </row>
     <row r="234">
@@ -6507,13 +6507,13 @@
         <v>0.8776121735572815</v>
       </c>
       <c r="B234" t="n">
-        <v>0.1868473887443542</v>
+        <v>0.1868474036455154</v>
       </c>
       <c r="C234" t="n">
         <v>22.93546867370605</v>
       </c>
       <c r="D234" t="n">
-        <v>58.57997131347656</v>
+        <v>58.5799674987793</v>
       </c>
       <c r="E234" t="n">
         <v>2.13553524017334</v>
@@ -6522,7 +6522,7 @@
         <v>16.92017936706543</v>
       </c>
       <c r="G234" t="n">
-        <v>9.248022079467773</v>
+        <v>9.248021125793457</v>
       </c>
       <c r="H234" t="n">
         <v>1.042618870735168</v>
@@ -6533,25 +6533,25 @@
         <v>0.9031599164009094</v>
       </c>
       <c r="B235" t="n">
-        <v>0.2206747531890869</v>
+        <v>0.2206747680902481</v>
       </c>
       <c r="C235" t="n">
-        <v>24.91757774353027</v>
+        <v>24.91757965087891</v>
       </c>
       <c r="D235" t="n">
-        <v>54.17562103271484</v>
+        <v>54.17561721801758</v>
       </c>
       <c r="E235" t="n">
-        <v>3.010587930679321</v>
+        <v>3.0105881690979</v>
       </c>
       <c r="F235" t="n">
         <v>14.00596809387207</v>
       </c>
       <c r="G235" t="n">
-        <v>7.093613147735596</v>
+        <v>7.093612670898438</v>
       </c>
       <c r="H235" t="n">
-        <v>1.315624713897705</v>
+        <v>1.315624594688416</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
         <v>0.2531938254833221</v>
       </c>
       <c r="C236" t="n">
-        <v>26.29769134521484</v>
+        <v>26.29769325256348</v>
       </c>
       <c r="D236" t="n">
-        <v>48.02933502197266</v>
+        <v>48.02933883666992</v>
       </c>
       <c r="E236" t="n">
         <v>3.411523580551147</v>
@@ -6574,7 +6574,7 @@
         <v>11.22652244567871</v>
       </c>
       <c r="G236" t="n">
-        <v>5.457214832305908</v>
+        <v>5.45721435546875</v>
       </c>
       <c r="H236" t="n">
         <v>1.95520806312561</v>
@@ -6597,10 +6597,10 @@
         <v>3.351086616516113</v>
       </c>
       <c r="F237" t="n">
-        <v>8.558293342590332</v>
+        <v>8.558294296264648</v>
       </c>
       <c r="G237" t="n">
-        <v>4.313275814056396</v>
+        <v>4.313276290893555</v>
       </c>
       <c r="H237" t="n">
         <v>2.946658611297607</v>
@@ -6623,10 +6623,10 @@
         <v>2.600748538970947</v>
       </c>
       <c r="F238" t="n">
-        <v>5.930118560791016</v>
+        <v>5.930117607116699</v>
       </c>
       <c r="G238" t="n">
-        <v>3.478049755096436</v>
+        <v>3.478049993515015</v>
       </c>
       <c r="H238" t="n">
         <v>4.125571250915527</v>
@@ -6634,16 +6634,16 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B239" t="n">
         <v>0.3433105647563934</v>
       </c>
       <c r="C239" t="n">
-        <v>27.1884937286377</v>
+        <v>27.18849563598633</v>
       </c>
       <c r="D239" t="n">
-        <v>24.06142616271973</v>
+        <v>24.06142425537109</v>
       </c>
       <c r="E239" t="n">
         <v>0.9494385719299316</v>
@@ -6652,15 +6652,15 @@
         <v>3.244021415710449</v>
       </c>
       <c r="G239" t="n">
-        <v>2.722131252288818</v>
+        <v>2.72213339805603</v>
       </c>
       <c r="H239" t="n">
-        <v>5.272953510284424</v>
+        <v>5.272953033447266</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B240" t="n">
         <v>0.3732841610908508</v>
@@ -6672,13 +6672,13 @@
         <v>16.09529304504395</v>
       </c>
       <c r="E240" t="n">
-        <v>-1.3554847240448</v>
+        <v>-1.355484843254089</v>
       </c>
       <c r="F240" t="n">
-        <v>0.4227895736694336</v>
+        <v>0.4227877259254456</v>
       </c>
       <c r="G240" t="n">
-        <v>1.878974437713623</v>
+        <v>1.878974795341492</v>
       </c>
       <c r="H240" t="n">
         <v>6.249489784240723</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B241" t="n">
-        <v>0.4047656953334808</v>
+        <v>0.4047657251358032</v>
       </c>
       <c r="C241" t="n">
         <v>26.39948081970215</v>
@@ -6704,7 +6704,7 @@
         <v>-2.540711402893066</v>
       </c>
       <c r="G241" t="n">
-        <v>0.9102359414100647</v>
+        <v>0.9102362394332886</v>
       </c>
       <c r="H241" t="n">
         <v>7.068041801452637</v>
@@ -6712,33 +6712,33 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B242" t="n">
         <v>0.437834769487381</v>
       </c>
       <c r="C242" t="n">
-        <v>26.32605743408203</v>
+        <v>26.32605934143066</v>
       </c>
       <c r="D242" t="n">
-        <v>3.313671588897705</v>
+        <v>3.313672542572021</v>
       </c>
       <c r="E242" t="n">
         <v>-3.967965602874756</v>
       </c>
       <c r="F242" t="n">
-        <v>-5.562165260314941</v>
+        <v>-5.562167167663574</v>
       </c>
       <c r="G242" t="n">
-        <v>-0.08888095617294312</v>
+        <v>-0.08888065814971924</v>
       </c>
       <c r="H242" t="n">
-        <v>7.768787384033203</v>
+        <v>7.768786907196045</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B243" t="n">
         <v>0.4715505540370941</v>
@@ -6747,16 +6747,16 @@
         <v>26.6735782623291</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.5154222249984741</v>
+        <v>-0.5154204964637756</v>
       </c>
       <c r="E243" t="n">
-        <v>-3.133389472961426</v>
+        <v>-3.133388996124268</v>
       </c>
       <c r="F243" t="n">
         <v>-8.497763633728027</v>
       </c>
       <c r="G243" t="n">
-        <v>-0.9346889853477478</v>
+        <v>-0.9346886873245239</v>
       </c>
       <c r="H243" t="n">
         <v>8.368043899536133</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B244" t="n">
         <v>0.50430828332901</v>
@@ -6773,16 +6773,16 @@
         <v>27.29908561706543</v>
       </c>
       <c r="D244" t="n">
-        <v>-2.156373500823975</v>
+        <v>-2.156371593475342</v>
       </c>
       <c r="E244" t="n">
-        <v>-1.871567249298096</v>
+        <v>-1.871567368507385</v>
       </c>
       <c r="F244" t="n">
         <v>-11.19789409637451</v>
       </c>
       <c r="G244" t="n">
-        <v>-1.421621799468994</v>
+        <v>-1.421621441841125</v>
       </c>
       <c r="H244" t="n">
         <v>8.86894702911377</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.9468367695808411</v>
+        <v>0.9468367099761963</v>
       </c>
       <c r="B245" t="n">
         <v>0.5344384908676147</v>
@@ -6799,16 +6799,16 @@
         <v>27.95905685424805</v>
       </c>
       <c r="D245" t="n">
-        <v>-1.769334197044373</v>
+        <v>-1.769334316253662</v>
       </c>
       <c r="E245" t="n">
-        <v>-1.282746076583862</v>
+        <v>-1.282746195793152</v>
       </c>
       <c r="F245" t="n">
         <v>-13.53405284881592</v>
       </c>
       <c r="G245" t="n">
-        <v>-1.350719928741455</v>
+        <v>-1.350719571113586</v>
       </c>
       <c r="H245" t="n">
         <v>9.24886417388916</v>
@@ -6825,19 +6825,19 @@
         <v>28.52372550964355</v>
       </c>
       <c r="D246" t="n">
-        <v>0.2792726755142212</v>
+        <v>0.2792725265026093</v>
       </c>
       <c r="E246" t="n">
-        <v>-1.847443580627441</v>
+        <v>-1.847443461418152</v>
       </c>
       <c r="F246" t="n">
-        <v>-15.39405727386475</v>
+        <v>-15.39406108856201</v>
       </c>
       <c r="G246" t="n">
-        <v>-0.5190243124961853</v>
+        <v>-0.5190259218215942</v>
       </c>
       <c r="H246" t="n">
-        <v>9.439069747924805</v>
+        <v>9.439068794250488</v>
       </c>
     </row>
     <row r="247">
@@ -6857,10 +6857,10 @@
         <v>-3.327019691467285</v>
       </c>
       <c r="F247" t="n">
-        <v>-16.66753005981445</v>
+        <v>-16.66752433776855</v>
       </c>
       <c r="G247" t="n">
-        <v>1.267756938934326</v>
+        <v>1.267757296562195</v>
       </c>
       <c r="H247" t="n">
         <v>9.326447486877441</v>
@@ -6874,27 +6874,27 @@
         <v>0.5954729914665222</v>
       </c>
       <c r="C248" t="n">
-        <v>29.39312362670898</v>
+        <v>29.39312553405762</v>
       </c>
       <c r="D248" t="n">
-        <v>7.358151912689209</v>
+        <v>7.358150959014893</v>
       </c>
       <c r="E248" t="n">
         <v>-5.071263313293457</v>
       </c>
       <c r="F248" t="n">
-        <v>-17.24724578857422</v>
+        <v>-17.24724006652832</v>
       </c>
       <c r="G248" t="n">
-        <v>4.134988307952881</v>
+        <v>4.134988784790039</v>
       </c>
       <c r="H248" t="n">
-        <v>8.633083343505859</v>
+        <v>8.633082389831543</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.9670507311820984</v>
+        <v>0.9670506715774536</v>
       </c>
       <c r="B249" t="n">
         <v>0.6019418835639954</v>
@@ -6909,13 +6909,13 @@
         <v>-6.292547225952148</v>
       </c>
       <c r="F249" t="n">
-        <v>-17.04879379272461</v>
+        <v>-17.04879188537598</v>
       </c>
       <c r="G249" t="n">
-        <v>8.071103096008301</v>
+        <v>8.071102142333984</v>
       </c>
       <c r="H249" t="n">
-        <v>6.696540355682373</v>
+        <v>6.696539878845215</v>
       </c>
     </row>
     <row r="250">
@@ -6926,16 +6926,16 @@
         <v>0.6034062504768372</v>
       </c>
       <c r="C250" t="n">
-        <v>31.66978645324707</v>
+        <v>31.6697883605957</v>
       </c>
       <c r="D250" t="n">
-        <v>9.356435775756836</v>
+        <v>9.35643482208252</v>
       </c>
       <c r="E250" t="n">
         <v>-3.321012496948242</v>
       </c>
       <c r="F250" t="n">
-        <v>-17.92427444458008</v>
+        <v>-17.92427253723145</v>
       </c>
       <c r="G250" t="n">
         <v>18.3529109954834</v>
@@ -6946,13 +6946,13 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B251" t="n">
         <v>0.601510226726532</v>
       </c>
       <c r="C251" t="n">
-        <v>31.87593269348145</v>
+        <v>31.87593460083008</v>
       </c>
       <c r="D251" t="n">
         <v>12.98259449005127</v>
@@ -6961,7 +6961,7 @@
         <v>-5.858014106750488</v>
       </c>
       <c r="F251" t="n">
-        <v>-16.00893402099609</v>
+        <v>-16.00893211364746</v>
       </c>
       <c r="G251" t="n">
         <v>23.39445686340332</v>
@@ -6972,13 +6972,13 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B252" t="n">
         <v>0.6168283820152283</v>
       </c>
       <c r="C252" t="n">
-        <v>31.93228721618652</v>
+        <v>31.93228912353516</v>
       </c>
       <c r="D252" t="n">
         <v>16.9053840637207</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B253" t="n">
         <v>0.638782799243927</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>0.001692271674983203</v>
+        <v>0.001692262594588101</v>
       </c>
       <c r="B254" t="n">
         <v>0.6668967008590698</v>
@@ -7036,10 +7036,10 @@
         <v>21.53725242614746</v>
       </c>
       <c r="E254" t="n">
-        <v>-1.859369993209839</v>
+        <v>-1.859370112419128</v>
       </c>
       <c r="F254" t="n">
-        <v>-5.58716869354248</v>
+        <v>-5.587170600891113</v>
       </c>
       <c r="G254" t="n">
         <v>43.60052871704102</v>
@@ -7050,33 +7050,33 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>0.0187742467969656</v>
+        <v>0.018774239346385</v>
       </c>
       <c r="B255" t="n">
         <v>0.7001776099205017</v>
       </c>
       <c r="C255" t="n">
-        <v>27.82575416564941</v>
+        <v>27.82575607299805</v>
       </c>
       <c r="D255" t="n">
         <v>20.2386646270752</v>
       </c>
       <c r="E255" t="n">
-        <v>0.1563393622636795</v>
+        <v>0.1563394367694855</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.9973249435424805</v>
+        <v>-0.9973248839378357</v>
       </c>
       <c r="G255" t="n">
-        <v>50.55424118041992</v>
+        <v>50.55423736572266</v>
       </c>
       <c r="H255" t="n">
-        <v>-10.69872283935547</v>
+        <v>-10.69872379302979</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>0.04923168569803238</v>
+        <v>0.04923167452216148</v>
       </c>
       <c r="B256" t="n">
         <v>0.7368854284286499</v>
@@ -7091,18 +7091,18 @@
         <v>1.591849207878113</v>
       </c>
       <c r="F256" t="n">
-        <v>3.693600654602051</v>
+        <v>3.693599700927734</v>
       </c>
       <c r="G256" t="n">
-        <v>55.79479598999023</v>
+        <v>55.79479217529297</v>
       </c>
       <c r="H256" t="n">
-        <v>-5.353937149047852</v>
+        <v>-5.35393762588501</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>0.08755681663751602</v>
+        <v>0.08755680918693542</v>
       </c>
       <c r="B257" t="n">
         <v>0.7744016051292419</v>
@@ -7114,13 +7114,13 @@
         <v>14.87725353240967</v>
       </c>
       <c r="E257" t="n">
-        <v>2.757955551147461</v>
+        <v>2.75795578956604</v>
       </c>
       <c r="F257" t="n">
         <v>8.169285774230957</v>
       </c>
       <c r="G257" t="n">
-        <v>58.60062026977539</v>
+        <v>58.60061645507812</v>
       </c>
       <c r="H257" t="n">
         <v>-0.8587443828582764</v>
@@ -7137,13 +7137,13 @@
         <v>18.97776985168457</v>
       </c>
       <c r="D258" t="n">
-        <v>13.11509895324707</v>
+        <v>13.11509799957275</v>
       </c>
       <c r="E258" t="n">
         <v>3.841182231903076</v>
       </c>
       <c r="F258" t="n">
-        <v>12.20143604278564</v>
+        <v>12.20143699645996</v>
       </c>
       <c r="G258" t="n">
         <v>58.77616882324219</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>0.1625504791736603</v>
+        <v>0.1625505089759827</v>
       </c>
       <c r="B259" t="n">
         <v>0.8424440026283264</v>
@@ -7169,18 +7169,18 @@
         <v>4.738645553588867</v>
       </c>
       <c r="F259" t="n">
-        <v>15.67985343933105</v>
+        <v>15.67985439300537</v>
       </c>
       <c r="G259" t="n">
-        <v>56.53317642211914</v>
+        <v>56.53317260742188</v>
       </c>
       <c r="H259" t="n">
-        <v>3.506303787231445</v>
+        <v>3.506303548812866</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>0.1950334310531616</v>
+        <v>0.195033460855484</v>
       </c>
       <c r="B260" t="n">
         <v>0.8702630400657654</v>
@@ -7201,12 +7201,12 @@
         <v>52.38088226318359</v>
       </c>
       <c r="H260" t="n">
-        <v>4.035130977630615</v>
+        <v>4.035130500793457</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>0.226650595664978</v>
+        <v>0.2266506254673004</v>
       </c>
       <c r="B261" t="n">
         <v>0.8933151364326477</v>
@@ -7238,7 +7238,7 @@
         <v>0.9112644791603088</v>
       </c>
       <c r="C262" t="n">
-        <v>8.672328948974609</v>
+        <v>8.672327995300293</v>
       </c>
       <c r="D262" t="n">
         <v>5.682637691497803</v>
@@ -7253,7 +7253,7 @@
         <v>40.2563362121582</v>
       </c>
       <c r="H262" t="n">
-        <v>4.190563678741455</v>
+        <v>4.190563201904297</v>
       </c>
     </row>
     <row r="263">
@@ -7264,10 +7264,10 @@
         <v>0.9237741827964783</v>
       </c>
       <c r="C263" t="n">
-        <v>5.844160079956055</v>
+        <v>5.844159603118896</v>
       </c>
       <c r="D263" t="n">
-        <v>3.595280170440674</v>
+        <v>3.59528112411499</v>
       </c>
       <c r="E263" t="n">
         <v>6.184038639068604</v>
@@ -7276,7 +7276,7 @@
         <v>23.26683044433594</v>
       </c>
       <c r="G263" t="n">
-        <v>32.77508163452148</v>
+        <v>32.77508544921875</v>
       </c>
       <c r="H263" t="n">
         <v>3.746766805648804</v>
@@ -7290,13 +7290,13 @@
         <v>0.9309407472610474</v>
       </c>
       <c r="C264" t="n">
-        <v>2.984752416610718</v>
+        <v>2.984753131866455</v>
       </c>
       <c r="D264" t="n">
-        <v>1.955737709999084</v>
+        <v>1.955738544464111</v>
       </c>
       <c r="E264" t="n">
-        <v>6.777115345001221</v>
+        <v>6.777114868164062</v>
       </c>
       <c r="F264" t="n">
         <v>23.59543800354004</v>
@@ -7316,10 +7316,10 @@
         <v>0.9335688352584839</v>
       </c>
       <c r="C265" t="n">
-        <v>0.1822297722101212</v>
+        <v>0.1822294890880585</v>
       </c>
       <c r="D265" t="n">
-        <v>0.8602758646011353</v>
+        <v>0.8602756857872009</v>
       </c>
       <c r="E265" t="n">
         <v>7.666539192199707</v>
@@ -7336,16 +7336,16 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>0.4032706916332245</v>
+        <v>0.4032706618309021</v>
       </c>
       <c r="B266" t="n">
         <v>0.9335688352584839</v>
       </c>
       <c r="C266" t="n">
-        <v>-2.444585084915161</v>
+        <v>-2.444584369659424</v>
       </c>
       <c r="D266" t="n">
-        <v>0.3979192972183228</v>
+        <v>0.3979191482067108</v>
       </c>
       <c r="E266" t="n">
         <v>8.844539642333984</v>
@@ -7357,7 +7357,7 @@
         <v>8.901814460754395</v>
       </c>
       <c r="H266" t="n">
-        <v>-0.0167310107499361</v>
+        <v>-0.01673091575503349</v>
       </c>
     </row>
     <row r="267">
@@ -7368,10 +7368,10 @@
         <v>0.9335688352584839</v>
       </c>
       <c r="C267" t="n">
-        <v>-4.782082557678223</v>
+        <v>-4.782082080841064</v>
       </c>
       <c r="D267" t="n">
-        <v>0.6112104654312134</v>
+        <v>0.6112102866172791</v>
       </c>
       <c r="E267" t="n">
         <v>10.2617712020874</v>
@@ -7380,7 +7380,7 @@
         <v>23.1527042388916</v>
       </c>
       <c r="G267" t="n">
-        <v>2.307258129119873</v>
+        <v>2.307258367538452</v>
       </c>
       <c r="H267" t="n">
         <v>-0.7932679653167725</v>
@@ -7394,10 +7394,10 @@
         <v>0.9335688352584839</v>
       </c>
       <c r="C268" t="n">
-        <v>-6.775271415710449</v>
+        <v>-6.775272846221924</v>
       </c>
       <c r="D268" t="n">
-        <v>1.412594437599182</v>
+        <v>1.412596225738525</v>
       </c>
       <c r="E268" t="n">
         <v>11.76390361785889</v>
@@ -7406,10 +7406,10 @@
         <v>23.20088577270508</v>
       </c>
       <c r="G268" t="n">
-        <v>-2.506289005279541</v>
+        <v>-2.506288766860962</v>
       </c>
       <c r="H268" t="n">
-        <v>-0.9441506862640381</v>
+        <v>-0.9441509246826172</v>
       </c>
     </row>
     <row r="269">
@@ -7420,19 +7420,19 @@
         <v>0.9335688352584839</v>
       </c>
       <c r="C269" t="n">
-        <v>-8.457688331604004</v>
+        <v>-8.457690238952637</v>
       </c>
       <c r="D269" t="n">
         <v>2.572008609771729</v>
       </c>
       <c r="E269" t="n">
-        <v>13.08506202697754</v>
+        <v>13.08506107330322</v>
       </c>
       <c r="F269" t="n">
         <v>23.49345016479492</v>
       </c>
       <c r="G269" t="n">
-        <v>-4.942520618438721</v>
+        <v>-4.942520141601562</v>
       </c>
       <c r="H269" t="n">
         <v>-0.5351746082305908</v>
@@ -7452,16 +7452,16 @@
         <v>3.869619846343994</v>
       </c>
       <c r="E270" t="n">
-        <v>13.97856330871582</v>
+        <v>13.97856426239014</v>
       </c>
       <c r="F270" t="n">
         <v>23.98394203186035</v>
       </c>
       <c r="G270" t="n">
-        <v>-4.872562885284424</v>
+        <v>-4.872562408447266</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1904264837503433</v>
+        <v>0.1904264539480209</v>
       </c>
     </row>
     <row r="271">
@@ -7478,13 +7478,13 @@
         <v>5.337913036346436</v>
       </c>
       <c r="E271" t="n">
-        <v>14.42393970489502</v>
+        <v>14.42394065856934</v>
       </c>
       <c r="F271" t="n">
         <v>24.58280944824219</v>
       </c>
       <c r="G271" t="n">
-        <v>-2.732729434967041</v>
+        <v>-2.732731103897095</v>
       </c>
       <c r="H271" t="n">
         <v>0.7501280307769775</v>
@@ -7498,7 +7498,7 @@
         <v>0.941465437412262</v>
       </c>
       <c r="C272" t="n">
-        <v>-12.15121746063232</v>
+        <v>-12.15121936798096</v>
       </c>
       <c r="D272" t="n">
         <v>7.319169521331787</v>
@@ -7510,10 +7510,10 @@
         <v>25.18586921691895</v>
       </c>
       <c r="G272" t="n">
-        <v>0.6705909371376038</v>
+        <v>0.6705931425094604</v>
       </c>
       <c r="H272" t="n">
-        <v>0.4851628541946411</v>
+        <v>0.4851627349853516</v>
       </c>
     </row>
     <row r="273">
@@ -7527,19 +7527,19 @@
         <v>-12.62585544586182</v>
       </c>
       <c r="D273" t="n">
-        <v>10.28879356384277</v>
+        <v>10.28879261016846</v>
       </c>
       <c r="E273" t="n">
-        <v>14.03341293334961</v>
+        <v>14.03341197967529</v>
       </c>
       <c r="F273" t="n">
-        <v>25.7301139831543</v>
+        <v>25.73011589050293</v>
       </c>
       <c r="G273" t="n">
-        <v>4.542938709259033</v>
+        <v>4.542939186096191</v>
       </c>
       <c r="H273" t="n">
-        <v>-1.09139609336853</v>
+        <v>-1.091395854949951</v>
       </c>
     </row>
     <row r="274">
@@ -7550,13 +7550,13 @@
         <v>0.9506411552429199</v>
       </c>
       <c r="C274" t="n">
-        <v>-12.36716938018799</v>
+        <v>-12.36716747283936</v>
       </c>
       <c r="D274" t="n">
         <v>14.52314949035645</v>
       </c>
       <c r="E274" t="n">
-        <v>12.35265064239502</v>
+        <v>12.35265159606934</v>
       </c>
       <c r="F274" t="n">
         <v>26.21180152893066</v>
@@ -7565,7 +7565,7 @@
         <v>8.490161895751953</v>
       </c>
       <c r="H274" t="n">
-        <v>-3.587117195129395</v>
+        <v>-3.587116956710815</v>
       </c>
     </row>
     <row r="275">
@@ -7573,7 +7573,7 @@
         <v>0.5698345899581909</v>
       </c>
       <c r="B275" t="n">
-        <v>0.9544935822486877</v>
+        <v>0.954493522644043</v>
       </c>
       <c r="C275" t="n">
         <v>-11.25396633148193</v>
@@ -7585,13 +7585,13 @@
         <v>8.268256187438965</v>
       </c>
       <c r="F275" t="n">
-        <v>31.90181159973145</v>
+        <v>31.90181350708008</v>
       </c>
       <c r="G275" t="n">
-        <v>9.901644706726074</v>
+        <v>9.901643753051758</v>
       </c>
       <c r="H275" t="n">
-        <v>-3.978342056274414</v>
+        <v>-3.978342294692993</v>
       </c>
     </row>
     <row r="276">
@@ -7599,10 +7599,10 @@
         <v>0.5807086825370789</v>
       </c>
       <c r="B276" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C276" t="n">
-        <v>-9.380328178405762</v>
+        <v>-9.380330085754395</v>
       </c>
       <c r="D276" t="n">
         <v>25.51922607421875</v>
@@ -7625,13 +7625,13 @@
         <v>0.5990108847618103</v>
       </c>
       <c r="B277" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C277" t="n">
-        <v>-7.038327217102051</v>
+        <v>-7.038326740264893</v>
       </c>
       <c r="D277" t="n">
-        <v>31.05094909667969</v>
+        <v>31.05095100402832</v>
       </c>
       <c r="E277" t="n">
         <v>-8.73859977722168</v>
@@ -7651,13 +7651,13 @@
         <v>0.6218882203102112</v>
       </c>
       <c r="B278" t="n">
-        <v>0.001636601402424276</v>
+        <v>0.00163664179854095</v>
       </c>
       <c r="C278" t="n">
-        <v>-4.389912605285645</v>
+        <v>-4.389912128448486</v>
       </c>
       <c r="D278" t="n">
-        <v>36.28329467773438</v>
+        <v>36.28329849243164</v>
       </c>
       <c r="E278" t="n">
         <v>-15.86844348907471</v>
@@ -7677,16 +7677,16 @@
         <v>0.6477586627006531</v>
       </c>
       <c r="B279" t="n">
-        <v>0.01145277079194784</v>
+        <v>0.01145275216549635</v>
       </c>
       <c r="C279" t="n">
-        <v>-1.338902711868286</v>
+        <v>-1.338901996612549</v>
       </c>
       <c r="D279" t="n">
-        <v>41.59658432006836</v>
+        <v>41.59658813476562</v>
       </c>
       <c r="E279" t="n">
-        <v>-17.52121162414551</v>
+        <v>-17.52120971679688</v>
       </c>
       <c r="F279" t="n">
         <v>29.37483024597168</v>
@@ -7695,7 +7695,7 @@
         <v>20.1416187286377</v>
       </c>
       <c r="H279" t="n">
-        <v>-2.611788272857666</v>
+        <v>-2.611788034439087</v>
       </c>
     </row>
     <row r="280">
@@ -7703,19 +7703,19 @@
         <v>0.6775618195533752</v>
       </c>
       <c r="B280" t="n">
-        <v>0.02913973480463028</v>
+        <v>0.02913971431553364</v>
       </c>
       <c r="C280" t="n">
-        <v>2.27518630027771</v>
+        <v>2.275186061859131</v>
       </c>
       <c r="D280" t="n">
         <v>47.29164505004883</v>
       </c>
       <c r="E280" t="n">
-        <v>-14.71038341522217</v>
+        <v>-14.7103853225708</v>
       </c>
       <c r="F280" t="n">
-        <v>27.15071296691895</v>
+        <v>27.15071487426758</v>
       </c>
       <c r="G280" t="n">
         <v>19.93883895874023</v>
@@ -7729,25 +7729,25 @@
         <v>0.7128652334213257</v>
       </c>
       <c r="B281" t="n">
-        <v>0.05478701740503311</v>
+        <v>0.05478699877858162</v>
       </c>
       <c r="C281" t="n">
-        <v>6.418020248413086</v>
+        <v>6.418019771575928</v>
       </c>
       <c r="D281" t="n">
-        <v>52.91487121582031</v>
+        <v>52.91486740112305</v>
       </c>
       <c r="E281" t="n">
         <v>-10.16516590118408</v>
       </c>
       <c r="F281" t="n">
-        <v>24.37943458557129</v>
+        <v>24.37943649291992</v>
       </c>
       <c r="G281" t="n">
         <v>18.67798805236816</v>
       </c>
       <c r="H281" t="n">
-        <v>1.242243528366089</v>
+        <v>1.242243409156799</v>
       </c>
     </row>
     <row r="282">
@@ -7755,10 +7755,10 @@
         <v>0.7533336281776428</v>
       </c>
       <c r="B282" t="n">
-        <v>0.08674380928277969</v>
+        <v>0.08674384653568268</v>
       </c>
       <c r="C282" t="n">
-        <v>10.78283500671387</v>
+        <v>10.78283405303955</v>
       </c>
       <c r="D282" t="n">
         <v>57.51180648803711</v>
@@ -7781,7 +7781,7 @@
         <v>0.7959703803062439</v>
       </c>
       <c r="B283" t="n">
-        <v>0.1224347129464149</v>
+        <v>0.1224347203969955</v>
       </c>
       <c r="C283" t="n">
         <v>14.93144512176514</v>
@@ -7790,7 +7790,7 @@
         <v>60.28279876708984</v>
       </c>
       <c r="E283" t="n">
-        <v>-1.677969932556152</v>
+        <v>-1.677970051765442</v>
       </c>
       <c r="F283" t="n">
         <v>18.06912994384766</v>
@@ -7799,7 +7799,7 @@
         <v>14.74167251586914</v>
       </c>
       <c r="H283" t="n">
-        <v>3.454236507415771</v>
+        <v>3.454236268997192</v>
       </c>
     </row>
     <row r="284">
@@ -7807,16 +7807,16 @@
         <v>0.8364951610565186</v>
       </c>
       <c r="B284" t="n">
-        <v>0.1595107316970825</v>
+        <v>0.1595107465982437</v>
       </c>
       <c r="C284" t="n">
         <v>18.52582550048828</v>
       </c>
       <c r="D284" t="n">
-        <v>60.81089019775391</v>
+        <v>60.81088638305664</v>
       </c>
       <c r="E284" t="n">
-        <v>1.485304713249207</v>
+        <v>1.485304594039917</v>
       </c>
       <c r="F284" t="n">
         <v>14.85952091217041</v>
@@ -7825,7 +7825,7 @@
         <v>12.25128364562988</v>
       </c>
       <c r="H284" t="n">
-        <v>3.900246858596802</v>
+        <v>3.900246620178223</v>
       </c>
     </row>
     <row r="285">
@@ -7833,25 +7833,25 @@
         <v>0.8716061115264893</v>
       </c>
       <c r="B285" t="n">
-        <v>0.1965221464633942</v>
+        <v>0.196522131562233</v>
       </c>
       <c r="C285" t="n">
         <v>21.44092559814453</v>
       </c>
       <c r="D285" t="n">
-        <v>59.03470611572266</v>
+        <v>59.03470230102539</v>
       </c>
       <c r="E285" t="n">
-        <v>3.687251329421997</v>
+        <v>3.687251091003418</v>
       </c>
       <c r="F285" t="n">
         <v>11.71191692352295</v>
       </c>
       <c r="G285" t="n">
-        <v>9.486035346984863</v>
+        <v>9.486034393310547</v>
       </c>
       <c r="H285" t="n">
-        <v>3.948690891265869</v>
+        <v>3.94869065284729</v>
       </c>
     </row>
     <row r="286">
@@ -7859,7 +7859,7 @@
         <v>0.9000815749168396</v>
       </c>
       <c r="B286" t="n">
-        <v>0.2328185439109802</v>
+        <v>0.232818529009819</v>
       </c>
       <c r="C286" t="n">
         <v>23.69665718078613</v>
@@ -7874,7 +7874,7 @@
         <v>8.657866477966309</v>
       </c>
       <c r="G286" t="n">
-        <v>6.796084880828857</v>
+        <v>6.796085357666016</v>
       </c>
       <c r="H286" t="n">
         <v>3.950659275054932</v>
@@ -7882,7 +7882,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>0.9221162796020508</v>
+        <v>0.922116219997406</v>
       </c>
       <c r="B287" t="n">
         <v>0.2680361270904541</v>
@@ -7900,15 +7900,15 @@
         <v>5.721749305725098</v>
       </c>
       <c r="G287" t="n">
-        <v>4.566328525543213</v>
+        <v>4.566328048706055</v>
       </c>
       <c r="H287" t="n">
-        <v>4.229508876800537</v>
+        <v>4.229508399963379</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>0.9382445216178894</v>
+        <v>0.9382444620132446</v>
       </c>
       <c r="B288" t="n">
         <v>0.3018938004970551</v>
@@ -7926,10 +7926,10 @@
         <v>2.917705535888672</v>
       </c>
       <c r="G288" t="n">
-        <v>2.998502254486084</v>
+        <v>2.998502492904663</v>
       </c>
       <c r="H288" t="n">
-        <v>4.915377616882324</v>
+        <v>4.915377140045166</v>
       </c>
     </row>
     <row r="289">
@@ -7946,13 +7946,13 @@
         <v>34.83768463134766</v>
       </c>
       <c r="E289" t="n">
-        <v>3.63729190826416</v>
+        <v>3.637292146682739</v>
       </c>
       <c r="F289" t="n">
-        <v>0.2260293811559677</v>
+        <v>0.2260294556617737</v>
       </c>
       <c r="G289" t="n">
-        <v>2.077577114105225</v>
+        <v>2.077577352523804</v>
       </c>
       <c r="H289" t="n">
         <v>6.00917387008667</v>
@@ -7960,13 +7960,13 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>0.9541657567024231</v>
+        <v>0.9541656970977783</v>
       </c>
       <c r="B290" t="n">
         <v>0.3652673661708832</v>
       </c>
       <c r="C290" t="n">
-        <v>27.07328224182129</v>
+        <v>27.07328033447266</v>
       </c>
       <c r="D290" t="n">
         <v>26.84604263305664</v>
@@ -7978,10 +7978,10 @@
         <v>-2.410183906555176</v>
       </c>
       <c r="G290" t="n">
-        <v>1.613036632537842</v>
+        <v>1.61303699016571</v>
       </c>
       <c r="H290" t="n">
-        <v>7.393527030944824</v>
+        <v>7.393526554107666</v>
       </c>
     </row>
     <row r="291">
@@ -7989,7 +7989,7 @@
         <v>0.9551000595092773</v>
       </c>
       <c r="B291" t="n">
-        <v>0.3956666886806488</v>
+        <v>0.3956667184829712</v>
       </c>
       <c r="C291" t="n">
         <v>26.84768867492676</v>
@@ -7998,16 +7998,16 @@
         <v>19.14215469360352</v>
       </c>
       <c r="E291" t="n">
-        <v>0.704343318939209</v>
+        <v>0.7043432593345642</v>
       </c>
       <c r="F291" t="n">
         <v>-5.05064868927002</v>
       </c>
       <c r="G291" t="n">
-        <v>1.343421459197998</v>
+        <v>1.343419909477234</v>
       </c>
       <c r="H291" t="n">
-        <v>8.84004020690918</v>
+        <v>8.840039253234863</v>
       </c>
     </row>
     <row r="292">
@@ -8024,16 +8024,16 @@
         <v>11.99857044219971</v>
       </c>
       <c r="E292" t="n">
-        <v>-0.1150013580918312</v>
+        <v>-0.1150012984871864</v>
       </c>
       <c r="F292" t="n">
         <v>-7.705105781555176</v>
       </c>
       <c r="G292" t="n">
-        <v>1.087508678436279</v>
+        <v>1.087509036064148</v>
       </c>
       <c r="H292" t="n">
-        <v>10.10252571105957</v>
+        <v>10.10252475738525</v>
       </c>
     </row>
     <row r="293">
@@ -8044,22 +8044,22 @@
         <v>0.4567247629165649</v>
       </c>
       <c r="C293" t="n">
-        <v>26.1852855682373</v>
+        <v>26.18528747558594</v>
       </c>
       <c r="D293" t="n">
         <v>5.646430492401123</v>
       </c>
       <c r="E293" t="n">
-        <v>-0.277513176202774</v>
+        <v>-0.2775132358074188</v>
       </c>
       <c r="F293" t="n">
         <v>-10.306077003479</v>
       </c>
       <c r="G293" t="n">
-        <v>0.8509936928749084</v>
+        <v>0.8509958982467651</v>
       </c>
       <c r="H293" t="n">
-        <v>11.04039096832275</v>
+        <v>11.04039001464844</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
         <v>0.486717700958252</v>
       </c>
       <c r="C294" t="n">
-        <v>26.11285591125488</v>
+        <v>26.11285781860352</v>
       </c>
       <c r="D294" t="n">
-        <v>0.6741682291030884</v>
+        <v>0.6741699576377869</v>
       </c>
       <c r="E294" t="n">
         <v>-0.1022987142205238</v>
@@ -8082,10 +8082,10 @@
         <v>-12.73534679412842</v>
       </c>
       <c r="G294" t="n">
-        <v>0.8164916634559631</v>
+        <v>0.8164900541305542</v>
       </c>
       <c r="H294" t="n">
-        <v>11.6800422668457</v>
+        <v>11.68004131317139</v>
       </c>
     </row>
     <row r="295">
@@ -8108,7 +8108,7 @@
         <v>-14.87861919403076</v>
       </c>
       <c r="G295" t="n">
-        <v>1.230447292327881</v>
+        <v>1.230445742607117</v>
       </c>
       <c r="H295" t="n">
         <v>12.15431213378906</v>
@@ -8128,16 +8128,16 @@
         <v>-2.43464994430542</v>
       </c>
       <c r="E296" t="n">
-        <v>0.9026802778244019</v>
+        <v>0.9026802182197571</v>
       </c>
       <c r="F296" t="n">
-        <v>-16.65167236328125</v>
+        <v>-16.65167045593262</v>
       </c>
       <c r="G296" t="n">
-        <v>2.305284023284912</v>
+        <v>2.305284261703491</v>
       </c>
       <c r="H296" t="n">
-        <v>12.54055881500244</v>
+        <v>12.54055786132812</v>
       </c>
     </row>
     <row r="297">
@@ -8151,19 +8151,19 @@
         <v>27.35630035400391</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.6113256216049194</v>
+        <v>-0.6113258004188538</v>
       </c>
       <c r="E297" t="n">
         <v>1.627059459686279</v>
       </c>
       <c r="F297" t="n">
-        <v>-18.02019500732422</v>
+        <v>-18.02019309997559</v>
       </c>
       <c r="G297" t="n">
-        <v>4.127233028411865</v>
+        <v>4.127233505249023</v>
       </c>
       <c r="H297" t="n">
-        <v>12.72392559051514</v>
+        <v>12.72392463684082</v>
       </c>
     </row>
     <row r="298">
@@ -8183,10 +8183,10 @@
         <v>1.70838725566864</v>
       </c>
       <c r="F298" t="n">
-        <v>-18.93483352661133</v>
+        <v>-18.9348316192627</v>
       </c>
       <c r="G298" t="n">
-        <v>6.708158016204834</v>
+        <v>6.708157539367676</v>
       </c>
       <c r="H298" t="n">
         <v>12.35292053222656</v>
@@ -8203,19 +8203,19 @@
         <v>27.7932243347168</v>
       </c>
       <c r="D299" t="n">
-        <v>5.071383953094482</v>
+        <v>5.071384906768799</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1474976092576981</v>
+        <v>0.1474975645542145</v>
       </c>
       <c r="F299" t="n">
-        <v>-19.30395126342773</v>
+        <v>-19.3039493560791</v>
       </c>
       <c r="G299" t="n">
         <v>9.998783111572266</v>
       </c>
       <c r="H299" t="n">
-        <v>10.83739471435547</v>
+        <v>10.83739376068115</v>
       </c>
     </row>
     <row r="300">
@@ -8232,16 +8232,16 @@
         <v>7.407253742218018</v>
       </c>
       <c r="E300" t="n">
-        <v>-2.949343204498291</v>
+        <v>-2.949342727661133</v>
       </c>
       <c r="F300" t="n">
-        <v>-19.0037956237793</v>
+        <v>-19.00379371643066</v>
       </c>
       <c r="G300" t="n">
         <v>13.90792655944824</v>
       </c>
       <c r="H300" t="n">
-        <v>7.416305065155029</v>
+        <v>7.416304588317871</v>
       </c>
     </row>
     <row r="301">
@@ -8255,36 +8255,36 @@
         <v>31.08670043945312</v>
       </c>
       <c r="D301" t="n">
-        <v>9.238125801086426</v>
+        <v>9.238124847412109</v>
       </c>
       <c r="E301" t="n">
         <v>-3.012162685394287</v>
       </c>
       <c r="F301" t="n">
-        <v>-17.85517883300781</v>
+        <v>-17.85517692565918</v>
       </c>
       <c r="G301" t="n">
         <v>16.28764343261719</v>
       </c>
       <c r="H301" t="n">
-        <v>-0.6944398880004883</v>
+        <v>-0.6944396495819092</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B302" t="n">
         <v>0.600782036781311</v>
       </c>
       <c r="C302" t="n">
-        <v>31.59165382385254</v>
+        <v>31.59165573120117</v>
       </c>
       <c r="D302" t="n">
         <v>13.06134128570557</v>
       </c>
       <c r="E302" t="n">
-        <v>-5.081531524658203</v>
+        <v>-5.081531047821045</v>
       </c>
       <c r="F302" t="n">
         <v>-15.53035640716553</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B303" t="n">
         <v>0.6182987093925476</v>
@@ -8316,7 +8316,7 @@
         <v>-12.30511379241943</v>
       </c>
       <c r="G303" t="n">
-        <v>27.8695182800293</v>
+        <v>27.86951637268066</v>
       </c>
       <c r="H303" t="n">
         <v>-15.69688892364502</v>
@@ -8324,19 +8324,19 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B304" t="n">
         <v>0.6425997018814087</v>
       </c>
       <c r="C304" t="n">
-        <v>31.55014991760254</v>
+        <v>31.55015182495117</v>
       </c>
       <c r="D304" t="n">
         <v>19.40524101257324</v>
       </c>
       <c r="E304" t="n">
-        <v>-4.682677745819092</v>
+        <v>-4.682677268981934</v>
       </c>
       <c r="F304" t="n">
         <v>-8.382142066955566</v>
@@ -8345,12 +8345,12 @@
         <v>34.65926361083984</v>
       </c>
       <c r="H304" t="n">
-        <v>-18.74748992919922</v>
+        <v>-18.74749183654785</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B305" t="n">
         <v>0.672157883644104</v>
@@ -8365,18 +8365,18 @@
         <v>-3.121367454528809</v>
       </c>
       <c r="F305" t="n">
-        <v>-3.973158836364746</v>
+        <v>-3.973160743713379</v>
       </c>
       <c r="G305" t="n">
         <v>41.58562469482422</v>
       </c>
       <c r="H305" t="n">
-        <v>-17.43003082275391</v>
+        <v>-17.43003273010254</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>0.009389794431626797</v>
+        <v>0.009389785118401051</v>
       </c>
       <c r="B306" t="n">
         <v>0.7053779363632202</v>
@@ -8388,21 +8388,21 @@
         <v>18.78349304199219</v>
       </c>
       <c r="E306" t="n">
-        <v>-1.64630651473999</v>
+        <v>-1.646306872367859</v>
       </c>
       <c r="F306" t="n">
-        <v>0.7387876510620117</v>
+        <v>0.7387877106666565</v>
       </c>
       <c r="G306" t="n">
         <v>47.93990707397461</v>
       </c>
       <c r="H306" t="n">
-        <v>-13.67917156219482</v>
+        <v>-13.67917251586914</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0.03655103594064713</v>
+        <v>0.03655102476477623</v>
       </c>
       <c r="B307" t="n">
         <v>0.7408807277679443</v>
@@ -8414,13 +8414,13 @@
         <v>16.41655158996582</v>
       </c>
       <c r="E307" t="n">
-        <v>-0.386653333902359</v>
+        <v>-0.3866532742977142</v>
       </c>
       <c r="F307" t="n">
         <v>5.578110694885254</v>
       </c>
       <c r="G307" t="n">
-        <v>53.00543594360352</v>
+        <v>53.00543212890625</v>
       </c>
       <c r="H307" t="n">
         <v>-9.418597221374512</v>
@@ -8428,7 +8428,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>0.07076839357614517</v>
+        <v>0.07076838612556458</v>
       </c>
       <c r="B308" t="n">
         <v>0.777343213558197</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>0.1071420982480049</v>
+        <v>0.1071420907974243</v>
       </c>
       <c r="B309" t="n">
         <v>0.8133320212364197</v>
@@ -8472,10 +8472,10 @@
         <v>14.86788082122803</v>
       </c>
       <c r="G309" t="n">
-        <v>57.64303588867188</v>
+        <v>57.64303207397461</v>
       </c>
       <c r="H309" t="n">
-        <v>-2.741374492645264</v>
+        <v>-2.741374254226685</v>
       </c>
     </row>
     <row r="310">
@@ -8489,16 +8489,16 @@
         <v>17.87735557556152</v>
       </c>
       <c r="D310" t="n">
-        <v>10.45798683166504</v>
+        <v>10.45798587799072</v>
       </c>
       <c r="E310" t="n">
-        <v>2.646105051040649</v>
+        <v>2.646105289459229</v>
       </c>
       <c r="F310" t="n">
         <v>18.93386268615723</v>
       </c>
       <c r="G310" t="n">
-        <v>57.0181770324707</v>
+        <v>57.01817321777344</v>
       </c>
       <c r="H310" t="n">
         <v>-0.4954097270965576</v>
@@ -8515,7 +8515,7 @@
         <v>15.22545909881592</v>
       </c>
       <c r="D311" t="n">
-        <v>8.244767189025879</v>
+        <v>8.244766235351562</v>
       </c>
       <c r="E311" t="n">
         <v>2.945981502532959</v>
@@ -8524,7 +8524,7 @@
         <v>22.4028148651123</v>
       </c>
       <c r="G311" t="n">
-        <v>54.56760406494141</v>
+        <v>54.56760025024414</v>
       </c>
       <c r="H311" t="n">
         <v>1.353364944458008</v>
@@ -8538,13 +8538,13 @@
         <v>0.9041112065315247</v>
       </c>
       <c r="C312" t="n">
-        <v>12.5055456161499</v>
+        <v>12.50554466247559</v>
       </c>
       <c r="D312" t="n">
         <v>5.696783542633057</v>
       </c>
       <c r="E312" t="n">
-        <v>2.958673477172852</v>
+        <v>2.958673238754272</v>
       </c>
       <c r="F312" t="n">
         <v>25.16475868225098</v>
@@ -8558,7 +8558,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>0.2509785592556</v>
+        <v>0.2509785294532776</v>
       </c>
       <c r="B313" t="n">
         <v>0.924921452999115</v>
@@ -8573,7 +8573,7 @@
         <v>3.033843278884888</v>
       </c>
       <c r="F313" t="n">
-        <v>27.15337371826172</v>
+        <v>27.15337562561035</v>
       </c>
       <c r="G313" t="n">
         <v>44.88462829589844</v>
@@ -8587,16 +8587,16 @@
         <v>0.2880197465419769</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9399049878120422</v>
+        <v>0.9399049282073975</v>
       </c>
       <c r="C314" t="n">
-        <v>7.074122428894043</v>
+        <v>7.074121952056885</v>
       </c>
       <c r="D314" t="n">
-        <v>1.315016388893127</v>
+        <v>1.315016269683838</v>
       </c>
       <c r="E314" t="n">
-        <v>3.395411729812622</v>
+        <v>3.395411968231201</v>
       </c>
       <c r="F314" t="n">
         <v>28.35718727111816</v>
@@ -8616,19 +8616,19 @@
         <v>0.9489752054214478</v>
       </c>
       <c r="C315" t="n">
-        <v>4.494717597961426</v>
+        <v>4.494717121124268</v>
       </c>
       <c r="D315" t="n">
-        <v>0.06683599203824997</v>
+        <v>0.06683583557605743</v>
       </c>
       <c r="E315" t="n">
-        <v>4.07505464553833</v>
+        <v>4.075055122375488</v>
       </c>
       <c r="F315" t="n">
         <v>28.83552742004395</v>
       </c>
       <c r="G315" t="n">
-        <v>29.94781303405762</v>
+        <v>29.94781112670898</v>
       </c>
       <c r="H315" t="n">
         <v>2.958987712860107</v>
@@ -8639,16 +8639,16 @@
         <v>0.3591820001602173</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C316" t="n">
-        <v>2.043290853500366</v>
+        <v>2.043290615081787</v>
       </c>
       <c r="D316" t="n">
-        <v>-0.5185369253158569</v>
+        <v>-0.5185371041297913</v>
       </c>
       <c r="E316" t="n">
-        <v>5.040205001831055</v>
+        <v>5.040204524993896</v>
       </c>
       <c r="F316" t="n">
         <v>28.72806739807129</v>
@@ -8665,25 +8665,25 @@
         <v>0.3922938108444214</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.2908270061016083</v>
+        <v>-0.2908263504505157</v>
       </c>
       <c r="D317" t="n">
-        <v>-0.5851091146469116</v>
+        <v>-0.5851092934608459</v>
       </c>
       <c r="E317" t="n">
-        <v>6.278819561004639</v>
+        <v>6.27881908416748</v>
       </c>
       <c r="F317" t="n">
-        <v>28.26858139038086</v>
+        <v>28.26858329772949</v>
       </c>
       <c r="G317" t="n">
-        <v>12.59984397888184</v>
+        <v>12.59984302520752</v>
       </c>
       <c r="H317" t="n">
-        <v>0.09127606451511383</v>
+        <v>0.09127604216337204</v>
       </c>
     </row>
     <row r="318">
@@ -8691,25 +8691,25 @@
         <v>0.4238210916519165</v>
       </c>
       <c r="B318" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C318" t="n">
-        <v>-2.513736009597778</v>
+        <v>-2.513737201690674</v>
       </c>
       <c r="D318" t="n">
-        <v>-0.2890008687973022</v>
+        <v>-0.2890010178089142</v>
       </c>
       <c r="E318" t="n">
-        <v>7.767562389373779</v>
+        <v>7.767562866210938</v>
       </c>
       <c r="F318" t="n">
-        <v>27.77482032775879</v>
+        <v>27.77482223510742</v>
       </c>
       <c r="G318" t="n">
-        <v>4.697786808013916</v>
+        <v>4.697787284851074</v>
       </c>
       <c r="H318" t="n">
-        <v>-1.157662391662598</v>
+        <v>-1.157662153244019</v>
       </c>
     </row>
     <row r="319">
@@ -8717,13 +8717,13 @@
         <v>0.453846275806427</v>
       </c>
       <c r="B319" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C319" t="n">
-        <v>-4.596842765808105</v>
+        <v>-4.596842288970947</v>
       </c>
       <c r="D319" t="n">
-        <v>0.2924333810806274</v>
+        <v>0.2924351394176483</v>
       </c>
       <c r="E319" t="n">
         <v>9.412167549133301</v>
@@ -8732,10 +8732,10 @@
         <v>27.5660514831543</v>
       </c>
       <c r="G319" t="n">
-        <v>-1.4242844581604</v>
+        <v>-1.424286007881165</v>
       </c>
       <c r="H319" t="n">
-        <v>-2.020573139190674</v>
+        <v>-2.020572900772095</v>
       </c>
     </row>
     <row r="320">
@@ -8743,25 +8743,25 @@
         <v>0.481983095407486</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C320" t="n">
-        <v>-6.494780540466309</v>
+        <v>-6.49478006362915</v>
       </c>
       <c r="D320" t="n">
-        <v>1.158592820167542</v>
+        <v>1.158592700958252</v>
       </c>
       <c r="E320" t="n">
-        <v>11.05802440643311</v>
+        <v>11.05802536010742</v>
       </c>
       <c r="F320" t="n">
         <v>27.82413673400879</v>
       </c>
       <c r="G320" t="n">
-        <v>-4.860735416412354</v>
+        <v>-4.860734939575195</v>
       </c>
       <c r="H320" t="n">
-        <v>-2.45328950881958</v>
+        <v>-2.453289747238159</v>
       </c>
     </row>
     <row r="321">
@@ -8769,7 +8769,7 @@
         <v>0.5076188445091248</v>
       </c>
       <c r="B321" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C321" t="n">
         <v>-8.176962852478027</v>
@@ -8781,13 +8781,13 @@
         <v>12.48443603515625</v>
       </c>
       <c r="F321" t="n">
-        <v>28.50441551208496</v>
+        <v>28.50441741943359</v>
       </c>
       <c r="G321" t="n">
-        <v>-5.260975360870361</v>
+        <v>-5.260976791381836</v>
       </c>
       <c r="H321" t="n">
-        <v>-2.448488712310791</v>
+        <v>-2.448487997055054</v>
       </c>
     </row>
     <row r="322">
@@ -8795,13 +8795,13 @@
         <v>0.5303403735160828</v>
       </c>
       <c r="B322" t="n">
-        <v>0.9525793194770813</v>
+        <v>0.9525792598724365</v>
       </c>
       <c r="C322" t="n">
         <v>-9.616084098815918</v>
       </c>
       <c r="D322" t="n">
-        <v>3.887897968292236</v>
+        <v>3.88789701461792</v>
       </c>
       <c r="E322" t="n">
         <v>13.44190311431885</v>
@@ -8810,10 +8810,10 @@
         <v>29.38434791564941</v>
       </c>
       <c r="G322" t="n">
-        <v>-3.072067737579346</v>
+        <v>-3.072067499160767</v>
       </c>
       <c r="H322" t="n">
-        <v>-2.232761859893799</v>
+        <v>-2.23276162147522</v>
       </c>
     </row>
     <row r="323">
@@ -8821,10 +8821,10 @@
         <v>0.5497787594795227</v>
       </c>
       <c r="B323" t="n">
-        <v>0.9567145705223083</v>
+        <v>0.9567145109176636</v>
       </c>
       <c r="C323" t="n">
-        <v>-10.72533893585205</v>
+        <v>-10.72534084320068</v>
       </c>
       <c r="D323" t="n">
         <v>5.991917133331299</v>
@@ -8833,13 +8833,13 @@
         <v>13.76377487182617</v>
       </c>
       <c r="F323" t="n">
-        <v>30.20112609863281</v>
+        <v>30.20112800598145</v>
       </c>
       <c r="G323" t="n">
-        <v>0.6637492775917053</v>
+        <v>0.6637495756149292</v>
       </c>
       <c r="H323" t="n">
-        <v>-2.4004225730896</v>
+        <v>-2.400422334671021</v>
       </c>
     </row>
     <row r="324">
@@ -8850,22 +8850,22 @@
         <v>0.9628686308860779</v>
       </c>
       <c r="C324" t="n">
-        <v>-11.32160472869873</v>
+        <v>-11.32160663604736</v>
       </c>
       <c r="D324" t="n">
-        <v>8.960597991943359</v>
+        <v>8.960597038269043</v>
       </c>
       <c r="E324" t="n">
-        <v>13.32777309417725</v>
+        <v>13.32777214050293</v>
       </c>
       <c r="F324" t="n">
-        <v>30.79345321655273</v>
+        <v>30.79345512390137</v>
       </c>
       <c r="G324" t="n">
-        <v>4.755143642425537</v>
+        <v>4.755143165588379</v>
       </c>
       <c r="H324" t="n">
-        <v>-3.626701354980469</v>
+        <v>-3.62670111656189</v>
       </c>
     </row>
     <row r="325">
@@ -8882,16 +8882,16 @@
         <v>13.06296539306641</v>
       </c>
       <c r="E325" t="n">
-        <v>11.76444721221924</v>
+        <v>11.76444816589355</v>
       </c>
       <c r="F325" t="n">
         <v>31.16432571411133</v>
       </c>
       <c r="G325" t="n">
-        <v>8.507850646972656</v>
+        <v>8.50784969329834</v>
       </c>
       <c r="H325" t="n">
-        <v>-5.855995178222656</v>
+        <v>-5.855995655059814</v>
       </c>
     </row>
     <row r="326">
@@ -8908,16 +8908,16 @@
         <v>18.18915748596191</v>
       </c>
       <c r="E326" t="n">
-        <v>8.210343360900879</v>
+        <v>8.210342407226562</v>
       </c>
       <c r="F326" t="n">
         <v>35.12921905517578</v>
       </c>
       <c r="G326" t="n">
-        <v>9.886086463928223</v>
+        <v>9.886085510253906</v>
       </c>
       <c r="H326" t="n">
-        <v>-2.825040340423584</v>
+        <v>-2.825040578842163</v>
       </c>
     </row>
     <row r="327">
@@ -8925,10 +8925,10 @@
         <v>0.5841001272201538</v>
       </c>
       <c r="B327" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C327" t="n">
-        <v>-8.46353816986084</v>
+        <v>-8.463540077209473</v>
       </c>
       <c r="D327" t="n">
         <v>23.76591110229492</v>
@@ -8943,7 +8943,7 @@
         <v>12.92237186431885</v>
       </c>
       <c r="H327" t="n">
-        <v>-5.510586261749268</v>
+        <v>-5.510586738586426</v>
       </c>
     </row>
     <row r="328">
@@ -8951,19 +8951,19 @@
         <v>0.601605236530304</v>
       </c>
       <c r="B328" t="n">
-        <v>0.001552022411487997</v>
+        <v>0.001552003202959895</v>
       </c>
       <c r="C328" t="n">
-        <v>-6.209860801696777</v>
+        <v>-6.209860324859619</v>
       </c>
       <c r="D328" t="n">
-        <v>29.22015762329102</v>
+        <v>29.22015953063965</v>
       </c>
       <c r="E328" t="n">
-        <v>-7.456207752227783</v>
+        <v>-7.456206798553467</v>
       </c>
       <c r="F328" t="n">
-        <v>34.66277694702148</v>
+        <v>34.66277313232422</v>
       </c>
       <c r="G328" t="n">
         <v>16.15936851501465</v>
@@ -8977,10 +8977,10 @@
         <v>0.6243067979812622</v>
       </c>
       <c r="B329" t="n">
-        <v>0.005020714830607176</v>
+        <v>0.005020695738494396</v>
       </c>
       <c r="C329" t="n">
-        <v>-3.597981691360474</v>
+        <v>-3.597980976104736</v>
       </c>
       <c r="D329" t="n">
         <v>34.4768180847168</v>
@@ -8992,7 +8992,7 @@
         <v>33.97869873046875</v>
       </c>
       <c r="G329" t="n">
-        <v>19.26612091064453</v>
+        <v>19.26612281799316</v>
       </c>
       <c r="H329" t="n">
         <v>-5.942198276519775</v>
@@ -9003,10 +9003,10 @@
         <v>0.6506165862083435</v>
       </c>
       <c r="B330" t="n">
-        <v>0.01238391455262899</v>
+        <v>0.01238395553082228</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.597454309463501</v>
+        <v>-0.597452700138092</v>
       </c>
       <c r="D330" t="n">
         <v>39.9274787902832</v>
@@ -9029,10 +9029,10 @@
         <v>0.680841326713562</v>
       </c>
       <c r="B331" t="n">
-        <v>0.02671311050653458</v>
+        <v>0.02671314962208271</v>
       </c>
       <c r="C331" t="n">
-        <v>2.85665488243103</v>
+        <v>2.856654644012451</v>
       </c>
       <c r="D331" t="n">
         <v>45.81814956665039</v>
@@ -9041,13 +9041,13 @@
         <v>-15.93201923370361</v>
       </c>
       <c r="F331" t="n">
-        <v>30.52179908752441</v>
+        <v>30.52180099487305</v>
       </c>
       <c r="G331" t="n">
-        <v>21.61802291870117</v>
+        <v>21.61802101135254</v>
       </c>
       <c r="H331" t="n">
-        <v>-1.96739387512207</v>
+        <v>-1.967394113540649</v>
       </c>
     </row>
     <row r="332">
@@ -9055,10 +9055,10 @@
         <v>0.7156350016593933</v>
       </c>
       <c r="B332" t="n">
-        <v>0.04959318786859512</v>
+        <v>0.04959316924214363</v>
       </c>
       <c r="C332" t="n">
-        <v>6.671505928039551</v>
+        <v>6.671505451202393</v>
       </c>
       <c r="D332" t="n">
         <v>51.62485885620117</v>
@@ -9073,7 +9073,7 @@
         <v>20.3947639465332</v>
       </c>
       <c r="H332" t="n">
-        <v>-0.207306370139122</v>
+        <v>-0.2073061615228653</v>
       </c>
     </row>
     <row r="333">
@@ -9081,7 +9081,7 @@
         <v>0.7540625333786011</v>
       </c>
       <c r="B333" t="n">
-        <v>0.07986346632242203</v>
+        <v>0.07986350357532501</v>
       </c>
       <c r="C333" t="n">
         <v>10.58195209503174</v>
@@ -9093,13 +9093,13 @@
         <v>-6.182998657226562</v>
       </c>
       <c r="F333" t="n">
-        <v>24.4766845703125</v>
+        <v>24.47668647766113</v>
       </c>
       <c r="G333" t="n">
         <v>18.20417785644531</v>
       </c>
       <c r="H333" t="n">
-        <v>0.9674419164657593</v>
+        <v>0.9674418568611145</v>
       </c>
     </row>
     <row r="334">
@@ -9107,13 +9107,13 @@
         <v>0.7934529781341553</v>
       </c>
       <c r="B334" t="n">
-        <v>0.1146613135933876</v>
+        <v>0.1146613210439682</v>
       </c>
       <c r="C334" t="n">
         <v>14.29731559753418</v>
       </c>
       <c r="D334" t="n">
-        <v>59.27574920654297</v>
+        <v>59.2757453918457</v>
       </c>
       <c r="E334" t="n">
         <v>-2.070919752120972</v>
@@ -9122,10 +9122,10 @@
         <v>21.09543228149414</v>
       </c>
       <c r="G334" t="n">
-        <v>15.60926055908203</v>
+        <v>15.60925960540771</v>
       </c>
       <c r="H334" t="n">
-        <v>1.598337531089783</v>
+        <v>1.598337650299072</v>
       </c>
     </row>
     <row r="335">
@@ -9133,7 +9133,7 @@
         <v>0.8308783173561096</v>
       </c>
       <c r="B335" t="n">
-        <v>0.151056319475174</v>
+        <v>0.1510563045740128</v>
       </c>
       <c r="C335" t="n">
         <v>17.62735366821289</v>
@@ -9159,19 +9159,19 @@
         <v>0.8644222021102905</v>
       </c>
       <c r="B336" t="n">
-        <v>0.186930239200592</v>
+        <v>0.1869302242994308</v>
       </c>
       <c r="C336" t="n">
         <v>20.49263000488281</v>
       </c>
       <c r="D336" t="n">
-        <v>58.6508903503418</v>
+        <v>58.65088653564453</v>
       </c>
       <c r="E336" t="n">
         <v>3.050923585891724</v>
       </c>
       <c r="F336" t="n">
-        <v>14.59097671508789</v>
+        <v>14.59097766876221</v>
       </c>
       <c r="G336" t="n">
         <v>10.36567115783691</v>
@@ -9185,22 +9185,22 @@
         <v>0.8932844996452332</v>
       </c>
       <c r="B337" t="n">
-        <v>0.2210687100887299</v>
+        <v>0.2210686951875687</v>
       </c>
       <c r="C337" t="n">
         <v>22.85014343261719</v>
       </c>
       <c r="D337" t="n">
-        <v>55.17966079711914</v>
+        <v>55.17965698242188</v>
       </c>
       <c r="E337" t="n">
         <v>4.08879566192627</v>
       </c>
       <c r="F337" t="n">
-        <v>11.62411975860596</v>
+        <v>11.62412071228027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.174694061279297</v>
+        <v>8.174695014953613</v>
       </c>
       <c r="H337" t="n">
         <v>2.490543603897095</v>
@@ -9223,13 +9223,13 @@
         <v>4.264204978942871</v>
       </c>
       <c r="F338" t="n">
-        <v>8.840458869934082</v>
+        <v>8.840459823608398</v>
       </c>
       <c r="G338" t="n">
-        <v>6.516834735870361</v>
+        <v>6.516834259033203</v>
       </c>
       <c r="H338" t="n">
-        <v>3.392050743103027</v>
+        <v>3.392050504684448</v>
       </c>
     </row>
     <row r="339">
@@ -9249,10 +9249,10 @@
         <v>3.666229009628296</v>
       </c>
       <c r="F339" t="n">
-        <v>6.159235000610352</v>
+        <v>6.159235954284668</v>
       </c>
       <c r="G339" t="n">
-        <v>5.366410732269287</v>
+        <v>5.366410255432129</v>
       </c>
       <c r="H339" t="n">
         <v>4.711570739746094</v>
@@ -9269,7 +9269,7 @@
         <v>26.42049789428711</v>
       </c>
       <c r="D340" t="n">
-        <v>34.93935012817383</v>
+        <v>34.93934631347656</v>
       </c>
       <c r="E340" t="n">
         <v>2.283150911331177</v>
@@ -9278,10 +9278,10 @@
         <v>3.46970272064209</v>
       </c>
       <c r="G340" t="n">
-        <v>4.548820018768311</v>
+        <v>4.548820495605469</v>
       </c>
       <c r="H340" t="n">
-        <v>6.238395214080811</v>
+        <v>6.238394737243652</v>
       </c>
     </row>
     <row r="341">
@@ -9301,10 +9301,10 @@
         <v>0.2739945352077484</v>
       </c>
       <c r="F341" t="n">
-        <v>0.6750707626342773</v>
+        <v>0.6750727295875549</v>
       </c>
       <c r="G341" t="n">
-        <v>3.864814281463623</v>
+        <v>3.864812612533569</v>
       </c>
       <c r="H341" t="n">
         <v>7.750905513763428</v>
@@ -9324,13 +9324,13 @@
         <v>18.49092292785645</v>
       </c>
       <c r="E342" t="n">
-        <v>-1.708052396774292</v>
+        <v>-1.708052515983582</v>
       </c>
       <c r="F342" t="n">
-        <v>-2.266818046569824</v>
+        <v>-2.266816139221191</v>
       </c>
       <c r="G342" t="n">
-        <v>3.18481969833374</v>
+        <v>3.184818029403687</v>
       </c>
       <c r="H342" t="n">
         <v>9.176568031311035</v>
@@ -9347,19 +9347,19 @@
         <v>26.05327606201172</v>
       </c>
       <c r="D343" t="n">
-        <v>11.33625602722168</v>
+        <v>11.33625507354736</v>
       </c>
       <c r="E343" t="n">
         <v>-2.777345418930054</v>
       </c>
       <c r="F343" t="n">
-        <v>-5.323195457458496</v>
+        <v>-5.323197364807129</v>
       </c>
       <c r="G343" t="n">
-        <v>2.490951061248779</v>
+        <v>2.490949392318726</v>
       </c>
       <c r="H343" t="n">
-        <v>10.55712699890137</v>
+        <v>10.55712604522705</v>
       </c>
     </row>
     <row r="344">
@@ -9370,7 +9370,7 @@
         <v>0.4354200959205627</v>
       </c>
       <c r="C344" t="n">
-        <v>25.92457580566406</v>
+        <v>25.9245777130127</v>
       </c>
       <c r="D344" t="n">
         <v>5.423089504241943</v>
@@ -9382,7 +9382,7 @@
         <v>-8.385991096496582</v>
       </c>
       <c r="G344" t="n">
-        <v>1.876876354217529</v>
+        <v>1.876876711845398</v>
       </c>
       <c r="H344" t="n">
         <v>11.85321807861328</v>
@@ -9399,19 +9399,19 @@
         <v>26.04547691345215</v>
       </c>
       <c r="D345" t="n">
-        <v>1.197556138038635</v>
+        <v>1.197557926177979</v>
       </c>
       <c r="E345" t="n">
-        <v>-1.986711502075195</v>
+        <v>-1.986711621284485</v>
       </c>
       <c r="F345" t="n">
         <v>-11.30513477325439</v>
       </c>
       <c r="G345" t="n">
-        <v>1.49354887008667</v>
+        <v>1.493549227714539</v>
       </c>
       <c r="H345" t="n">
-        <v>12.93313217163086</v>
+        <v>12.93313312530518</v>
       </c>
     </row>
     <row r="346">
@@ -9425,16 +9425,16 @@
         <v>26.34553337097168</v>
       </c>
       <c r="D346" t="n">
-        <v>-0.9006665945053101</v>
+        <v>-0.9006667733192444</v>
       </c>
       <c r="E346" t="n">
-        <v>-1.429258823394775</v>
+        <v>-1.429258942604065</v>
       </c>
       <c r="F346" t="n">
         <v>-13.93363285064697</v>
       </c>
       <c r="G346" t="n">
-        <v>1.505536556243896</v>
+        <v>1.505535006523132</v>
       </c>
       <c r="H346" t="n">
         <v>13.67775630950928</v>
@@ -9451,16 +9451,16 @@
         <v>26.6917552947998</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.8145784139633179</v>
+        <v>-0.8145785927772522</v>
       </c>
       <c r="E347" t="n">
-        <v>-1.07324743270874</v>
+        <v>-1.07324755191803</v>
       </c>
       <c r="F347" t="n">
-        <v>-16.15388870239258</v>
+        <v>-16.15388679504395</v>
       </c>
       <c r="G347" t="n">
-        <v>2.072434902191162</v>
+        <v>2.072435140609741</v>
       </c>
       <c r="H347" t="n">
         <v>13.98475742340088</v>
@@ -9477,19 +9477,19 @@
         <v>27.0377368927002</v>
       </c>
       <c r="D348" t="n">
-        <v>1.11769163608551</v>
+        <v>1.117689609527588</v>
       </c>
       <c r="E348" t="n">
         <v>-1.053805947303772</v>
       </c>
       <c r="F348" t="n">
-        <v>-17.88127899169922</v>
+        <v>-17.88127708435059</v>
       </c>
       <c r="G348" t="n">
-        <v>3.321691036224365</v>
+        <v>3.321691274642944</v>
       </c>
       <c r="H348" t="n">
-        <v>13.69215393066406</v>
+        <v>13.69215297698975</v>
       </c>
     </row>
     <row r="349">
@@ -9500,19 +9500,19 @@
         <v>0.5705922842025757</v>
       </c>
       <c r="C349" t="n">
-        <v>27.41770553588867</v>
+        <v>27.4177074432373</v>
       </c>
       <c r="D349" t="n">
-        <v>4.263927936553955</v>
+        <v>4.263928890228271</v>
       </c>
       <c r="E349" t="n">
-        <v>-1.944524049758911</v>
+        <v>-1.944524168968201</v>
       </c>
       <c r="F349" t="n">
-        <v>-19.03940582275391</v>
+        <v>-19.03940391540527</v>
       </c>
       <c r="G349" t="n">
-        <v>5.328329563140869</v>
+        <v>5.328330039978027</v>
       </c>
       <c r="H349" t="n">
         <v>12.51068115234375</v>
@@ -9529,16 +9529,16 @@
         <v>27.84372138977051</v>
       </c>
       <c r="D350" t="n">
-        <v>7.858651638031006</v>
+        <v>7.858650684356689</v>
       </c>
       <c r="E350" t="n">
         <v>-4.101238250732422</v>
       </c>
       <c r="F350" t="n">
-        <v>-19.52038955688477</v>
+        <v>-19.52038764953613</v>
       </c>
       <c r="G350" t="n">
-        <v>8.130464553833008</v>
+        <v>8.130465507507324</v>
       </c>
       <c r="H350" t="n">
         <v>10.05116844177246</v>
@@ -9555,16 +9555,16 @@
         <v>28.28158950805664</v>
       </c>
       <c r="D351" t="n">
-        <v>11.53035449981689</v>
+        <v>11.53035354614258</v>
       </c>
       <c r="E351" t="n">
-        <v>-6.544770240783691</v>
+        <v>-6.54477071762085</v>
       </c>
       <c r="F351" t="n">
-        <v>-19.17511749267578</v>
+        <v>-19.17511558532715</v>
       </c>
       <c r="G351" t="n">
-        <v>11.76816558837891</v>
+        <v>11.76816463470459</v>
       </c>
       <c r="H351" t="n">
         <v>5.797392845153809</v>
@@ -9581,10 +9581,10 @@
         <v>32.18456268310547</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4702287912368774</v>
+        <v>0.4702286422252655</v>
       </c>
       <c r="E352" t="n">
-        <v>-5.446859836578369</v>
+        <v>-5.446859359741211</v>
       </c>
       <c r="F352" t="n">
         <v>-4.766512870788574</v>
@@ -9598,16 +9598,16 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>-2.344919813879187e-08</v>
+        <v>2.717084690573301e-08</v>
       </c>
       <c r="B353" t="n">
         <v>0.6068375706672668</v>
       </c>
       <c r="C353" t="n">
-        <v>30.90678215026855</v>
+        <v>30.90678405761719</v>
       </c>
       <c r="D353" t="n">
-        <v>1.628517746925354</v>
+        <v>1.628519535064697</v>
       </c>
       <c r="E353" t="n">
         <v>-7.153579235076904</v>
@@ -9619,12 +9619,12 @@
         <v>24.97526550292969</v>
       </c>
       <c r="H353" t="n">
-        <v>7.456566333770752</v>
+        <v>7.456565856933594</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>0.01942179165780544</v>
+        <v>0.01942178420722485</v>
       </c>
       <c r="B354" t="n">
         <v>0.6101404428482056</v>
@@ -9633,7 +9633,7 @@
         <v>29.37425804138184</v>
       </c>
       <c r="D354" t="n">
-        <v>2.633836269378662</v>
+        <v>2.633837223052979</v>
       </c>
       <c r="E354" t="n">
         <v>-7.99292516708374</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>0.04271558672189713</v>
+        <v>0.04271557554602623</v>
       </c>
       <c r="B355" t="n">
         <v>0.6210901141166687</v>
@@ -9662,7 +9662,7 @@
         <v>3.36967134475708</v>
       </c>
       <c r="E355" t="n">
-        <v>-7.874219417572021</v>
+        <v>-7.874218463897705</v>
       </c>
       <c r="F355" t="n">
         <v>-1.554974555969238</v>
@@ -9671,12 +9671,12 @@
         <v>35.98350524902344</v>
       </c>
       <c r="H355" t="n">
-        <v>-4.798434257507324</v>
+        <v>-4.798434734344482</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>0.06969443708658218</v>
+        <v>0.06969442963600159</v>
       </c>
       <c r="B356" t="n">
         <v>0.6405146718025208</v>
@@ -9691,7 +9691,7 @@
         <v>-7.030215740203857</v>
       </c>
       <c r="F356" t="n">
-        <v>1.124111175537109</v>
+        <v>1.124112129211426</v>
       </c>
       <c r="G356" t="n">
         <v>42.61345291137695</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>0.1008086875081062</v>
+        <v>0.1008086800575256</v>
       </c>
       <c r="B357" t="n">
         <v>0.6686083078384399</v>
@@ -9711,7 +9711,7 @@
         <v>23.2596549987793</v>
       </c>
       <c r="D357" t="n">
-        <v>3.348803997039795</v>
+        <v>3.348804950714111</v>
       </c>
       <c r="E357" t="n">
         <v>-5.898867130279541</v>
@@ -9737,13 +9737,13 @@
         <v>20.79283332824707</v>
       </c>
       <c r="D358" t="n">
-        <v>2.588545322418213</v>
+        <v>2.588546276092529</v>
       </c>
       <c r="E358" t="n">
         <v>-4.782667636871338</v>
       </c>
       <c r="F358" t="n">
-        <v>8.314407348632812</v>
+        <v>8.314406394958496</v>
       </c>
       <c r="G358" t="n">
         <v>55.83676528930664</v>
@@ -9763,19 +9763,19 @@
         <v>18.25476455688477</v>
       </c>
       <c r="D359" t="n">
-        <v>1.52885115146637</v>
+        <v>1.52885103225708</v>
       </c>
       <c r="E359" t="n">
-        <v>-3.806578159332275</v>
+        <v>-3.806577682495117</v>
       </c>
       <c r="F359" t="n">
-        <v>12.33372211456299</v>
+        <v>12.3337230682373</v>
       </c>
       <c r="G359" t="n">
         <v>60.83515930175781</v>
       </c>
       <c r="H359" t="n">
-        <v>-13.25527000427246</v>
+        <v>-13.25526905059814</v>
       </c>
     </row>
     <row r="360">
@@ -9789,16 +9789,16 @@
         <v>15.75786018371582</v>
       </c>
       <c r="D360" t="n">
-        <v>0.4145323038101196</v>
+        <v>0.4145340621471405</v>
       </c>
       <c r="E360" t="n">
-        <v>-2.917726278305054</v>
+        <v>-2.917726039886475</v>
       </c>
       <c r="F360" t="n">
         <v>16.28795433044434</v>
       </c>
       <c r="G360" t="n">
-        <v>63.94037246704102</v>
+        <v>63.94036865234375</v>
       </c>
       <c r="H360" t="n">
         <v>-9.02980899810791</v>
@@ -9812,13 +9812,13 @@
         <v>0.8276205658912659</v>
       </c>
       <c r="C361" t="n">
-        <v>13.39148044586182</v>
+        <v>13.3914794921875</v>
       </c>
       <c r="D361" t="n">
-        <v>-0.5524476766586304</v>
+        <v>-0.5524478554725647</v>
       </c>
       <c r="E361" t="n">
-        <v>-1.998679399490356</v>
+        <v>-1.998679280281067</v>
       </c>
       <c r="F361" t="n">
         <v>19.99280166625977</v>
@@ -9841,19 +9841,19 @@
         <v>11.22716903686523</v>
       </c>
       <c r="D362" t="n">
-        <v>-1.225449919700623</v>
+        <v>-1.225450038909912</v>
       </c>
       <c r="E362" t="n">
-        <v>-0.9531592726707458</v>
+        <v>-0.9531592130661011</v>
       </c>
       <c r="F362" t="n">
         <v>23.31063270568848</v>
       </c>
       <c r="G362" t="n">
-        <v>63.98999786376953</v>
+        <v>63.98999404907227</v>
       </c>
       <c r="H362" t="n">
-        <v>-0.2534465789794922</v>
+        <v>-0.2534463405609131</v>
       </c>
     </row>
     <row r="363">
@@ -9864,22 +9864,22 @@
         <v>0.9012623429298401</v>
       </c>
       <c r="C363" t="n">
-        <v>9.282947540283203</v>
+        <v>9.282946586608887</v>
       </c>
       <c r="D363" t="n">
-        <v>-1.564141631126404</v>
+        <v>-1.564139842987061</v>
       </c>
       <c r="E363" t="n">
-        <v>0.2429277449846268</v>
+        <v>0.242927759885788</v>
       </c>
       <c r="F363" t="n">
-        <v>26.17411613464355</v>
+        <v>26.17411804199219</v>
       </c>
       <c r="G363" t="n">
-        <v>61.12539672851562</v>
+        <v>61.12539291381836</v>
       </c>
       <c r="H363" t="n">
-        <v>3.173304319381714</v>
+        <v>3.173304080963135</v>
       </c>
     </row>
     <row r="364">
@@ -9893,7 +9893,7 @@
         <v>7.528273105621338</v>
       </c>
       <c r="D364" t="n">
-        <v>-1.60957658290863</v>
+        <v>-1.60957670211792</v>
       </c>
       <c r="E364" t="n">
         <v>1.563114523887634</v>
@@ -9902,7 +9902,7 @@
         <v>28.53836441040039</v>
       </c>
       <c r="G364" t="n">
-        <v>56.63148880004883</v>
+        <v>56.63148498535156</v>
       </c>
       <c r="H364" t="n">
         <v>5.678918361663818</v>
@@ -9910,22 +9910,22 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>0.3747666478157043</v>
+        <v>0.374766618013382</v>
       </c>
       <c r="B365" t="n">
         <v>0.956081748008728</v>
       </c>
       <c r="C365" t="n">
-        <v>5.913900375366211</v>
+        <v>5.913900852203369</v>
       </c>
       <c r="D365" t="n">
-        <v>-1.425002455711365</v>
+        <v>-1.425002574920654</v>
       </c>
       <c r="E365" t="n">
         <v>2.978968143463135</v>
       </c>
       <c r="F365" t="n">
-        <v>30.33066749572754</v>
+        <v>30.33066940307617</v>
       </c>
       <c r="G365" t="n">
         <v>50.65621185302734</v>
@@ -9939,25 +9939,25 @@
         <v>0.3993045091629028</v>
       </c>
       <c r="B366" t="n">
-        <v>0.9748764038085938</v>
+        <v>0.974876344203949</v>
       </c>
       <c r="C366" t="n">
-        <v>4.38072681427002</v>
+        <v>4.380726337432861</v>
       </c>
       <c r="D366" t="n">
-        <v>-1.092339873313904</v>
+        <v>-1.092338085174561</v>
       </c>
       <c r="E366" t="n">
         <v>4.459642887115479</v>
       </c>
       <c r="F366" t="n">
-        <v>31.5382194519043</v>
+        <v>31.53822135925293</v>
       </c>
       <c r="G366" t="n">
         <v>43.55517959594727</v>
       </c>
       <c r="H366" t="n">
-        <v>7.576860427856445</v>
+        <v>7.576859474182129</v>
       </c>
     </row>
     <row r="367">
@@ -9968,16 +9968,16 @@
         <v>0.9875391125679016</v>
       </c>
       <c r="C367" t="n">
-        <v>2.881196737289429</v>
+        <v>2.88119649887085</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.6992944478988647</v>
+        <v>-0.6992946267127991</v>
       </c>
       <c r="E367" t="n">
-        <v>5.957253456115723</v>
+        <v>5.957253932952881</v>
       </c>
       <c r="F367" t="n">
-        <v>32.17497253417969</v>
+        <v>32.17497634887695</v>
       </c>
       <c r="G367" t="n">
         <v>35.74450302124023</v>
@@ -9994,22 +9994,22 @@
         <v>0.99421626329422</v>
       </c>
       <c r="C368" t="n">
-        <v>1.387698888778687</v>
+        <v>1.387698650360107</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.3274492025375366</v>
+        <v>-0.3274493515491486</v>
       </c>
       <c r="E368" t="n">
-        <v>7.401836395263672</v>
+        <v>7.40183687210083</v>
       </c>
       <c r="F368" t="n">
         <v>32.27909851074219</v>
       </c>
       <c r="G368" t="n">
-        <v>27.66982269287109</v>
+        <v>27.66982078552246</v>
       </c>
       <c r="H368" t="n">
-        <v>5.788424491882324</v>
+        <v>5.788424015045166</v>
       </c>
     </row>
     <row r="369">
@@ -10020,10 +10020,10 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.09775374084711075</v>
+        <v>-0.09775307774543762</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.01871622540056705</v>
+        <v>-0.01871637813746929</v>
       </c>
       <c r="E369" t="n">
         <v>8.734431266784668</v>
@@ -10032,10 +10032,10 @@
         <v>32.00242233276367</v>
       </c>
       <c r="G369" t="n">
-        <v>19.82099723815918</v>
+        <v>19.82099533081055</v>
       </c>
       <c r="H369" t="n">
-        <v>4.218388557434082</v>
+        <v>4.218388080596924</v>
       </c>
     </row>
     <row r="370">
@@ -10046,10 +10046,10 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C370" t="n">
-        <v>-1.537333726882935</v>
+        <v>-1.537333011627197</v>
       </c>
       <c r="D370" t="n">
-        <v>0.2691351175308228</v>
+        <v>0.2691349685192108</v>
       </c>
       <c r="E370" t="n">
         <v>9.943787574768066</v>
@@ -10061,7 +10061,7 @@
         <v>12.7351713180542</v>
       </c>
       <c r="H370" t="n">
-        <v>2.890978336334229</v>
+        <v>2.890978097915649</v>
       </c>
     </row>
     <row r="371">
@@ -10072,10 +10072,10 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C371" t="n">
-        <v>-2.87389874458313</v>
+        <v>-2.873898029327393</v>
       </c>
       <c r="D371" t="n">
-        <v>0.6441751718521118</v>
+        <v>0.6441749930381775</v>
       </c>
       <c r="E371" t="n">
         <v>11.02846813201904</v>
@@ -10084,7 +10084,7 @@
         <v>30.99393463134766</v>
       </c>
       <c r="G371" t="n">
-        <v>7.153585910797119</v>
+        <v>7.153587341308594</v>
       </c>
       <c r="H371" t="n">
         <v>2.219315767288208</v>
@@ -10098,10 +10098,10 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C372" t="n">
-        <v>-4.061036109924316</v>
+        <v>-4.061039447784424</v>
       </c>
       <c r="D372" t="n">
-        <v>1.240339875221252</v>
+        <v>1.240339756011963</v>
       </c>
       <c r="E372" t="n">
         <v>11.96594429016113</v>
@@ -10110,7 +10110,7 @@
         <v>30.56024932861328</v>
       </c>
       <c r="G372" t="n">
-        <v>3.567990779876709</v>
+        <v>3.567991018295288</v>
       </c>
       <c r="H372" t="n">
         <v>2.097066164016724</v>
@@ -10124,10 +10124,10 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C373" t="n">
-        <v>-5.103541374206543</v>
+        <v>-5.103540897369385</v>
       </c>
       <c r="D373" t="n">
-        <v>2.135076999664307</v>
+        <v>2.135078907012939</v>
       </c>
       <c r="E373" t="n">
         <v>12.72584915161133</v>
@@ -10136,7 +10136,7 @@
         <v>30.24405097961426</v>
       </c>
       <c r="G373" t="n">
-        <v>2.108869075775146</v>
+        <v>2.108869314193726</v>
       </c>
       <c r="H373" t="n">
         <v>2.046056747436523</v>
@@ -10150,7 +10150,7 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C374" t="n">
-        <v>-6.03299617767334</v>
+        <v>-6.032995700836182</v>
       </c>
       <c r="D374" t="n">
         <v>3.360687732696533</v>
@@ -10159,10 +10159,10 @@
         <v>13.26511192321777</v>
       </c>
       <c r="F374" t="n">
-        <v>29.98687362670898</v>
+        <v>29.98687553405762</v>
       </c>
       <c r="G374" t="n">
-        <v>2.479588985443115</v>
+        <v>2.479589223861694</v>
       </c>
       <c r="H374" t="n">
         <v>1.349458336830139</v>
@@ -10176,7 +10176,7 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C375" t="n">
-        <v>-6.888833045959473</v>
+        <v>-6.888832569122314</v>
       </c>
       <c r="D375" t="n">
         <v>4.920792102813721</v>
@@ -10188,10 +10188,10 @@
         <v>29.67742347717285</v>
       </c>
       <c r="G375" t="n">
-        <v>3.815743923187256</v>
+        <v>3.815744161605835</v>
       </c>
       <c r="H375" t="n">
-        <v>-0.4979972839355469</v>
+        <v>-0.4979970455169678</v>
       </c>
     </row>
     <row r="376">
@@ -10202,7 +10202,7 @@
         <v>0.9953081011772156</v>
       </c>
       <c r="C376" t="n">
-        <v>-7.680294990539551</v>
+        <v>-7.680296421051025</v>
       </c>
       <c r="D376" t="n">
         <v>6.797675609588623</v>
@@ -10214,10 +10214,10 @@
         <v>29.22984886169434</v>
       </c>
       <c r="G376" t="n">
-        <v>5.452352046966553</v>
+        <v>5.452352523803711</v>
       </c>
       <c r="H376" t="n">
-        <v>-3.368998050689697</v>
+        <v>-3.368997812271118</v>
       </c>
     </row>
     <row r="377">
@@ -10231,7 +10231,7 @@
         <v>-8.333846092224121</v>
       </c>
       <c r="D377" t="n">
-        <v>9.057035446166992</v>
+        <v>9.057034492492676</v>
       </c>
       <c r="E377" t="n">
         <v>12.34715557098389</v>
@@ -10240,10 +10240,10 @@
         <v>32.72652816772461</v>
       </c>
       <c r="G377" t="n">
-        <v>3.954198360443115</v>
+        <v>3.954198598861694</v>
       </c>
       <c r="H377" t="n">
-        <v>-2.018710613250732</v>
+        <v>-2.018710374832153</v>
       </c>
     </row>
     <row r="378">
@@ -10251,25 +10251,25 @@
         <v>0.6158651113510132</v>
       </c>
       <c r="B378" t="n">
-        <v>-2.297013779184454e-08</v>
+        <v>1.746720634798749e-08</v>
       </c>
       <c r="C378" t="n">
         <v>-8.65126895904541</v>
       </c>
       <c r="D378" t="n">
-        <v>11.8926362991333</v>
+        <v>11.89263534545898</v>
       </c>
       <c r="E378" t="n">
         <v>10.21060657501221</v>
       </c>
       <c r="F378" t="n">
-        <v>31.99587631225586</v>
+        <v>31.99587821960449</v>
       </c>
       <c r="G378" t="n">
-        <v>5.740691661834717</v>
+        <v>5.740692138671875</v>
       </c>
       <c r="H378" t="n">
-        <v>-4.987510681152344</v>
+        <v>-4.987511157989502</v>
       </c>
     </row>
     <row r="379">
@@ -10277,10 +10277,10 @@
         <v>0.6206898093223572</v>
       </c>
       <c r="B379" t="n">
-        <v>0.01182577665895224</v>
+        <v>0.01182581763714552</v>
       </c>
       <c r="C379" t="n">
-        <v>-8.401886940002441</v>
+        <v>-8.401888847351074</v>
       </c>
       <c r="D379" t="n">
         <v>15.4909029006958</v>
@@ -10292,7 +10292,7 @@
         <v>31.12182998657227</v>
       </c>
       <c r="G379" t="n">
-        <v>7.645551204681396</v>
+        <v>7.645550727844238</v>
       </c>
       <c r="H379" t="n">
         <v>-6.828047752380371</v>
@@ -10303,10 +10303,10 @@
         <v>0.6230062246322632</v>
       </c>
       <c r="B380" t="n">
-        <v>0.02597258239984512</v>
+        <v>0.02597256191074848</v>
       </c>
       <c r="C380" t="n">
-        <v>-7.352435111999512</v>
+        <v>-7.352436542510986</v>
       </c>
       <c r="D380" t="n">
         <v>20.05574989318848</v>
@@ -10329,19 +10329,19 @@
         <v>0.6327542066574097</v>
       </c>
       <c r="B381" t="n">
-        <v>0.04351840168237686</v>
+        <v>0.04351838305592537</v>
       </c>
       <c r="C381" t="n">
-        <v>-5.302992820739746</v>
+        <v>-5.302992343902588</v>
       </c>
       <c r="D381" t="n">
         <v>25.77397155761719</v>
       </c>
       <c r="E381" t="n">
-        <v>-5.712520599365234</v>
+        <v>-5.712520122528076</v>
       </c>
       <c r="F381" t="n">
-        <v>28.63880729675293</v>
+        <v>28.63880920410156</v>
       </c>
       <c r="G381" t="n">
         <v>10.726806640625</v>
@@ -10355,25 +10355,25 @@
         <v>0.6517907977104187</v>
       </c>
       <c r="B382" t="n">
-        <v>0.0661611333489418</v>
+        <v>0.06616111099720001</v>
       </c>
       <c r="C382" t="n">
-        <v>-2.29651951789856</v>
+        <v>-2.296520709991455</v>
       </c>
       <c r="D382" t="n">
         <v>32.53843688964844</v>
       </c>
       <c r="E382" t="n">
-        <v>-12.52554321289062</v>
+        <v>-12.52554225921631</v>
       </c>
       <c r="F382" t="n">
-        <v>26.89430809020996</v>
+        <v>26.89430999755859</v>
       </c>
       <c r="G382" t="n">
         <v>11.35634899139404</v>
       </c>
       <c r="H382" t="n">
-        <v>-3.928468227386475</v>
+        <v>-3.928467988967896</v>
       </c>
     </row>
     <row r="383">
@@ -10381,16 +10381,16 @@
         <v>0.6797168850898743</v>
       </c>
       <c r="B383" t="n">
-        <v>0.09439641982316971</v>
+        <v>0.09439642727375031</v>
       </c>
       <c r="C383" t="n">
-        <v>1.51532244682312</v>
+        <v>1.515322208404541</v>
       </c>
       <c r="D383" t="n">
         <v>40.00061416625977</v>
       </c>
       <c r="E383" t="n">
-        <v>-17.64094734191895</v>
+        <v>-17.64094924926758</v>
       </c>
       <c r="F383" t="n">
         <v>24.83669471740723</v>
@@ -10399,7 +10399,7 @@
         <v>11.24954319000244</v>
       </c>
       <c r="H383" t="n">
-        <v>-2.108511447906494</v>
+        <v>-2.108511686325073</v>
       </c>
     </row>
     <row r="384">
@@ -10407,10 +10407,10 @@
         <v>0.7151238322257996</v>
       </c>
       <c r="B384" t="n">
-        <v>0.1276996433734894</v>
+        <v>0.1276995986700058</v>
       </c>
       <c r="C384" t="n">
-        <v>5.889498710632324</v>
+        <v>5.889498233795166</v>
       </c>
       <c r="D384" t="n">
         <v>47.47826385498047</v>
@@ -10433,25 +10433,25 @@
         <v>0.7557540535926819</v>
       </c>
       <c r="B385" t="n">
-        <v>0.1646370589733124</v>
+        <v>0.1646370440721512</v>
       </c>
       <c r="C385" t="n">
         <v>10.48462867736816</v>
       </c>
       <c r="D385" t="n">
-        <v>54.09918594360352</v>
+        <v>54.09918212890625</v>
       </c>
       <c r="E385" t="n">
-        <v>-17.9802303314209</v>
+        <v>-17.98023223876953</v>
       </c>
       <c r="F385" t="n">
-        <v>20.17119979858398</v>
+        <v>20.17120170593262</v>
       </c>
       <c r="G385" t="n">
-        <v>9.335122108459473</v>
+        <v>9.335121154785156</v>
       </c>
       <c r="H385" t="n">
-        <v>0.5427778959274292</v>
+        <v>0.5427780151367188</v>
       </c>
     </row>
     <row r="386">
@@ -10459,22 +10459,22 @@
         <v>0.7984366416931152</v>
       </c>
       <c r="B386" t="n">
-        <v>0.2032122015953064</v>
+        <v>0.20321224629879</v>
       </c>
       <c r="C386" t="n">
         <v>15.02622032165527</v>
       </c>
       <c r="D386" t="n">
-        <v>59.16971206665039</v>
+        <v>59.16970825195312</v>
       </c>
       <c r="E386" t="n">
-        <v>-14.09178447723389</v>
+        <v>-14.0917854309082</v>
       </c>
       <c r="F386" t="n">
         <v>17.78373146057129</v>
       </c>
       <c r="G386" t="n">
-        <v>7.976321697235107</v>
+        <v>7.976322174072266</v>
       </c>
       <c r="H386" t="n">
         <v>1.485339164733887</v>
@@ -10485,22 +10485,22 @@
         <v>0.8406220078468323</v>
       </c>
       <c r="B387" t="n">
-        <v>0.241854190826416</v>
+        <v>0.2418541759252548</v>
       </c>
       <c r="C387" t="n">
         <v>19.31408309936523</v>
       </c>
       <c r="D387" t="n">
-        <v>62.22658538818359</v>
+        <v>62.22658157348633</v>
       </c>
       <c r="E387" t="n">
-        <v>-9.21835994720459</v>
+        <v>-9.218358993530273</v>
       </c>
       <c r="F387" t="n">
         <v>15.4851770401001</v>
       </c>
       <c r="G387" t="n">
-        <v>6.659142017364502</v>
+        <v>6.65914249420166</v>
       </c>
       <c r="H387" t="n">
         <v>2.330123901367188</v>
@@ -10526,7 +10526,7 @@
         <v>13.34041690826416</v>
       </c>
       <c r="G388" t="n">
-        <v>5.584938526153564</v>
+        <v>5.58493709564209</v>
       </c>
       <c r="H388" t="n">
         <v>3.182194709777832</v>
@@ -10543,16 +10543,16 @@
         <v>26.69367599487305</v>
       </c>
       <c r="D389" t="n">
-        <v>62.29938125610352</v>
+        <v>62.29937744140625</v>
       </c>
       <c r="E389" t="n">
-        <v>-0.4982364475727081</v>
+        <v>-0.4982365071773529</v>
       </c>
       <c r="F389" t="n">
         <v>11.38720321655273</v>
       </c>
       <c r="G389" t="n">
-        <v>4.879885196685791</v>
+        <v>4.879885673522949</v>
       </c>
       <c r="H389" t="n">
         <v>4.125606536865234</v>
@@ -10560,7 +10560,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>0.9489970207214355</v>
+        <v>0.9489969611167908</v>
       </c>
       <c r="B390" t="n">
         <v>0.3453842103481293</v>
@@ -10569,7 +10569,7 @@
         <v>29.6345100402832</v>
       </c>
       <c r="D390" t="n">
-        <v>59.57680892944336</v>
+        <v>59.57680511474609</v>
       </c>
       <c r="E390" t="n">
         <v>2.575315952301025</v>
@@ -10578,10 +10578,10 @@
         <v>9.631290435791016</v>
       </c>
       <c r="G390" t="n">
-        <v>4.592555522918701</v>
+        <v>4.592556953430176</v>
       </c>
       <c r="H390" t="n">
-        <v>5.233341217041016</v>
+        <v>5.233340740203857</v>
       </c>
     </row>
     <row r="391">
@@ -10589,7 +10589,7 @@
         <v>0.9763134121894836</v>
       </c>
       <c r="B391" t="n">
-        <v>0.3738042712211609</v>
+        <v>0.3738042414188385</v>
       </c>
       <c r="C391" t="n">
         <v>31.99310874938965</v>
@@ -10604,7 +10604,7 @@
         <v>8.033862113952637</v>
       </c>
       <c r="G391" t="n">
-        <v>4.663746356964111</v>
+        <v>4.66374683380127</v>
       </c>
       <c r="H391" t="n">
         <v>6.500419616699219</v>
@@ -10615,10 +10615,10 @@
         <v>0.9982216358184814</v>
       </c>
       <c r="B392" t="n">
-        <v>0.3996592164039612</v>
+        <v>0.3996591866016388</v>
       </c>
       <c r="C392" t="n">
-        <v>33.74184036254883</v>
+        <v>33.74184417724609</v>
       </c>
       <c r="D392" t="n">
         <v>49.56372451782227</v>
@@ -10630,7 +10630,7 @@
         <v>6.547124862670898</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00180196762085</v>
+        <v>5.001801490783691</v>
       </c>
       <c r="H392" t="n">
         <v>7.846288681030273</v>
@@ -10650,13 +10650,13 @@
         <v>42.72377777099609</v>
       </c>
       <c r="E393" t="n">
-        <v>6.306887626647949</v>
+        <v>6.306888103485107</v>
       </c>
       <c r="F393" t="n">
-        <v>5.113340377807617</v>
+        <v>5.113339424133301</v>
       </c>
       <c r="G393" t="n">
-        <v>5.475825786590576</v>
+        <v>5.475825309753418</v>
       </c>
       <c r="H393" t="n">
         <v>9.15485954284668</v>
@@ -10682,7 +10682,7 @@
         <v>3.693695068359375</v>
       </c>
       <c r="G394" t="n">
-        <v>5.973424434661865</v>
+        <v>5.973424911499023</v>
       </c>
       <c r="H394" t="n">
         <v>10.35428142547607</v>
@@ -10696,22 +10696,22 @@
         <v>0.4699062407016754</v>
       </c>
       <c r="C395" t="n">
-        <v>35.24254608154297</v>
+        <v>35.24254989624023</v>
       </c>
       <c r="D395" t="n">
         <v>26.83361053466797</v>
       </c>
       <c r="E395" t="n">
-        <v>4.673952579498291</v>
+        <v>4.673953056335449</v>
       </c>
       <c r="F395" t="n">
         <v>2.295432090759277</v>
       </c>
       <c r="G395" t="n">
-        <v>6.470982074737549</v>
+        <v>6.470980644226074</v>
       </c>
       <c r="H395" t="n">
-        <v>11.41268062591553</v>
+        <v>11.41267967224121</v>
       </c>
     </row>
     <row r="396">
@@ -10728,16 +10728,16 @@
         <v>18.53747749328613</v>
       </c>
       <c r="E396" t="n">
-        <v>3.561429977416992</v>
+        <v>3.561429738998413</v>
       </c>
       <c r="F396" t="n">
-        <v>0.9632272720336914</v>
+        <v>0.9632273316383362</v>
       </c>
       <c r="G396" t="n">
-        <v>7.037947177886963</v>
+        <v>7.037947654724121</v>
       </c>
       <c r="H396" t="n">
-        <v>12.31132316589355</v>
+        <v>12.31132411956787</v>
       </c>
     </row>
     <row r="397">
@@ -10748,22 +10748,22 @@
         <v>0.5140998363494873</v>
       </c>
       <c r="C397" t="n">
-        <v>34.10771179199219</v>
+        <v>34.10770797729492</v>
       </c>
       <c r="D397" t="n">
         <v>10.68671321868896</v>
       </c>
       <c r="E397" t="n">
-        <v>2.868483781814575</v>
+        <v>2.868484020233154</v>
       </c>
       <c r="F397" t="n">
-        <v>-0.2601118087768555</v>
+        <v>-0.2601136565208435</v>
       </c>
       <c r="G397" t="n">
-        <v>7.784332752227783</v>
+        <v>7.784333229064941</v>
       </c>
       <c r="H397" t="n">
-        <v>13.04566955566406</v>
+        <v>13.04567050933838</v>
       </c>
     </row>
     <row r="398">
@@ -10774,7 +10774,7 @@
         <v>0.5338999629020691</v>
       </c>
       <c r="C398" t="n">
-        <v>33.40517425537109</v>
+        <v>33.40517044067383</v>
       </c>
       <c r="D398" t="n">
         <v>4.010454654693604</v>
@@ -10803,7 +10803,7 @@
         <v>32.80168151855469</v>
       </c>
       <c r="D399" t="n">
-        <v>-0.6952069997787476</v>
+        <v>-0.6952090859413147</v>
       </c>
       <c r="E399" t="n">
         <v>2.392953872680664</v>
@@ -10858,10 +10858,10 @@
         <v>-2.635667324066162</v>
       </c>
       <c r="E401" t="n">
-        <v>-0.2177453488111496</v>
+        <v>-0.2177453935146332</v>
       </c>
       <c r="F401" t="n">
-        <v>-3.965996742248535</v>
+        <v>-3.965994834899902</v>
       </c>
       <c r="G401" t="n">
         <v>14.34756755828857</v>

--- a/Predictions/rolling_gt_next_tick_with_pv.xlsx
+++ b/Predictions/rolling_gt_next_tick_with_pv.xlsx
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1107624769210815</v>
+        <v>0.1107625067234039</v>
       </c>
       <c r="B2" t="n">
         <v>0.7629929184913635</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1374954283237457</v>
+        <v>0.1374953985214233</v>
       </c>
       <c r="B3" t="n">
         <v>0.8006601929664612</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.166948139667511</v>
+        <v>0.1669481098651886</v>
       </c>
       <c r="B4" t="n">
         <v>0.8350825905799866</v>
@@ -631,7 +631,7 @@
         <v>0.2967199087142944</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9389622807502747</v>
+        <v>0.9389623403549194</v>
       </c>
       <c r="C8" t="n">
         <v>9.480586051940918</v>
@@ -657,7 +657,7 @@
         <v>0.3283927738666534</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9561896920204163</v>
+        <v>0.956189751625061</v>
       </c>
       <c r="C9" t="n">
         <v>7.545021057128906</v>
@@ -969,7 +969,7 @@
         <v>0.5925468802452087</v>
       </c>
       <c r="B21" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C21" t="n">
         <v>-7.093594074249268</v>
@@ -995,7 +995,7 @@
         <v>0.5929203629493713</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0072680888697505</v>
+        <v>0.00726810609921813</v>
       </c>
       <c r="C22" t="n">
         <v>-6.299343585968018</v>
@@ -1021,7 +1021,7 @@
         <v>0.6016235947608948</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01752712018787861</v>
+        <v>0.01752707920968533</v>
       </c>
       <c r="C23" t="n">
         <v>-4.545923709869385</v>
@@ -1047,7 +1047,7 @@
         <v>0.6208371520042419</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0306404996663332</v>
+        <v>0.03064051829278469</v>
       </c>
       <c r="C24" t="n">
         <v>-1.95525598526001</v>
@@ -1073,7 +1073,7 @@
         <v>0.6492250561714172</v>
       </c>
       <c r="B25" t="n">
-        <v>0.04692758992314339</v>
+        <v>0.04692760482430458</v>
       </c>
       <c r="C25" t="n">
         <v>1.239973545074463</v>
@@ -1099,7 +1099,7 @@
         <v>0.6842376589775085</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06713230907917023</v>
+        <v>0.06713233143091202</v>
       </c>
       <c r="C26" t="n">
         <v>4.734203815460205</v>
@@ -1125,7 +1125,7 @@
         <v>0.7225265502929688</v>
       </c>
       <c r="B27" t="n">
-        <v>0.09150777757167816</v>
+        <v>0.09150777012109756</v>
       </c>
       <c r="C27" t="n">
         <v>8.234172821044922</v>
@@ -1151,7 +1151,7 @@
         <v>0.7608784437179565</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1198380142450333</v>
+        <v>0.1198380365967751</v>
       </c>
       <c r="C28" t="n">
         <v>11.54106521606445</v>
@@ -1177,7 +1177,7 @@
         <v>0.7971145510673523</v>
       </c>
       <c r="B29" t="n">
-        <v>0.151369646191597</v>
+        <v>0.1513696312904358</v>
       </c>
       <c r="C29" t="n">
         <v>14.54943466186523</v>
@@ -1203,7 +1203,7 @@
         <v>0.8300795555114746</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1851050406694412</v>
+        <v>0.1851050555706024</v>
       </c>
       <c r="C30" t="n">
         <v>17.20433235168457</v>
@@ -1229,7 +1229,7 @@
         <v>0.8591712713241577</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2201094478368759</v>
+        <v>0.2201094925403595</v>
       </c>
       <c r="C31" t="n">
         <v>19.48697662353516</v>
@@ -1333,7 +1333,7 @@
         <v>0.9362504482269287</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3604375720024109</v>
+        <v>0.3604375422000885</v>
       </c>
       <c r="C35" t="n">
         <v>25.19003677368164</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.9466767907142639</v>
+        <v>0.9466768503189087</v>
       </c>
       <c r="B36" t="n">
         <v>0.3920238316059113</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.9608076214790344</v>
+        <v>0.9608076810836792</v>
       </c>
       <c r="B38" t="n">
         <v>0.4452469348907471</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.973432183265686</v>
+        <v>0.9734322428703308</v>
       </c>
       <c r="B40" t="n">
         <v>0.486019492149353</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B47" t="n">
         <v>0.6052631139755249</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01604279689490795</v>
+        <v>0.01604276895523071</v>
       </c>
       <c r="B48" t="n">
         <v>0.607780933380127</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.03489365801215172</v>
+        <v>0.03489363193511963</v>
       </c>
       <c r="B49" t="n">
         <v>0.6204983592033386</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.05470236763358116</v>
+        <v>0.05470234155654907</v>
       </c>
       <c r="B50" t="n">
         <v>0.6435858607292175</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.07494953274726868</v>
+        <v>0.07494950294494629</v>
       </c>
       <c r="B51" t="n">
         <v>0.6749206185340881</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.1806264519691467</v>
+        <v>0.1806264221668243</v>
       </c>
       <c r="B55" t="n">
         <v>0.8176935315132141</v>
@@ -1957,7 +1957,7 @@
         <v>0.3155545890331268</v>
       </c>
       <c r="B59" t="n">
-        <v>0.9233917593955994</v>
+        <v>0.9233918190002441</v>
       </c>
       <c r="C59" t="n">
         <v>7.990589141845703</v>
@@ -1983,7 +1983,7 @@
         <v>0.3472479581832886</v>
       </c>
       <c r="B60" t="n">
-        <v>0.941520631313324</v>
+        <v>0.9415206909179688</v>
       </c>
       <c r="C60" t="n">
         <v>6.044664859771729</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.4070127010345459</v>
+        <v>0.4070127308368683</v>
       </c>
       <c r="B62" t="n">
         <v>0.9635723829269409</v>
@@ -2295,7 +2295,7 @@
         <v>0.5999999046325684</v>
       </c>
       <c r="B72" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C72" t="n">
         <v>-8.007962226867676</v>
@@ -2321,7 +2321,7 @@
         <v>0.6013975143432617</v>
       </c>
       <c r="B73" t="n">
-        <v>0.005424040369689465</v>
+        <v>0.005424057599157095</v>
       </c>
       <c r="C73" t="n">
         <v>-7.028366565704346</v>
@@ -2347,7 +2347,7 @@
         <v>0.61162930727005</v>
       </c>
       <c r="B74" t="n">
-        <v>0.01338745933026075</v>
+        <v>0.01338747702538967</v>
       </c>
       <c r="C74" t="n">
         <v>-5.141279697418213</v>
@@ -2373,7 +2373,7 @@
         <v>0.6313397884368896</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0240215826779604</v>
+        <v>0.02402154169976711</v>
       </c>
       <c r="C75" t="n">
         <v>-2.45647668838501</v>
@@ -2399,7 +2399,7 @@
         <v>0.6593824028968811</v>
       </c>
       <c r="B76" t="n">
-        <v>0.03823157027363777</v>
+        <v>0.03823158517479897</v>
       </c>
       <c r="C76" t="n">
         <v>0.7708210349082947</v>
@@ -2425,7 +2425,7 @@
         <v>0.6930912733078003</v>
       </c>
       <c r="B77" t="n">
-        <v>0.05715467408299446</v>
+        <v>0.05715462937951088</v>
       </c>
       <c r="C77" t="n">
         <v>4.227010250091553</v>
@@ -2451,7 +2451,7 @@
         <v>0.7291909456253052</v>
       </c>
       <c r="B78" t="n">
-        <v>0.08121927082538605</v>
+        <v>0.08121929317712784</v>
       </c>
       <c r="C78" t="n">
         <v>7.626901626586914</v>
@@ -2477,7 +2477,7 @@
         <v>0.7647025585174561</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1102267056703568</v>
+        <v>0.1102267280220985</v>
       </c>
       <c r="C79" t="n">
         <v>10.79610252380371</v>
@@ -2503,7 +2503,7 @@
         <v>0.7978046536445618</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1436107903718948</v>
+        <v>0.1436108350753784</v>
       </c>
       <c r="C80" t="n">
         <v>13.64182281494141</v>
@@ -2529,7 +2529,7 @@
         <v>0.8275279998779297</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1802560538053513</v>
+        <v>0.1802560985088348</v>
       </c>
       <c r="C81" t="n">
         <v>16.12667274475098</v>
@@ -2555,7 +2555,7 @@
         <v>0.8534821271896362</v>
       </c>
       <c r="B82" t="n">
-        <v>0.2192039340734482</v>
+        <v>0.2192039489746094</v>
       </c>
       <c r="C82" t="n">
         <v>18.22812461853027</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.9367565512657166</v>
+        <v>0.9367566108703613</v>
       </c>
       <c r="B89" t="n">
         <v>0.4582995176315308</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.9408068060874939</v>
+        <v>0.9408068656921387</v>
       </c>
       <c r="B90" t="n">
         <v>0.4774189293384552</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.9523091316223145</v>
+        <v>0.9523091912269592</v>
       </c>
       <c r="B92" t="n">
         <v>0.5082769393920898</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.9654043912887573</v>
+        <v>0.9654044508934021</v>
       </c>
       <c r="B94" t="n">
         <v>0.5402244329452515</v>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B98" t="n">
         <v>0.6025266051292419</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B99" t="n">
         <v>0.6164657473564148</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B100" t="n">
         <v>0.6369240880012512</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B101" t="n">
         <v>0.6631808280944824</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B102" t="n">
         <v>0.6940001845359802</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.008664277382194996</v>
+        <v>0.008664251305162907</v>
       </c>
       <c r="B103" t="n">
         <v>0.727738082408905</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.03818186745047569</v>
+        <v>0.0381818413734436</v>
       </c>
       <c r="B104" t="n">
         <v>0.7625082731246948</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.07395091652870178</v>
+        <v>0.07395088672637939</v>
       </c>
       <c r="B105" t="n">
         <v>0.796481192111969</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.1996541023254395</v>
+        <v>0.1996540725231171</v>
       </c>
       <c r="B108" t="n">
         <v>0.8814589977264404</v>
@@ -3413,7 +3413,7 @@
         <v>0.4526273906230927</v>
       </c>
       <c r="B115" t="n">
-        <v>0.94820237159729</v>
+        <v>0.9482024312019348</v>
       </c>
       <c r="C115" t="n">
         <v>-2.402330875396729</v>
@@ -3439,7 +3439,7 @@
         <v>0.4827049970626831</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9502482414245605</v>
+        <v>0.9502483010292053</v>
       </c>
       <c r="C116" t="n">
         <v>-4.526888370513916</v>
@@ -3517,7 +3517,7 @@
         <v>0.5615153908729553</v>
       </c>
       <c r="B119" t="n">
-        <v>0.9634087085723877</v>
+        <v>0.9634087681770325</v>
       </c>
       <c r="C119" t="n">
         <v>-9.456295967102051</v>
@@ -3569,7 +3569,7 @@
         <v>0.5928204655647278</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9731182456016541</v>
+        <v>0.9731183052062988</v>
       </c>
       <c r="C121" t="n">
         <v>-10.93469142913818</v>
@@ -3621,7 +3621,7 @@
         <v>0.6003017425537109</v>
       </c>
       <c r="B123" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C123" t="n">
         <v>-10.21685314178467</v>
@@ -3647,7 +3647,7 @@
         <v>0.6065787672996521</v>
       </c>
       <c r="B124" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C124" t="n">
         <v>-8.885464668273926</v>
@@ -3673,7 +3673,7 @@
         <v>0.6187805533409119</v>
       </c>
       <c r="B125" t="n">
-        <v>0.003496962366625667</v>
+        <v>0.003496980061754584</v>
       </c>
       <c r="C125" t="n">
         <v>-6.977999210357666</v>
@@ -3699,7 +3699,7 @@
         <v>0.6362619400024414</v>
       </c>
       <c r="B126" t="n">
-        <v>0.01307179313153028</v>
+        <v>0.0130718108266592</v>
       </c>
       <c r="C126" t="n">
         <v>-4.505127429962158</v>
@@ -3725,7 +3725,7 @@
         <v>0.6589251160621643</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0291829276829958</v>
+        <v>0.02918294630944729</v>
       </c>
       <c r="C127" t="n">
         <v>-1.396151065826416</v>
@@ -3751,7 +3751,7 @@
         <v>0.6874180436134338</v>
       </c>
       <c r="B128" t="n">
-        <v>0.05181904509663582</v>
+        <v>0.05181905999779701</v>
       </c>
       <c r="C128" t="n">
         <v>2.3663649559021</v>
@@ -3777,7 +3777,7 @@
         <v>0.7219004034996033</v>
       </c>
       <c r="B129" t="n">
-        <v>0.08015646040439606</v>
+        <v>0.08015648275613785</v>
       </c>
       <c r="C129" t="n">
         <v>6.582391262054443</v>
@@ -3803,7 +3803,7 @@
         <v>0.7605391144752502</v>
       </c>
       <c r="B130" t="n">
-        <v>0.112908735871315</v>
+        <v>0.1129087284207344</v>
       </c>
       <c r="C130" t="n">
         <v>10.92053031921387</v>
@@ -3829,7 +3829,7 @@
         <v>0.8002969622612</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1486511379480362</v>
+        <v>0.1486511528491974</v>
       </c>
       <c r="C131" t="n">
         <v>15.04599761962891</v>
@@ -3855,7 +3855,7 @@
         <v>0.8381056785583496</v>
       </c>
       <c r="B132" t="n">
-        <v>0.1858607679605484</v>
+        <v>0.1858607530593872</v>
       </c>
       <c r="C132" t="n">
         <v>18.74056243896484</v>
@@ -3881,7 +3881,7 @@
         <v>0.8719653487205505</v>
       </c>
       <c r="B133" t="n">
-        <v>0.2228649407625198</v>
+        <v>0.2228649258613586</v>
       </c>
       <c r="C133" t="n">
         <v>21.90056228637695</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.9657270908355713</v>
+        <v>0.9657271504402161</v>
       </c>
       <c r="B145" t="n">
         <v>0.5746930837631226</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.972370445728302</v>
+        <v>0.9723705053329468</v>
       </c>
       <c r="B147" t="n">
         <v>0.5940595269203186</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B149" t="n">
         <v>0.5945975184440613</v>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B150" t="n">
         <v>0.6086172461509705</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B151" t="n">
         <v>0.6290242075920105</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.002122191013768315</v>
+        <v>0.002122164471074939</v>
       </c>
       <c r="B152" t="n">
         <v>0.6552510857582092</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.02146240882575512</v>
+        <v>0.02146244049072266</v>
       </c>
       <c r="B153" t="n">
         <v>0.6864588260650635</v>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.05032887682318687</v>
+        <v>0.05032885074615479</v>
       </c>
       <c r="B154" t="n">
         <v>0.7213463187217712</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.08345457911491394</v>
+        <v>0.08345460891723633</v>
       </c>
       <c r="B155" t="n">
         <v>0.7580199241638184</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.1166190803050995</v>
+        <v>0.1166191101074219</v>
       </c>
       <c r="B156" t="n">
         <v>0.794208824634552</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.1834928095340729</v>
+        <v>0.1834927797317505</v>
       </c>
       <c r="B158" t="n">
         <v>0.8571236133575439</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.2216275930404663</v>
+        <v>0.2216275632381439</v>
       </c>
       <c r="B159" t="n">
         <v>0.8814563751220703</v>
@@ -4632,7 +4632,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0.3407293558120728</v>
+        <v>0.3407293856143951</v>
       </c>
       <c r="B162" t="n">
         <v>0.921866238117218</v>
@@ -4869,7 +4869,7 @@
         <v>0.5785559415817261</v>
       </c>
       <c r="B171" t="n">
-        <v>0.9325688481330872</v>
+        <v>0.9325689077377319</v>
       </c>
       <c r="C171" t="n">
         <v>-11.3001127243042</v>
@@ -4947,7 +4947,7 @@
         <v>0.5968697667121887</v>
       </c>
       <c r="B174" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C174" t="n">
         <v>-9.259345054626465</v>
@@ -4973,7 +4973,7 @@
         <v>0.6112648248672485</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0005332406144589186</v>
+        <v>0.0005331986467354</v>
       </c>
       <c r="C175" t="n">
         <v>-7.096271991729736</v>
@@ -4999,7 +4999,7 @@
         <v>0.6318724751472473</v>
       </c>
       <c r="B176" t="n">
-        <v>0.00439180713146925</v>
+        <v>0.00439182436093688</v>
       </c>
       <c r="C176" t="n">
         <v>-4.484146595001221</v>
@@ -5025,7 +5025,7 @@
         <v>0.656758189201355</v>
       </c>
       <c r="B177" t="n">
-        <v>0.01303072553128004</v>
+        <v>0.01303074322640896</v>
       </c>
       <c r="C177" t="n">
         <v>-1.416090488433838</v>
@@ -5051,7 +5051,7 @@
         <v>0.6859877109527588</v>
       </c>
       <c r="B178" t="n">
-        <v>0.02864708192646503</v>
+        <v>0.02864704094827175</v>
       </c>
       <c r="C178" t="n">
         <v>2.237298488616943</v>
@@ -5077,7 +5077,7 @@
         <v>0.720793604850769</v>
       </c>
       <c r="B179" t="n">
-        <v>0.05231745913624763</v>
+        <v>0.05231747403740883</v>
       </c>
       <c r="C179" t="n">
         <v>6.468019008636475</v>
@@ -5103,7 +5103,7 @@
         <v>0.7610998153686523</v>
       </c>
       <c r="B180" t="n">
-        <v>0.08323611319065094</v>
+        <v>0.08323613554239273</v>
       </c>
       <c r="C180" t="n">
         <v>10.96612358093262</v>
@@ -5129,7 +5129,7 @@
         <v>0.8039534091949463</v>
       </c>
       <c r="B181" t="n">
-        <v>0.1194589287042618</v>
+        <v>0.1194589510560036</v>
       </c>
       <c r="C181" t="n">
         <v>15.29684925079346</v>
@@ -5155,7 +5155,7 @@
         <v>0.8452123403549194</v>
       </c>
       <c r="B182" t="n">
-        <v>0.1588316112756729</v>
+        <v>0.1588315665721893</v>
       </c>
       <c r="C182" t="n">
         <v>19.12456130981445</v>
@@ -5181,7 +5181,7 @@
         <v>0.8816790580749512</v>
       </c>
       <c r="B183" t="n">
-        <v>0.1992898136377335</v>
+        <v>0.1992897987365723</v>
       </c>
       <c r="C183" t="n">
         <v>22.31101608276367</v>
@@ -5207,7 +5207,7 @@
         <v>0.9120364785194397</v>
       </c>
       <c r="B184" t="n">
-        <v>0.2388261705636978</v>
+        <v>0.2388262152671814</v>
       </c>
       <c r="C184" t="n">
         <v>24.83685302734375</v>
@@ -5337,7 +5337,7 @@
         <v>0.9696836471557617</v>
       </c>
       <c r="B189" t="n">
-        <v>0.3907465040683746</v>
+        <v>0.390746533870697</v>
       </c>
       <c r="C189" t="n">
         <v>27.78414726257324</v>
@@ -5363,7 +5363,7 @@
         <v>0.9696836471557617</v>
       </c>
       <c r="B190" t="n">
-        <v>0.4164748787879944</v>
+        <v>0.4164749085903168</v>
       </c>
       <c r="C190" t="n">
         <v>27.27387237548828</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.9719565510749817</v>
+        <v>0.9719566106796265</v>
       </c>
       <c r="B195" t="n">
         <v>0.5456681847572327</v>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.977044939994812</v>
+        <v>0.9770449995994568</v>
       </c>
       <c r="B196" t="n">
         <v>0.5650774240493774</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B200" t="n">
         <v>0.61091148853302</v>
@@ -5646,7 +5646,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B201" t="n">
         <v>0.624312162399292</v>
@@ -5672,7 +5672,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B202" t="n">
         <v>0.6430636048316956</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B203" t="n">
         <v>0.6665224432945251</v>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.009759274311363697</v>
+        <v>0.009759307838976383</v>
       </c>
       <c r="B204" t="n">
         <v>0.6941239833831787</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.03729578480124474</v>
+        <v>0.03729581832885742</v>
       </c>
       <c r="B205" t="n">
         <v>0.7251701354980469</v>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.07081446051597595</v>
+        <v>0.07081443071365356</v>
       </c>
       <c r="B206" t="n">
         <v>0.7585616111755371</v>
@@ -5802,7 +5802,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.1076857149600983</v>
+        <v>0.1076857447624207</v>
       </c>
       <c r="B207" t="n">
         <v>0.7928006649017334</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0.1469742655754089</v>
+        <v>0.1469742357730865</v>
       </c>
       <c r="B208" t="n">
         <v>0.8261861205101013</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0.1881630420684814</v>
+        <v>0.1881630122661591</v>
       </c>
       <c r="B209" t="n">
         <v>0.8571828603744507</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.2293924987316132</v>
+        <v>0.2293924391269684</v>
       </c>
       <c r="B210" t="n">
         <v>0.8846994042396545</v>
@@ -6143,7 +6143,7 @@
         <v>0.5398764610290527</v>
       </c>
       <c r="B220" t="n">
-        <v>0.956315279006958</v>
+        <v>0.9563153386116028</v>
       </c>
       <c r="C220" t="n">
         <v>-8.682629585266113</v>
@@ -6273,7 +6273,7 @@
         <v>0.5842673182487488</v>
       </c>
       <c r="B225" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C225" t="n">
         <v>-7.674902439117432</v>
@@ -6299,7 +6299,7 @@
         <v>0.6003067493438721</v>
       </c>
       <c r="B226" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C226" t="n">
         <v>-5.44089937210083</v>
@@ -6325,7 +6325,7 @@
         <v>0.6224095225334167</v>
       </c>
       <c r="B227" t="n">
-        <v>5.747634349972941e-05</v>
+        <v>5.749394767917693e-05</v>
       </c>
       <c r="C227" t="n">
         <v>-2.660976886749268</v>
@@ -6351,7 +6351,7 @@
         <v>0.6499136090278625</v>
       </c>
       <c r="B228" t="n">
-        <v>0.009586411528289318</v>
+        <v>0.009586429223418236</v>
       </c>
       <c r="C228" t="n">
         <v>0.7270388007164001</v>
@@ -6377,7 +6377,7 @@
         <v>0.6834339499473572</v>
       </c>
       <c r="B229" t="n">
-        <v>0.02728827483952045</v>
+        <v>0.02728829346597195</v>
       </c>
       <c r="C229" t="n">
         <v>4.71494722366333</v>
@@ -6403,7 +6403,7 @@
         <v>0.7228895425796509</v>
       </c>
       <c r="B230" t="n">
-        <v>0.05262782052159309</v>
+        <v>0.05262783542275429</v>
       </c>
       <c r="C230" t="n">
         <v>9.05533504486084</v>
@@ -6429,7 +6429,7 @@
         <v>0.7658325433731079</v>
       </c>
       <c r="B231" t="n">
-        <v>0.08349384367465973</v>
+        <v>0.08349386602640152</v>
       </c>
       <c r="C231" t="n">
         <v>13.32387351989746</v>
@@ -6455,7 +6455,7 @@
         <v>0.8080646395683289</v>
       </c>
       <c r="B232" t="n">
-        <v>0.117336705327034</v>
+        <v>0.1173367276787758</v>
       </c>
       <c r="C232" t="n">
         <v>17.14870452880859</v>
@@ -6481,7 +6481,7 @@
         <v>0.8459067940711975</v>
       </c>
       <c r="B233" t="n">
-        <v>0.1521753817796707</v>
+        <v>0.1521754264831543</v>
       </c>
       <c r="C233" t="n">
         <v>20.35327529907227</v>
@@ -6507,7 +6507,7 @@
         <v>0.8776121735572815</v>
       </c>
       <c r="B234" t="n">
-        <v>0.1868474036455154</v>
+        <v>0.1868473887443542</v>
       </c>
       <c r="C234" t="n">
         <v>22.93546867370605</v>
@@ -6533,7 +6533,7 @@
         <v>0.9031599164009094</v>
       </c>
       <c r="B235" t="n">
-        <v>0.2206747680902481</v>
+        <v>0.2206747531890869</v>
       </c>
       <c r="C235" t="n">
         <v>24.91757965087891</v>
@@ -6559,7 +6559,7 @@
         <v>0.9227705597877502</v>
       </c>
       <c r="B236" t="n">
-        <v>0.2531938254833221</v>
+        <v>0.2531938552856445</v>
       </c>
       <c r="C236" t="n">
         <v>26.29769325256348</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B239" t="n">
         <v>0.3433105647563934</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B240" t="n">
         <v>0.3732841610908508</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B241" t="n">
-        <v>0.4047657251358032</v>
+        <v>0.4047656953334808</v>
       </c>
       <c r="C241" t="n">
         <v>26.39948081970215</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B242" t="n">
         <v>0.437834769487381</v>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B243" t="n">
         <v>0.4715505540370941</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B244" t="n">
         <v>0.50430828332901</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.9468367099761963</v>
+        <v>0.9468367695808411</v>
       </c>
       <c r="B245" t="n">
         <v>0.5344384908676147</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0.9630874991416931</v>
+        <v>0.9630875587463379</v>
       </c>
       <c r="B248" t="n">
         <v>0.5954729914665222</v>
@@ -6894,7 +6894,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.9670506715774536</v>
+        <v>0.9670507311820984</v>
       </c>
       <c r="B249" t="n">
         <v>0.6019418835639954</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B251" t="n">
         <v>0.601510226726532</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B252" t="n">
         <v>0.6168283820152283</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B253" t="n">
         <v>0.638782799243927</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>0.001692262594588101</v>
+        <v>0.001692295772954822</v>
       </c>
       <c r="B254" t="n">
         <v>0.6668967008590698</v>
@@ -7050,7 +7050,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>0.018774239346385</v>
+        <v>0.01877427101135254</v>
       </c>
       <c r="B255" t="n">
         <v>0.7001776099205017</v>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>0.04923167452216148</v>
+        <v>0.04923170804977417</v>
       </c>
       <c r="B256" t="n">
         <v>0.7368854284286499</v>
@@ -7102,7 +7102,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>0.08755680918693542</v>
+        <v>0.08755683898925781</v>
       </c>
       <c r="B257" t="n">
         <v>0.7744016051292419</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>0.2266506254673004</v>
+        <v>0.226650595664978</v>
       </c>
       <c r="B261" t="n">
         <v>0.8933151364326477</v>
@@ -7599,7 +7599,7 @@
         <v>0.5807086825370789</v>
       </c>
       <c r="B276" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C276" t="n">
         <v>-9.380330085754395</v>
@@ -7625,7 +7625,7 @@
         <v>0.5990108847618103</v>
       </c>
       <c r="B277" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C277" t="n">
         <v>-7.038326740264893</v>
@@ -7651,7 +7651,7 @@
         <v>0.6218882203102112</v>
       </c>
       <c r="B278" t="n">
-        <v>0.00163664179854095</v>
+        <v>0.00163659977260977</v>
       </c>
       <c r="C278" t="n">
         <v>-4.389912128448486</v>
@@ -7677,7 +7677,7 @@
         <v>0.6477586627006531</v>
       </c>
       <c r="B279" t="n">
-        <v>0.01145275216549635</v>
+        <v>0.01145276986062527</v>
       </c>
       <c r="C279" t="n">
         <v>-1.338901996612549</v>
@@ -7703,7 +7703,7 @@
         <v>0.6775618195533752</v>
       </c>
       <c r="B280" t="n">
-        <v>0.02913971431553364</v>
+        <v>0.02913973294198513</v>
       </c>
       <c r="C280" t="n">
         <v>2.275186061859131</v>
@@ -7729,7 +7729,7 @@
         <v>0.7128652334213257</v>
       </c>
       <c r="B281" t="n">
-        <v>0.05478699877858162</v>
+        <v>0.05478701367974281</v>
       </c>
       <c r="C281" t="n">
         <v>6.418019771575928</v>
@@ -7755,7 +7755,7 @@
         <v>0.7533336281776428</v>
       </c>
       <c r="B282" t="n">
-        <v>0.08674384653568268</v>
+        <v>0.08674380928277969</v>
       </c>
       <c r="C282" t="n">
         <v>10.78283405303955</v>
@@ -7781,7 +7781,7 @@
         <v>0.7959703803062439</v>
       </c>
       <c r="B283" t="n">
-        <v>0.1224347203969955</v>
+        <v>0.1224347129464149</v>
       </c>
       <c r="C283" t="n">
         <v>14.93144512176514</v>
@@ -7807,7 +7807,7 @@
         <v>0.8364951610565186</v>
       </c>
       <c r="B284" t="n">
-        <v>0.1595107465982437</v>
+        <v>0.1595107316970825</v>
       </c>
       <c r="C284" t="n">
         <v>18.52582550048828</v>
@@ -7833,7 +7833,7 @@
         <v>0.8716061115264893</v>
       </c>
       <c r="B285" t="n">
-        <v>0.196522131562233</v>
+        <v>0.1965221464633942</v>
       </c>
       <c r="C285" t="n">
         <v>21.44092559814453</v>
@@ -7859,7 +7859,7 @@
         <v>0.9000815749168396</v>
       </c>
       <c r="B286" t="n">
-        <v>0.232818529009819</v>
+        <v>0.2328185737133026</v>
       </c>
       <c r="C286" t="n">
         <v>23.69665718078613</v>
@@ -7908,7 +7908,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>0.9382444620132446</v>
+        <v>0.9382445216178894</v>
       </c>
       <c r="B288" t="n">
         <v>0.3018938004970551</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>0.9488030672073364</v>
+        <v>0.9488031268119812</v>
       </c>
       <c r="B289" t="n">
         <v>0.3342284560203552</v>
@@ -7960,7 +7960,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>0.9541656970977783</v>
+        <v>0.9541657567024231</v>
       </c>
       <c r="B290" t="n">
         <v>0.3652673661708832</v>
@@ -7989,7 +7989,7 @@
         <v>0.9551000595092773</v>
       </c>
       <c r="B291" t="n">
-        <v>0.3956667184829712</v>
+        <v>0.3956666886806488</v>
       </c>
       <c r="C291" t="n">
         <v>26.84768867492676</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B302" t="n">
         <v>0.600782036781311</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B303" t="n">
         <v>0.6182987093925476</v>
@@ -8324,7 +8324,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B304" t="n">
         <v>0.6425997018814087</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B305" t="n">
         <v>0.672157883644104</v>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>0.009389785118401051</v>
+        <v>0.009389759041368961</v>
       </c>
       <c r="B306" t="n">
         <v>0.7053779363632202</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0.03655102476477623</v>
+        <v>0.03655105829238892</v>
       </c>
       <c r="B307" t="n">
         <v>0.7408807277679443</v>
@@ -8428,7 +8428,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>0.07076838612556458</v>
+        <v>0.07076835632324219</v>
       </c>
       <c r="B308" t="n">
         <v>0.777343213558197</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>0.1071420907974243</v>
+        <v>0.1071420609951019</v>
       </c>
       <c r="B309" t="n">
         <v>0.8133320212364197</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>0.1430668532848358</v>
+        <v>0.1430668234825134</v>
       </c>
       <c r="B310" t="n">
         <v>0.8473382592201233</v>
@@ -8506,7 +8506,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>0.1784206330776215</v>
+        <v>0.1784206032752991</v>
       </c>
       <c r="B311" t="n">
         <v>0.8779739141464233</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>0.2142402231693268</v>
+        <v>0.2142402529716492</v>
       </c>
       <c r="B312" t="n">
         <v>0.9041112065315247</v>
@@ -8639,7 +8639,7 @@
         <v>0.3591820001602173</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C316" t="n">
         <v>2.043290615081787</v>
@@ -8665,7 +8665,7 @@
         <v>0.3922938108444214</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C317" t="n">
         <v>-0.2908263504505157</v>
@@ -8691,7 +8691,7 @@
         <v>0.4238210916519165</v>
       </c>
       <c r="B318" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C318" t="n">
         <v>-2.513737201690674</v>
@@ -8717,7 +8717,7 @@
         <v>0.453846275806427</v>
       </c>
       <c r="B319" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C319" t="n">
         <v>-4.596842288970947</v>
@@ -8743,7 +8743,7 @@
         <v>0.481983095407486</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C320" t="n">
         <v>-6.49478006362915</v>
@@ -8769,7 +8769,7 @@
         <v>0.5076188445091248</v>
       </c>
       <c r="B321" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C321" t="n">
         <v>-8.176962852478027</v>
@@ -8795,7 +8795,7 @@
         <v>0.5303403735160828</v>
       </c>
       <c r="B322" t="n">
-        <v>0.9525792598724365</v>
+        <v>0.9525793194770813</v>
       </c>
       <c r="C322" t="n">
         <v>-9.616084098815918</v>
@@ -8925,7 +8925,7 @@
         <v>0.5841001272201538</v>
       </c>
       <c r="B327" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C327" t="n">
         <v>-8.463540077209473</v>
@@ -8951,7 +8951,7 @@
         <v>0.601605236530304</v>
       </c>
       <c r="B328" t="n">
-        <v>0.001552003202959895</v>
+        <v>0.001552020781673491</v>
       </c>
       <c r="C328" t="n">
         <v>-6.209860324859619</v>
@@ -8977,7 +8977,7 @@
         <v>0.6243067979812622</v>
       </c>
       <c r="B329" t="n">
-        <v>0.005020695738494396</v>
+        <v>0.005020712967962027</v>
       </c>
       <c r="C329" t="n">
         <v>-3.597980976104736</v>
@@ -9003,7 +9003,7 @@
         <v>0.6506165862083435</v>
       </c>
       <c r="B330" t="n">
-        <v>0.01238395553082228</v>
+        <v>0.01238391362130642</v>
       </c>
       <c r="C330" t="n">
         <v>-0.597452700138092</v>
@@ -9029,7 +9029,7 @@
         <v>0.680841326713562</v>
       </c>
       <c r="B331" t="n">
-        <v>0.02671314962208271</v>
+        <v>0.02671310864388943</v>
       </c>
       <c r="C331" t="n">
         <v>2.856654644012451</v>
@@ -9055,7 +9055,7 @@
         <v>0.7156350016593933</v>
       </c>
       <c r="B332" t="n">
-        <v>0.04959316924214363</v>
+        <v>0.04959318414330482</v>
       </c>
       <c r="C332" t="n">
         <v>6.671505451202393</v>
@@ -9081,7 +9081,7 @@
         <v>0.7540625333786011</v>
       </c>
       <c r="B333" t="n">
-        <v>0.07986350357532501</v>
+        <v>0.07986346632242203</v>
       </c>
       <c r="C333" t="n">
         <v>10.58195209503174</v>
@@ -9107,7 +9107,7 @@
         <v>0.7934529781341553</v>
       </c>
       <c r="B334" t="n">
-        <v>0.1146613210439682</v>
+        <v>0.11466134339571</v>
       </c>
       <c r="C334" t="n">
         <v>14.29731559753418</v>
@@ -9133,7 +9133,7 @@
         <v>0.8308783173561096</v>
       </c>
       <c r="B335" t="n">
-        <v>0.1510563045740128</v>
+        <v>0.1510562896728516</v>
       </c>
       <c r="C335" t="n">
         <v>17.62735366821289</v>
@@ -9159,7 +9159,7 @@
         <v>0.8644222021102905</v>
       </c>
       <c r="B336" t="n">
-        <v>0.1869302242994308</v>
+        <v>0.1869302093982697</v>
       </c>
       <c r="C336" t="n">
         <v>20.49263000488281</v>
@@ -9185,7 +9185,7 @@
         <v>0.8932844996452332</v>
       </c>
       <c r="B337" t="n">
-        <v>0.2210686951875687</v>
+        <v>0.2210687100887299</v>
       </c>
       <c r="C337" t="n">
         <v>22.85014343261719</v>
@@ -9289,7 +9289,7 @@
         <v>0.9529967308044434</v>
       </c>
       <c r="B341" t="n">
-        <v>0.3407754302024841</v>
+        <v>0.3407754600048065</v>
       </c>
       <c r="C341" t="n">
         <v>26.52870178222656</v>
@@ -9598,7 +9598,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2.717084690573301e-08</v>
+        <v>6.666477370131929e-10</v>
       </c>
       <c r="B353" t="n">
         <v>0.6068375706672668</v>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>0.01942178420722485</v>
+        <v>0.01942175626754761</v>
       </c>
       <c r="B354" t="n">
         <v>0.6101404428482056</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>0.04271557554602623</v>
+        <v>0.04271560907363892</v>
       </c>
       <c r="B355" t="n">
         <v>0.6210901141166687</v>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>0.06969442963600159</v>
+        <v>0.06969445943832397</v>
       </c>
       <c r="B356" t="n">
         <v>0.6405146718025208</v>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>0.1356553435325623</v>
+        <v>0.1356553137302399</v>
       </c>
       <c r="B358" t="n">
         <v>0.7039221525192261</v>
@@ -9887,7 +9887,7 @@
         <v>0.3480962216854095</v>
       </c>
       <c r="B364" t="n">
-        <v>0.9312896132469177</v>
+        <v>0.9312896728515625</v>
       </c>
       <c r="C364" t="n">
         <v>7.528273105621338</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>0.374766618013382</v>
+        <v>0.3747666478157043</v>
       </c>
       <c r="B365" t="n">
         <v>0.956081748008728</v>
@@ -10017,7 +10017,7 @@
         <v>0.4681011438369751</v>
       </c>
       <c r="B369" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C369" t="n">
         <v>-0.09775307774543762</v>
@@ -10043,7 +10043,7 @@
         <v>0.4906794726848602</v>
       </c>
       <c r="B370" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C370" t="n">
         <v>-1.537333011627197</v>
@@ -10069,7 +10069,7 @@
         <v>0.5125605463981628</v>
       </c>
       <c r="B371" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C371" t="n">
         <v>-2.873898029327393</v>
@@ -10095,7 +10095,7 @@
         <v>0.5328758955001831</v>
       </c>
       <c r="B372" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C372" t="n">
         <v>-4.061039447784424</v>
@@ -10121,7 +10121,7 @@
         <v>0.5509199500083923</v>
       </c>
       <c r="B373" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C373" t="n">
         <v>-5.103540897369385</v>
@@ -10147,7 +10147,7 @@
         <v>0.5667656660079956</v>
       </c>
       <c r="B374" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C374" t="n">
         <v>-6.032995700836182</v>
@@ -10173,7 +10173,7 @@
         <v>0.5808930397033691</v>
       </c>
       <c r="B375" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C375" t="n">
         <v>-6.888832569122314</v>
@@ -10199,7 +10199,7 @@
         <v>0.5939013957977295</v>
       </c>
       <c r="B376" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C376" t="n">
         <v>-7.680296421051025</v>
@@ -10225,7 +10225,7 @@
         <v>0.6059313416481018</v>
       </c>
       <c r="B377" t="n">
-        <v>0.9953081011772156</v>
+        <v>0.9953081607818604</v>
       </c>
       <c r="C377" t="n">
         <v>-8.333846092224121</v>
@@ -10251,7 +10251,7 @@
         <v>0.6158651113510132</v>
       </c>
       <c r="B378" t="n">
-        <v>1.746720634798749e-08</v>
+        <v>-2.453420044901122e-08</v>
       </c>
       <c r="C378" t="n">
         <v>-8.65126895904541</v>
@@ -10277,7 +10277,7 @@
         <v>0.6206898093223572</v>
       </c>
       <c r="B379" t="n">
-        <v>0.01182581763714552</v>
+        <v>0.01182577572762966</v>
       </c>
       <c r="C379" t="n">
         <v>-8.401888847351074</v>
@@ -10303,7 +10303,7 @@
         <v>0.6230062246322632</v>
       </c>
       <c r="B380" t="n">
-        <v>0.02597256191074848</v>
+        <v>0.02597258053719997</v>
       </c>
       <c r="C380" t="n">
         <v>-7.352436542510986</v>
@@ -10329,7 +10329,7 @@
         <v>0.6327542066574097</v>
       </c>
       <c r="B381" t="n">
-        <v>0.04351838305592537</v>
+        <v>0.04351839795708656</v>
       </c>
       <c r="C381" t="n">
         <v>-5.302992343902588</v>
@@ -10355,7 +10355,7 @@
         <v>0.6517907977104187</v>
       </c>
       <c r="B382" t="n">
-        <v>0.06616111099720001</v>
+        <v>0.0661611333489418</v>
       </c>
       <c r="C382" t="n">
         <v>-2.296520709991455</v>
@@ -10381,7 +10381,7 @@
         <v>0.6797168850898743</v>
       </c>
       <c r="B383" t="n">
-        <v>0.09439642727375031</v>
+        <v>0.0943964496254921</v>
       </c>
       <c r="C383" t="n">
         <v>1.515322208404541</v>
@@ -10407,7 +10407,7 @@
         <v>0.7151238322257996</v>
       </c>
       <c r="B384" t="n">
-        <v>0.1276995986700058</v>
+        <v>0.127699613571167</v>
       </c>
       <c r="C384" t="n">
         <v>5.889498233795166</v>
@@ -10433,7 +10433,7 @@
         <v>0.7557540535926819</v>
       </c>
       <c r="B385" t="n">
-        <v>0.1646370440721512</v>
+        <v>0.16463702917099</v>
       </c>
       <c r="C385" t="n">
         <v>10.48462867736816</v>
@@ -10459,7 +10459,7 @@
         <v>0.7984366416931152</v>
       </c>
       <c r="B386" t="n">
-        <v>0.20321224629879</v>
+        <v>0.2032122015953064</v>
       </c>
       <c r="C386" t="n">
         <v>15.02622032165527</v>
@@ -10485,7 +10485,7 @@
         <v>0.8406220078468323</v>
       </c>
       <c r="B387" t="n">
-        <v>0.2418541759252548</v>
+        <v>0.241854190826416</v>
       </c>
       <c r="C387" t="n">
         <v>19.31408309936523</v>
@@ -10560,7 +10560,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>0.9489969611167908</v>
+        <v>0.9489970207214355</v>
       </c>
       <c r="B390" t="n">
         <v>0.3453842103481293</v>
@@ -10638,7 +10638,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B393" t="n">
         <v>0.423722505569458</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B394" t="n">
         <v>0.4469288289546967</v>
@@ -10690,7 +10690,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B395" t="n">
         <v>0.4699062407016754</v>
@@ -10716,7 +10716,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B396" t="n">
         <v>0.4925375878810883</v>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B397" t="n">
         <v>0.5140998363494873</v>
@@ -10768,7 +10768,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B398" t="n">
         <v>0.5338999629020691</v>
@@ -10794,7 +10794,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B399" t="n">
         <v>0.551588237285614</v>
@@ -10820,7 +10820,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B400" t="n">
         <v>0.5673367977142334</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>0.9999989867210388</v>
+        <v>1</v>
       </c>
       <c r="B401" t="n">
         <v>0.581520140171051</v>
